--- a/Excel/liste_complete.xlsx
+++ b/Excel/liste_complete.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookViews>
-    <workbookView activeTab="-1"/>
+    <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Export" sheetId="1" r:id="rId3"/>
+    <sheet name="Export" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Export'!$A$1:$J$132</definedName>

--- a/Excel/liste_complete.xlsx
+++ b/Excel/liste_complete.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookViews>
-    <workbookView/>
+    <workbookView activeTab="-1"/>
   </bookViews>
   <sheets>
-    <sheet name="Export" sheetId="1" r:id="rId1"/>
+    <sheet name="Export" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Export'!$A$1:$J$132</definedName>

--- a/Excel/liste_complete.xlsx
+++ b/Excel/liste_complete.xlsx
@@ -8,14 +8,14 @@
     <sheet name="Export" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Export'!$A$1:$J$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Export'!$A$1:$J$129</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="455">
   <si>
     <t>GROUPE</t>
   </si>
@@ -53,1255 +53,1240 @@
     <t>Marie-Joëlle / Nicolette LECOQ</t>
   </si>
   <si>
+    <t>AHMED MOHAMED OSMAN</t>
+  </si>
+  <si>
+    <t>Monira</t>
+  </si>
+  <si>
+    <t>01/01/1987</t>
+  </si>
+  <si>
+    <t>Soudan</t>
+  </si>
+  <si>
+    <t>Afrique</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
+  </si>
+  <si>
+    <t>MPUTU</t>
+  </si>
+  <si>
+    <t>Bella</t>
+  </si>
+  <si>
+    <t>20/05/1998</t>
+  </si>
+  <si>
+    <t>RDC</t>
+  </si>
+  <si>
+    <t>04/11/2025</t>
+  </si>
+  <si>
+    <t>PETROSYAN</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t>07/10/1992</t>
+  </si>
+  <si>
+    <t>Arménie</t>
+  </si>
+  <si>
+    <t>Asie</t>
+  </si>
+  <si>
+    <t>20/03/2025</t>
+  </si>
+  <si>
+    <t>POGHOSYAN</t>
+  </si>
+  <si>
+    <t>Gayane</t>
+  </si>
+  <si>
+    <t>25/09/1960</t>
+  </si>
+  <si>
+    <t>27/09/2023</t>
+  </si>
+  <si>
+    <t>SAYED</t>
+  </si>
+  <si>
+    <t>Mohammad</t>
+  </si>
+  <si>
+    <t>05/08/1989</t>
+  </si>
+  <si>
+    <t>Allemagne</t>
+  </si>
+  <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>16/09/2025</t>
+  </si>
+  <si>
+    <t>Tamara</t>
+  </si>
+  <si>
+    <t>24/07/1985</t>
+  </si>
+  <si>
+    <t>YELEJYAN</t>
+  </si>
+  <si>
+    <t>Gohar</t>
+  </si>
+  <si>
+    <t>20/12/1983</t>
+  </si>
+  <si>
+    <t>03/09/2025</t>
+  </si>
+  <si>
+    <t>Hélène Tharaud / Christiane PETIT</t>
+  </si>
+  <si>
+    <t>KVARATSKHEILIA</t>
+  </si>
+  <si>
+    <t>Giorgi</t>
+  </si>
+  <si>
+    <t>13/03/2022</t>
+  </si>
+  <si>
+    <t>Géorgie</t>
+  </si>
+  <si>
+    <t>06/11/2025</t>
+  </si>
+  <si>
+    <t>MAKSHARPOV</t>
+  </si>
+  <si>
+    <t>Umar</t>
+  </si>
+  <si>
+    <t>21/01/1979</t>
+  </si>
+  <si>
+    <t>Tchétchénie</t>
+  </si>
+  <si>
+    <t>08/01/2023</t>
+  </si>
+  <si>
+    <t>MIAKHAIL</t>
+  </si>
+  <si>
+    <t>Karimullah</t>
+  </si>
+  <si>
+    <t>Afghanistan</t>
+  </si>
+  <si>
+    <t>20/11/2025</t>
+  </si>
+  <si>
+    <t>NKAMBA</t>
+  </si>
+  <si>
+    <t>Albertina</t>
+  </si>
+  <si>
+    <t>10/05/1959</t>
+  </si>
+  <si>
+    <t>Angola</t>
+  </si>
+  <si>
+    <t>25/02/2025</t>
+  </si>
+  <si>
+    <t>NYINGPA</t>
+  </si>
+  <si>
+    <t>Damchoe</t>
+  </si>
+  <si>
+    <t>02/07/1991</t>
+  </si>
+  <si>
+    <t>Tibet</t>
+  </si>
+  <si>
+    <t>07/10/2025</t>
+  </si>
+  <si>
+    <t>ONAL</t>
+  </si>
+  <si>
+    <t>Ali Imran</t>
+  </si>
+  <si>
+    <t>18/08/2006</t>
+  </si>
+  <si>
+    <t>Turquie</t>
+  </si>
+  <si>
+    <t>09/10/2025</t>
+  </si>
+  <si>
+    <t>POHOSIAN</t>
+  </si>
+  <si>
+    <t>Mykhailo</t>
+  </si>
+  <si>
+    <t>11/01/1953</t>
+  </si>
+  <si>
+    <t>Ukraine</t>
+  </si>
+  <si>
+    <t>SAKHESVILI</t>
+  </si>
+  <si>
+    <t>Eldari</t>
+  </si>
+  <si>
+    <t>10/02/1985</t>
+  </si>
+  <si>
+    <t>SHELIA</t>
+  </si>
+  <si>
+    <t>Vakhtang</t>
+  </si>
+  <si>
+    <t>06/02/1963</t>
+  </si>
+  <si>
+    <t>10/09/2024</t>
+  </si>
+  <si>
+    <t>TENZIN</t>
+  </si>
+  <si>
+    <t>Nyima</t>
+  </si>
+  <si>
+    <t>10/06/1997</t>
+  </si>
+  <si>
+    <t>TSANG</t>
+  </si>
+  <si>
+    <t>Karma</t>
+  </si>
+  <si>
+    <t>15/05/1988</t>
+  </si>
+  <si>
+    <t>Chine</t>
+  </si>
+  <si>
+    <t>Sylvie LABBE / Chantal PREVOST</t>
+  </si>
+  <si>
+    <t>ABIA</t>
+  </si>
+  <si>
+    <t>Flore</t>
+  </si>
+  <si>
+    <t>19/08/2000</t>
+  </si>
+  <si>
+    <t>23/09/2025</t>
+  </si>
+  <si>
+    <t>AVAGYAN</t>
+  </si>
+  <si>
+    <t>Karen</t>
+  </si>
+  <si>
+    <t>04/10/1980</t>
+  </si>
+  <si>
+    <t>10/12/2024</t>
+  </si>
+  <si>
+    <t>BURDULI</t>
+  </si>
+  <si>
+    <t>Sopio</t>
+  </si>
+  <si>
+    <t>02/04/1997</t>
+  </si>
+  <si>
+    <t>11/10/2023</t>
+  </si>
+  <si>
+    <t>HIRPA</t>
+  </si>
+  <si>
+    <t>Wakgari</t>
+  </si>
+  <si>
+    <t>Ethiopie</t>
+  </si>
+  <si>
+    <t>JISHKARIANI</t>
+  </si>
+  <si>
+    <t>Nino</t>
+  </si>
+  <si>
+    <t>11/02/1980</t>
+  </si>
+  <si>
+    <t>KATCHATRYAN</t>
+  </si>
+  <si>
+    <t>20/05/1980</t>
+  </si>
+  <si>
+    <t>07/11/2025</t>
+  </si>
+  <si>
+    <t>Mariam</t>
+  </si>
+  <si>
+    <t>26/08/1986</t>
+  </si>
+  <si>
+    <t>06/10/2022</t>
+  </si>
+  <si>
+    <t>MUGENI</t>
+  </si>
+  <si>
+    <t>Chantal</t>
+  </si>
+  <si>
+    <t>31/12/1996</t>
+  </si>
+  <si>
+    <t>MUSTAFAYEV</t>
+  </si>
+  <si>
+    <t>Elshan</t>
+  </si>
+  <si>
+    <t>17/07/1978</t>
+  </si>
+  <si>
+    <t>Azerbaïdjan</t>
+  </si>
+  <si>
+    <t>NAJJAR</t>
+  </si>
+  <si>
+    <t>Wuod</t>
+  </si>
+  <si>
+    <t>01/06/1970</t>
+  </si>
+  <si>
+    <t>Irak</t>
+  </si>
+  <si>
+    <t>15/11/2022</t>
+  </si>
+  <si>
+    <t>Prénom</t>
+  </si>
+  <si>
+    <t>02/03/1960</t>
+  </si>
+  <si>
+    <t>Andorre</t>
+  </si>
+  <si>
+    <t>02/05/2026</t>
+  </si>
+  <si>
+    <t>PETUKHOVA</t>
+  </si>
+  <si>
+    <t>Mariila</t>
+  </si>
+  <si>
+    <t>05/11/1951</t>
+  </si>
+  <si>
+    <t>10/09/2025</t>
+  </si>
+  <si>
+    <t>RAHHAL</t>
+  </si>
+  <si>
+    <t>Abdelkader</t>
+  </si>
+  <si>
+    <t>03/07/1984</t>
+  </si>
+  <si>
+    <t>Algérie</t>
+  </si>
+  <si>
+    <t>01/09/2025</t>
+  </si>
+  <si>
+    <t>SELIMAN</t>
+  </si>
+  <si>
+    <t>Kajol</t>
+  </si>
+  <si>
+    <t>08/07/2004</t>
+  </si>
+  <si>
+    <t>SHOTSHA</t>
+  </si>
+  <si>
+    <t>M'wemwe</t>
+  </si>
+  <si>
+    <t>05/05/1981</t>
+  </si>
+  <si>
+    <t>TOLA</t>
+  </si>
+  <si>
+    <t>Boja</t>
+  </si>
+  <si>
+    <t>27/08/2004</t>
+  </si>
+  <si>
+    <t>TSAGAREISHVILI</t>
+  </si>
+  <si>
+    <t>Gela</t>
+  </si>
+  <si>
+    <t>05/11/1984</t>
+  </si>
+  <si>
+    <t>28/05/2024</t>
+  </si>
+  <si>
+    <t>Monique LAVANANT / Chantal MEREL / Mariannic'k GODIN</t>
+  </si>
+  <si>
+    <t>ABDRAMAN IBRAHIM</t>
+  </si>
+  <si>
+    <t>Saladin</t>
+  </si>
+  <si>
+    <t>05/07/1950</t>
+  </si>
+  <si>
+    <t>Kenya</t>
+  </si>
+  <si>
+    <t>AMRANI</t>
+  </si>
+  <si>
+    <t>Abdulkadir Mohamed</t>
+  </si>
+  <si>
+    <t>04/04/1975</t>
+  </si>
+  <si>
+    <t>Tanzannie</t>
+  </si>
+  <si>
+    <t>17/09/2024</t>
+  </si>
+  <si>
+    <t>BATOL</t>
+  </si>
+  <si>
+    <t>Hassan</t>
+  </si>
+  <si>
+    <t>15/05/1997</t>
+  </si>
+  <si>
+    <t>01/09/2024</t>
+  </si>
+  <si>
+    <t>BEZHANISHVILI</t>
+  </si>
+  <si>
+    <t>Zurab</t>
+  </si>
+  <si>
+    <t>30/06/1974</t>
+  </si>
+  <si>
+    <t>06/02/2025</t>
+  </si>
+  <si>
+    <t>BOUZID</t>
+  </si>
+  <si>
+    <t>Bouchra</t>
+  </si>
+  <si>
+    <t>01/01/1983</t>
+  </si>
+  <si>
+    <t>Maroc</t>
+  </si>
+  <si>
+    <t>24/03/2023</t>
+  </si>
+  <si>
+    <t>KALANDIA</t>
+  </si>
+  <si>
+    <t>Tamar</t>
+  </si>
+  <si>
+    <t>09/10/1979</t>
+  </si>
+  <si>
+    <t>22/05/2024</t>
+  </si>
+  <si>
+    <t>KHACHATRYAN</t>
+  </si>
+  <si>
+    <t>Rita</t>
+  </si>
+  <si>
+    <t>21/01/1973</t>
+  </si>
+  <si>
+    <t>01/10/2024</t>
+  </si>
+  <si>
+    <t>KHUTSISHVILI</t>
+  </si>
+  <si>
+    <t>Rusudan</t>
+  </si>
+  <si>
+    <t>08/11/1987</t>
+  </si>
+  <si>
+    <t>LENGO</t>
+  </si>
+  <si>
+    <t>Lucoqui</t>
+  </si>
+  <si>
+    <t>07/11/1984</t>
+  </si>
+  <si>
+    <t>24/04/2025</t>
+  </si>
+  <si>
+    <t>MAMBA</t>
+  </si>
+  <si>
+    <t>Benayi</t>
+  </si>
+  <si>
+    <t>15/07/1985</t>
+  </si>
+  <si>
+    <t>12/09/2024</t>
+  </si>
+  <si>
+    <t>MANTUIKA</t>
+  </si>
+  <si>
+    <t>Sara</t>
+  </si>
+  <si>
+    <t>15/12/1999</t>
+  </si>
+  <si>
+    <t>MEHMOOD</t>
+  </si>
+  <si>
+    <t>Aamir</t>
+  </si>
+  <si>
+    <t>15/05/1990</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>12/01/2025</t>
+  </si>
+  <si>
+    <t>MIAH</t>
+  </si>
+  <si>
+    <t>Mowab</t>
+  </si>
+  <si>
+    <t>28/05/1995</t>
+  </si>
+  <si>
+    <t>Bangladesh</t>
+  </si>
+  <si>
+    <t>01/09/2023</t>
+  </si>
+  <si>
+    <t>MOHAMED EL NOUR</t>
+  </si>
+  <si>
+    <t>Abdel</t>
+  </si>
+  <si>
+    <t>19/01/1977</t>
+  </si>
+  <si>
+    <t>MOHD</t>
+  </si>
+  <si>
+    <t>Azeem Pacha</t>
+  </si>
+  <si>
+    <t>04/04/1991</t>
+  </si>
+  <si>
+    <t>Inde</t>
+  </si>
+  <si>
+    <t>21/01/2025</t>
+  </si>
+  <si>
+    <t>NDUGBE</t>
+  </si>
+  <si>
+    <t>Josiah</t>
+  </si>
+  <si>
+    <t>10/10/1982</t>
+  </si>
+  <si>
+    <t>Nigéria</t>
+  </si>
+  <si>
+    <t>19/11/2023</t>
+  </si>
+  <si>
+    <t>NEHREBA</t>
+  </si>
+  <si>
+    <t>Iryna</t>
+  </si>
+  <si>
+    <t>28/02/1987</t>
+  </si>
+  <si>
+    <t>21/11/2024</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>Mohammed</t>
+  </si>
+  <si>
+    <t>01/01/1994</t>
+  </si>
+  <si>
+    <t>OVERCHENKO</t>
+  </si>
+  <si>
+    <t>Aleksandrova</t>
+  </si>
+  <si>
+    <t>30/09/1971</t>
+  </si>
+  <si>
+    <t>PINTO</t>
+  </si>
+  <si>
+    <t>Janet</t>
+  </si>
+  <si>
+    <t>23/02/1971</t>
+  </si>
+  <si>
+    <t>Pérou</t>
+  </si>
+  <si>
+    <t>Amérique du Sud</t>
+  </si>
+  <si>
+    <t>POPLEE</t>
+  </si>
+  <si>
+    <t>Daleep</t>
+  </si>
+  <si>
+    <t>01/09/1984</t>
+  </si>
+  <si>
+    <t>SHARIF IBRAHIM</t>
+  </si>
+  <si>
+    <t>Ahmed</t>
+  </si>
+  <si>
+    <t>01/01/1998</t>
+  </si>
+  <si>
+    <t>Somalie</t>
+  </si>
+  <si>
+    <t>SISSANI TORQUI</t>
+  </si>
+  <si>
+    <t>Malika</t>
+  </si>
+  <si>
+    <t>01/09/1956</t>
+  </si>
+  <si>
+    <t>Espagne</t>
+  </si>
+  <si>
+    <t>16/11/2023</t>
+  </si>
+  <si>
+    <t>YLDIRIM DOGAN</t>
+  </si>
+  <si>
+    <t>Ozgun</t>
+  </si>
+  <si>
+    <t>01/07/1979</t>
+  </si>
+  <si>
+    <t>Jocelyne PRECIADO / Véronique JANNES</t>
+  </si>
+  <si>
+    <t>ABAIDZE</t>
+  </si>
+  <si>
+    <t>Mariami</t>
+  </si>
+  <si>
+    <t>23/08/1991</t>
+  </si>
+  <si>
+    <t>ABDOU</t>
+  </si>
+  <si>
+    <t>Houfranie</t>
+  </si>
+  <si>
+    <t>31/12/1978</t>
+  </si>
+  <si>
+    <t>Comores</t>
+  </si>
+  <si>
+    <t>AHED MOHAMED</t>
+  </si>
+  <si>
+    <t>Mohamed</t>
+  </si>
+  <si>
+    <t>22/07/1993</t>
+  </si>
+  <si>
+    <t>01/05/2024</t>
+  </si>
+  <si>
+    <t>ALHAJ</t>
+  </si>
+  <si>
+    <t>Mudother</t>
+  </si>
+  <si>
+    <t>08/04/1999</t>
+  </si>
+  <si>
+    <t>25/11/2024</t>
+  </si>
+  <si>
+    <t>BEGUM</t>
+  </si>
+  <si>
+    <t>Lima</t>
+  </si>
+  <si>
+    <t>10/12/1990</t>
+  </si>
+  <si>
+    <t>CHKHAPELIA</t>
+  </si>
+  <si>
+    <t>Tamta</t>
+  </si>
+  <si>
+    <t>01/04/1992</t>
+  </si>
+  <si>
+    <t>01/01/2022</t>
+  </si>
+  <si>
+    <t>DIAMPITISA</t>
+  </si>
+  <si>
+    <t>Madalena</t>
+  </si>
+  <si>
+    <t>02/11/1967</t>
+  </si>
+  <si>
+    <t>EBRAHIM DUD</t>
+  </si>
+  <si>
+    <t>Nabil</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>Kiala Baptista</t>
+  </si>
+  <si>
+    <t>31/12/1994</t>
+  </si>
+  <si>
+    <t>ELIDRISSI BOUANANI</t>
+  </si>
+  <si>
+    <t>Fatima</t>
+  </si>
+  <si>
+    <t>01/01/1959</t>
+  </si>
+  <si>
+    <t>15/09/2022</t>
+  </si>
+  <si>
+    <t>FURAH KITAMBALA</t>
+  </si>
+  <si>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>26/11/2025</t>
+  </si>
+  <si>
+    <t>HASHEMI</t>
+  </si>
+  <si>
+    <t>Asghar</t>
+  </si>
+  <si>
+    <t>28/02/1999</t>
+  </si>
+  <si>
+    <t>IMERI</t>
+  </si>
+  <si>
+    <t>Mirela</t>
+  </si>
+  <si>
+    <t>30/05/1977</t>
+  </si>
+  <si>
+    <t>Albanie</t>
+  </si>
+  <si>
+    <t>10/05/2022</t>
+  </si>
+  <si>
+    <t>IREDIA</t>
+  </si>
+  <si>
+    <t>Tracy</t>
+  </si>
+  <si>
+    <t>27/07/1982</t>
+  </si>
+  <si>
+    <t>ISOMI</t>
+  </si>
+  <si>
+    <t>Febe</t>
+  </si>
+  <si>
+    <t>05/03/2001</t>
+  </si>
+  <si>
+    <t>JARA</t>
+  </si>
+  <si>
+    <t>Mario</t>
+  </si>
+  <si>
+    <t>19/01/2003</t>
+  </si>
+  <si>
+    <t>Chili</t>
+  </si>
+  <si>
+    <t>18/09/2025</t>
+  </si>
+  <si>
+    <t>KINAVUIDI</t>
+  </si>
+  <si>
+    <t>Viviane</t>
+  </si>
+  <si>
+    <t>29/06/1988</t>
+  </si>
+  <si>
+    <t>LAGOUNE</t>
+  </si>
+  <si>
+    <t>Ilham</t>
+  </si>
+  <si>
+    <t>15/08/2002</t>
+  </si>
+  <si>
+    <t>LUMBE OMOWO</t>
+  </si>
+  <si>
+    <t>Anne-Marie</t>
+  </si>
+  <si>
+    <t>18/03/1979</t>
+  </si>
+  <si>
+    <t>25/11/2025</t>
+  </si>
+  <si>
+    <t>MADALENA</t>
+  </si>
+  <si>
+    <t>Lidia</t>
+  </si>
+  <si>
+    <t>29/05/2018</t>
+  </si>
+  <si>
+    <t>14/11/2025</t>
+  </si>
+  <si>
+    <t>MATETA</t>
+  </si>
+  <si>
+    <t>Gloria</t>
+  </si>
+  <si>
+    <t>30/07/1994</t>
+  </si>
+  <si>
+    <t>NGELI</t>
+  </si>
+  <si>
+    <t>Yolande</t>
+  </si>
+  <si>
+    <t>06/12/1980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLIVEIRA </t>
+  </si>
+  <si>
+    <t>Laura</t>
+  </si>
+  <si>
+    <t>14/12/1986</t>
+  </si>
+  <si>
+    <t>02/06/2024</t>
+  </si>
+  <si>
+    <t>RIAHI</t>
+  </si>
+  <si>
+    <t>Souhail</t>
+  </si>
+  <si>
+    <t>13/11/1992</t>
+  </si>
+  <si>
+    <t>Tunisie</t>
+  </si>
+  <si>
+    <t>TIENE</t>
+  </si>
+  <si>
+    <t>Nawa</t>
+  </si>
+  <si>
+    <t>15/11/1996</t>
+  </si>
+  <si>
+    <t>Côte d'Ivoire</t>
+  </si>
+  <si>
+    <t>TINIKASCHVILI</t>
+  </si>
+  <si>
+    <t>Maka</t>
+  </si>
+  <si>
+    <t>21/09/1983</t>
+  </si>
+  <si>
+    <t>12/10/2021</t>
+  </si>
+  <si>
+    <t>TONOYAN</t>
+  </si>
+  <si>
+    <t>Alvard</t>
+  </si>
+  <si>
+    <t>10/01/1963</t>
+  </si>
+  <si>
+    <t>12/01/2016</t>
+  </si>
+  <si>
+    <t>VIUCHE GIRON</t>
+  </si>
+  <si>
+    <t>Sanyi</t>
+  </si>
+  <si>
+    <t>21/05/1995</t>
+  </si>
+  <si>
+    <t>Colombie</t>
+  </si>
+  <si>
+    <t>06/03/2025</t>
+  </si>
+  <si>
+    <t>Jean PITORIN / Jean-Luc HOUDAYER</t>
+  </si>
+  <si>
+    <t>BABALOLA</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
+    <t>10/11/1973</t>
+  </si>
+  <si>
+    <t>AFRIQUE</t>
+  </si>
+  <si>
+    <t>06/09/2022</t>
+  </si>
+  <si>
+    <t>01/12/2025</t>
+  </si>
+  <si>
+    <t>BARSEGHIAN</t>
+  </si>
+  <si>
+    <t>Norik</t>
+  </si>
+  <si>
+    <t>07/07/2006</t>
+  </si>
+  <si>
+    <t>11/09/2025</t>
+  </si>
+  <si>
+    <t>CARBONO FERNANDEZ</t>
+  </si>
+  <si>
+    <t>Carolina</t>
+  </si>
+  <si>
+    <t>16/01/2025</t>
+  </si>
+  <si>
+    <t>CHEGGARI</t>
+  </si>
+  <si>
+    <t>Nour Eddin</t>
+  </si>
+  <si>
+    <t>23/10/1994</t>
+  </si>
+  <si>
+    <t>31/05/2023</t>
+  </si>
+  <si>
+    <t>HALILAJ</t>
+  </si>
+  <si>
+    <t>Lindita</t>
+  </si>
+  <si>
+    <t>23/02/1979</t>
+  </si>
+  <si>
+    <t>09/11/2023</t>
+  </si>
+  <si>
+    <t>KIAKU</t>
+  </si>
+  <si>
+    <t>Ana Marcela</t>
+  </si>
+  <si>
+    <t>19/02/1992</t>
+  </si>
+  <si>
+    <t>20/09/2023</t>
+  </si>
+  <si>
+    <t>LMABROUK</t>
+  </si>
+  <si>
+    <t>Oussama</t>
+  </si>
+  <si>
+    <t>01/02/2025</t>
+  </si>
+  <si>
+    <t>MANGAY</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>25/06/1990</t>
+  </si>
+  <si>
+    <t>MENAYAME NGOMA</t>
+  </si>
+  <si>
+    <t>Mera</t>
+  </si>
+  <si>
+    <t>05/05/1994</t>
+  </si>
+  <si>
+    <t>MUSTAFAYEVA</t>
+  </si>
+  <si>
+    <t>Gulkanim</t>
+  </si>
+  <si>
+    <t>17/09/1990</t>
+  </si>
+  <si>
+    <t>26/06/2019</t>
+  </si>
+  <si>
+    <t>NYINAWUMUNTU</t>
+  </si>
+  <si>
+    <t>Marie-Louise</t>
+  </si>
+  <si>
+    <t>Rwanda</t>
+  </si>
+  <si>
+    <t>19/09/2024</t>
+  </si>
+  <si>
+    <t>OYEKAN</t>
+  </si>
+  <si>
+    <t>Patrick</t>
+  </si>
+  <si>
+    <t>17/01/1976</t>
+  </si>
+  <si>
+    <t>REYES OTERO</t>
+  </si>
+  <si>
+    <t>Victor Hugo</t>
+  </si>
+  <si>
+    <t>29/05/1986</t>
+  </si>
+  <si>
+    <t>06/05/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAUCEDO  FERNANDEZ</t>
+  </si>
+  <si>
+    <t>Verselia</t>
+  </si>
+  <si>
+    <t>03/07/1989</t>
+  </si>
+  <si>
+    <t>Samedi</t>
+  </si>
+  <si>
+    <t>Louise-Anne</t>
+  </si>
+  <si>
+    <t>ABAKAR ADAM</t>
+  </si>
+  <si>
+    <t>Seida</t>
+  </si>
+  <si>
+    <t>Soudan du Sud</t>
+  </si>
+  <si>
+    <t>ADDOUT SOULEMAN</t>
+  </si>
+  <si>
+    <t>Ibrahim</t>
+  </si>
+  <si>
     <t>AHMED</t>
   </si>
   <si>
-    <t>Ibrahim</t>
-  </si>
-  <si>
-    <t>01/01/1900</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>AHMED MOHAMED OSMAN</t>
-  </si>
-  <si>
-    <t>Monira</t>
-  </si>
-  <si>
-    <t>01/01/1987</t>
-  </si>
-  <si>
-    <t>Soudan</t>
-  </si>
-  <si>
-    <t>Afrique</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
-  </si>
-  <si>
-    <t>MPUTU</t>
-  </si>
-  <si>
-    <t>Bella</t>
-  </si>
-  <si>
-    <t>20/05/1998</t>
-  </si>
-  <si>
-    <t>RDC</t>
-  </si>
-  <si>
-    <t>04/11/2025</t>
-  </si>
-  <si>
-    <t>PETROSYAN</t>
-  </si>
-  <si>
-    <t>Anna</t>
-  </si>
-  <si>
-    <t>07/10/1992</t>
-  </si>
-  <si>
-    <t>Arménie</t>
-  </si>
-  <si>
-    <t>Asie</t>
-  </si>
-  <si>
-    <t>20/03/2025</t>
-  </si>
-  <si>
-    <t>POGHOSYAN</t>
-  </si>
-  <si>
-    <t>Gayane</t>
-  </si>
-  <si>
-    <t>25/09/1960</t>
-  </si>
-  <si>
-    <t>27/09/2023</t>
-  </si>
-  <si>
-    <t>SAYED</t>
-  </si>
-  <si>
-    <t>Mohammad</t>
-  </si>
-  <si>
-    <t>05/08/1989</t>
-  </si>
-  <si>
-    <t>Allemagne</t>
-  </si>
-  <si>
-    <t>Europe</t>
-  </si>
-  <si>
-    <t>16/09/2025</t>
-  </si>
-  <si>
-    <t>Tamara</t>
-  </si>
-  <si>
-    <t>24/07/1985</t>
-  </si>
-  <si>
-    <t>YELEJYAN</t>
-  </si>
-  <si>
-    <t>Gohar</t>
-  </si>
-  <si>
-    <t>20/12/1983</t>
-  </si>
-  <si>
-    <t>03/09/2025</t>
-  </si>
-  <si>
-    <t>Hélène Tharaud / Christiane PETIT</t>
-  </si>
-  <si>
-    <t>KVARATSHIVILI</t>
-  </si>
-  <si>
-    <t>Abo</t>
-  </si>
-  <si>
-    <t>29/11/2006</t>
-  </si>
-  <si>
-    <t>Géorgie</t>
-  </si>
-  <si>
-    <t>06/11/2025</t>
-  </si>
-  <si>
-    <t>KVARATSKHEILIA</t>
-  </si>
-  <si>
-    <t>Giorgi</t>
-  </si>
-  <si>
-    <t>13/03/2022</t>
-  </si>
-  <si>
-    <t>MAKSHARPOV</t>
-  </si>
-  <si>
-    <t>Umar</t>
-  </si>
-  <si>
-    <t>21/01/1979</t>
-  </si>
-  <si>
-    <t>Tchétchénie</t>
-  </si>
-  <si>
-    <t>08/01/2023</t>
-  </si>
-  <si>
-    <t>MIAKHAIL</t>
-  </si>
-  <si>
-    <t>Karimullah</t>
-  </si>
-  <si>
-    <t>Afghanistan</t>
-  </si>
-  <si>
-    <t>20/11/2025</t>
-  </si>
-  <si>
-    <t>NKAMBA</t>
-  </si>
-  <si>
-    <t>Albertina</t>
-  </si>
-  <si>
-    <t>10/05/1959</t>
-  </si>
-  <si>
-    <t>Angola</t>
-  </si>
-  <si>
-    <t>25/02/2025</t>
-  </si>
-  <si>
-    <t>NYINGPA</t>
-  </si>
-  <si>
-    <t>Damchoe</t>
-  </si>
-  <si>
-    <t>02/07/1991</t>
-  </si>
-  <si>
-    <t>Tibet</t>
-  </si>
-  <si>
-    <t>07/10/2025</t>
-  </si>
-  <si>
-    <t>ONAL</t>
-  </si>
-  <si>
-    <t>Ali Imran</t>
-  </si>
-  <si>
-    <t>18/08/2006</t>
-  </si>
-  <si>
-    <t>Turquie</t>
-  </si>
-  <si>
-    <t>09/10/2025</t>
-  </si>
-  <si>
-    <t>POHOSIAN</t>
-  </si>
-  <si>
-    <t>Mykhailo</t>
-  </si>
-  <si>
-    <t>11/01/1953</t>
-  </si>
-  <si>
-    <t>Ukraine</t>
-  </si>
-  <si>
-    <t>SAKHESVILI</t>
-  </si>
-  <si>
-    <t>Eldari</t>
-  </si>
-  <si>
-    <t>10/02/1985</t>
-  </si>
-  <si>
-    <t>SHELIA</t>
-  </si>
-  <si>
-    <t>Vakhtang</t>
-  </si>
-  <si>
-    <t>06/02/1963</t>
-  </si>
-  <si>
-    <t>10/09/2024</t>
-  </si>
-  <si>
-    <t>TENZIN</t>
-  </si>
-  <si>
-    <t>Nyima</t>
-  </si>
-  <si>
-    <t>10/06/1997</t>
-  </si>
-  <si>
-    <t>TSANG</t>
-  </si>
-  <si>
-    <t>Karma</t>
-  </si>
-  <si>
-    <t>15/05/1988</t>
-  </si>
-  <si>
-    <t>Chine</t>
-  </si>
-  <si>
-    <t>Sylvie LABBE / Chantal PREVOST</t>
-  </si>
-  <si>
-    <t>ABIA</t>
-  </si>
-  <si>
-    <t>Flore</t>
-  </si>
-  <si>
-    <t>19/08/2000</t>
-  </si>
-  <si>
-    <t>23/09/2025</t>
-  </si>
-  <si>
-    <t>AVAGYAN</t>
-  </si>
-  <si>
-    <t>Karen</t>
-  </si>
-  <si>
-    <t>04/10/1980</t>
-  </si>
-  <si>
-    <t>10/12/2024</t>
-  </si>
-  <si>
-    <t>BURDULI</t>
-  </si>
-  <si>
-    <t>Sopio</t>
-  </si>
-  <si>
-    <t>02/04/1997</t>
-  </si>
-  <si>
-    <t>11/10/2023</t>
-  </si>
-  <si>
-    <t>HIRPA</t>
-  </si>
-  <si>
-    <t>Wakgari</t>
-  </si>
-  <si>
-    <t>Ethiopie</t>
-  </si>
-  <si>
-    <t>JISHKARIANI</t>
-  </si>
-  <si>
-    <t>Nino</t>
-  </si>
-  <si>
-    <t>11/02/1980</t>
-  </si>
-  <si>
-    <t>KATCHATRYAN</t>
-  </si>
-  <si>
-    <t>20/05/1980</t>
-  </si>
-  <si>
-    <t>07/11/2025</t>
-  </si>
-  <si>
-    <t>Mariam</t>
-  </si>
-  <si>
-    <t>26/08/1986</t>
-  </si>
-  <si>
-    <t>06/10/2022</t>
-  </si>
-  <si>
-    <t>MUGENI</t>
-  </si>
-  <si>
-    <t>Chantal</t>
-  </si>
-  <si>
-    <t>31/12/1996</t>
-  </si>
-  <si>
-    <t>MUSTAFAYEV</t>
-  </si>
-  <si>
-    <t>Elshan</t>
-  </si>
-  <si>
-    <t>17/07/1978</t>
-  </si>
-  <si>
-    <t>Azerbaïdjan</t>
-  </si>
-  <si>
-    <t>NAJJAR</t>
-  </si>
-  <si>
-    <t>Wuod</t>
-  </si>
-  <si>
-    <t>01/06/1970</t>
-  </si>
-  <si>
-    <t>Irak</t>
-  </si>
-  <si>
-    <t>15/11/2022</t>
-  </si>
-  <si>
-    <t>Prénom</t>
-  </si>
-  <si>
-    <t>02/03/1960</t>
-  </si>
-  <si>
-    <t>Andorre</t>
-  </si>
-  <si>
-    <t>02/05/2026</t>
-  </si>
-  <si>
-    <t>PETUKHOVA</t>
-  </si>
-  <si>
-    <t>Mariila</t>
-  </si>
-  <si>
-    <t>05/11/1951</t>
-  </si>
-  <si>
-    <t>10/09/2025</t>
-  </si>
-  <si>
-    <t>RAHHAL</t>
-  </si>
-  <si>
-    <t>Abdelkader</t>
-  </si>
-  <si>
-    <t>03/07/1984</t>
-  </si>
-  <si>
-    <t>Algérie</t>
-  </si>
-  <si>
-    <t>01/09/2025</t>
-  </si>
-  <si>
-    <t>SELIMAN</t>
-  </si>
-  <si>
-    <t>Kajol</t>
-  </si>
-  <si>
-    <t>08/07/2004</t>
-  </si>
-  <si>
-    <t>SHOTSHA</t>
-  </si>
-  <si>
-    <t>M'wemwe</t>
-  </si>
-  <si>
-    <t>05/05/1981</t>
-  </si>
-  <si>
-    <t>TOLA</t>
-  </si>
-  <si>
-    <t>Boja</t>
-  </si>
-  <si>
-    <t>27/08/2004</t>
-  </si>
-  <si>
-    <t>TSAGAREISHVILI</t>
-  </si>
-  <si>
-    <t>Gela</t>
-  </si>
-  <si>
-    <t>05/11/1984</t>
-  </si>
-  <si>
-    <t>28/05/2024</t>
-  </si>
-  <si>
-    <t>WRETA</t>
-  </si>
-  <si>
-    <t>Abeje</t>
-  </si>
-  <si>
-    <t>05/05/1997</t>
-  </si>
-  <si>
-    <t>11/09/2025</t>
-  </si>
-  <si>
-    <t>Monique LAVANANT / Chantal MEREL / Mariannic'k GODIN</t>
-  </si>
-  <si>
-    <t>ABDRAMAN IBRAHIM</t>
-  </si>
-  <si>
-    <t>Saladin</t>
-  </si>
-  <si>
-    <t>05/07/1950</t>
-  </si>
-  <si>
-    <t>Kenya</t>
-  </si>
-  <si>
-    <t>AMRANI</t>
-  </si>
-  <si>
-    <t>Abdulkadir Mohamed</t>
-  </si>
-  <si>
-    <t>04/04/1975</t>
-  </si>
-  <si>
-    <t>Tanzannie</t>
-  </si>
-  <si>
-    <t>17/09/2024</t>
-  </si>
-  <si>
-    <t>BATOL</t>
-  </si>
-  <si>
-    <t>Hassan</t>
-  </si>
-  <si>
-    <t>15/05/1997</t>
-  </si>
-  <si>
-    <t>01/09/2024</t>
-  </si>
-  <si>
-    <t>BEZHANISHVILI</t>
-  </si>
-  <si>
-    <t>Zurab</t>
-  </si>
-  <si>
-    <t>30/06/1974</t>
-  </si>
-  <si>
-    <t>06/02/2025</t>
-  </si>
-  <si>
-    <t>BOUZID</t>
-  </si>
-  <si>
-    <t>Bouchra</t>
-  </si>
-  <si>
-    <t>01/01/1983</t>
-  </si>
-  <si>
-    <t>Maroc</t>
-  </si>
-  <si>
-    <t>24/03/2023</t>
-  </si>
-  <si>
-    <t>KALANDIA</t>
-  </si>
-  <si>
-    <t>Tamar</t>
-  </si>
-  <si>
-    <t>09/10/1979</t>
-  </si>
-  <si>
-    <t>22/05/2024</t>
-  </si>
-  <si>
-    <t>KHACHATRYAN</t>
-  </si>
-  <si>
-    <t>Rita</t>
-  </si>
-  <si>
-    <t>21/01/1973</t>
-  </si>
-  <si>
-    <t>01/10/2024</t>
-  </si>
-  <si>
-    <t>KHUTSISHVILI</t>
-  </si>
-  <si>
-    <t>Rusudan</t>
-  </si>
-  <si>
-    <t>08/11/1987</t>
-  </si>
-  <si>
-    <t>LENGO</t>
-  </si>
-  <si>
-    <t>Lucoqui</t>
-  </si>
-  <si>
-    <t>07/11/1984</t>
-  </si>
-  <si>
-    <t>24/04/2025</t>
-  </si>
-  <si>
-    <t>MAMBA</t>
-  </si>
-  <si>
-    <t>Benayi</t>
-  </si>
-  <si>
-    <t>15/07/1985</t>
-  </si>
-  <si>
-    <t>12/09/2024</t>
-  </si>
-  <si>
-    <t>MANTUIKA</t>
-  </si>
-  <si>
-    <t>Sara</t>
-  </si>
-  <si>
-    <t>15/12/1999</t>
-  </si>
-  <si>
-    <t>MEHMOOD</t>
-  </si>
-  <si>
-    <t>Aamir</t>
-  </si>
-  <si>
-    <t>15/05/1990</t>
-  </si>
-  <si>
-    <t>Pakistan</t>
-  </si>
-  <si>
-    <t>12/01/2025</t>
-  </si>
-  <si>
-    <t>MIAH</t>
-  </si>
-  <si>
-    <t>Mowab</t>
-  </si>
-  <si>
-    <t>28/05/1995</t>
-  </si>
-  <si>
-    <t>Bangladesh</t>
-  </si>
-  <si>
-    <t>01/09/2023</t>
-  </si>
-  <si>
-    <t>MOHAMED EL NOUR</t>
-  </si>
-  <si>
-    <t>Abdel</t>
-  </si>
-  <si>
-    <t>19/01/1977</t>
-  </si>
-  <si>
-    <t>MOHD</t>
-  </si>
-  <si>
-    <t>Azeem Pacha</t>
-  </si>
-  <si>
-    <t>04/04/1991</t>
-  </si>
-  <si>
-    <t>Inde</t>
-  </si>
-  <si>
-    <t>21/01/2025</t>
-  </si>
-  <si>
-    <t>NDUGBE</t>
-  </si>
-  <si>
-    <t>Josiah</t>
-  </si>
-  <si>
-    <t>10/10/1982</t>
-  </si>
-  <si>
-    <t>Nigéria</t>
-  </si>
-  <si>
-    <t>19/11/2023</t>
-  </si>
-  <si>
-    <t>NEHREBA</t>
-  </si>
-  <si>
-    <t>Iryna</t>
-  </si>
-  <si>
-    <t>28/02/1987</t>
-  </si>
-  <si>
-    <t>21/11/2024</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>Mohammed</t>
-  </si>
-  <si>
-    <t>01/01/1994</t>
-  </si>
-  <si>
-    <t>OVERCHENKO</t>
-  </si>
-  <si>
-    <t>Aleksandrova</t>
-  </si>
-  <si>
-    <t>30/09/1971</t>
-  </si>
-  <si>
-    <t>PINTO</t>
-  </si>
-  <si>
-    <t>Janet</t>
-  </si>
-  <si>
-    <t>23/02/1971</t>
-  </si>
-  <si>
-    <t>Pérou</t>
-  </si>
-  <si>
-    <t>Amérique du Sud</t>
-  </si>
-  <si>
-    <t>POPLEE</t>
-  </si>
-  <si>
-    <t>Daleep</t>
-  </si>
-  <si>
-    <t>01/09/1984</t>
-  </si>
-  <si>
-    <t>SHARIF IBRAHIM</t>
-  </si>
-  <si>
-    <t>Ahmed</t>
-  </si>
-  <si>
-    <t>01/01/1998</t>
-  </si>
-  <si>
-    <t>Somalie</t>
-  </si>
-  <si>
-    <t>SISSANI TORQUI</t>
-  </si>
-  <si>
-    <t>Malika</t>
-  </si>
-  <si>
-    <t>01/09/1956</t>
-  </si>
-  <si>
-    <t>Espagne</t>
-  </si>
-  <si>
-    <t>16/11/2023</t>
-  </si>
-  <si>
-    <t>YLDIRIM DOGAN</t>
-  </si>
-  <si>
-    <t>Ozgun</t>
-  </si>
-  <si>
-    <t>01/07/1979</t>
-  </si>
-  <si>
-    <t>Jocelyne PRECIADO / Véronique JANNES</t>
-  </si>
-  <si>
-    <t>ABAIDZE</t>
-  </si>
-  <si>
-    <t>Mariami</t>
-  </si>
-  <si>
-    <t>23/08/1991</t>
-  </si>
-  <si>
-    <t>ABDOU</t>
-  </si>
-  <si>
-    <t>Houfranie</t>
-  </si>
-  <si>
-    <t>31/12/1978</t>
-  </si>
-  <si>
-    <t>Comores</t>
-  </si>
-  <si>
-    <t>AHED MOHAMED</t>
-  </si>
-  <si>
-    <t>Mohamed</t>
-  </si>
-  <si>
-    <t>22/07/1993</t>
-  </si>
-  <si>
-    <t>01/05/2024</t>
-  </si>
-  <si>
-    <t>ALHAJ</t>
-  </si>
-  <si>
-    <t>Mudother</t>
-  </si>
-  <si>
-    <t>08/04/1999</t>
-  </si>
-  <si>
-    <t>25/11/2024</t>
-  </si>
-  <si>
-    <t>BEGUM</t>
-  </si>
-  <si>
-    <t>Lima</t>
-  </si>
-  <si>
-    <t>10/12/1990</t>
-  </si>
-  <si>
-    <t>CHKHAPELIA</t>
-  </si>
-  <si>
-    <t>Tamta</t>
-  </si>
-  <si>
-    <t>01/04/1992</t>
-  </si>
-  <si>
-    <t>01/01/2022</t>
-  </si>
-  <si>
-    <t>DIAMPITISA</t>
-  </si>
-  <si>
-    <t>Madalena</t>
-  </si>
-  <si>
-    <t>02/11/1967</t>
-  </si>
-  <si>
-    <t>EBRAHIM DUD</t>
-  </si>
-  <si>
-    <t>Nabil</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>Kiala Baptista</t>
-  </si>
-  <si>
-    <t>31/12/1994</t>
-  </si>
-  <si>
-    <t>ELIDRISSI BOUANANI</t>
-  </si>
-  <si>
-    <t>Fatima</t>
-  </si>
-  <si>
-    <t>01/01/1959</t>
-  </si>
-  <si>
-    <t>15/09/2022</t>
-  </si>
-  <si>
-    <t>FURAH KITAMBALA</t>
-  </si>
-  <si>
-    <t>Patricia</t>
-  </si>
-  <si>
-    <t>26/11/2025</t>
-  </si>
-  <si>
-    <t>HASHEMI</t>
-  </si>
-  <si>
-    <t>Asghar</t>
-  </si>
-  <si>
-    <t>28/02/1999</t>
-  </si>
-  <si>
-    <t>IMERI</t>
-  </si>
-  <si>
-    <t>Mirela</t>
-  </si>
-  <si>
-    <t>30/05/1977</t>
-  </si>
-  <si>
-    <t>Albanie</t>
-  </si>
-  <si>
-    <t>10/05/2022</t>
-  </si>
-  <si>
-    <t>IREDIA</t>
-  </si>
-  <si>
-    <t>Tracy</t>
-  </si>
-  <si>
-    <t>27/07/1982</t>
-  </si>
-  <si>
-    <t>ISOMI</t>
-  </si>
-  <si>
-    <t>Febe</t>
-  </si>
-  <si>
-    <t>05/03/2001</t>
-  </si>
-  <si>
-    <t>JARA</t>
-  </si>
-  <si>
-    <t>Mario</t>
-  </si>
-  <si>
-    <t>19/01/2003</t>
-  </si>
-  <si>
-    <t>Chili</t>
-  </si>
-  <si>
-    <t>18/09/2025</t>
-  </si>
-  <si>
-    <t>KINAVUIDI</t>
-  </si>
-  <si>
-    <t>Viviane</t>
-  </si>
-  <si>
-    <t>29/06/1988</t>
-  </si>
-  <si>
-    <t>LAGOUNE</t>
-  </si>
-  <si>
-    <t>Ilham</t>
-  </si>
-  <si>
-    <t>15/08/2002</t>
-  </si>
-  <si>
-    <t>LUMBE OMOWO</t>
-  </si>
-  <si>
-    <t>Anne-Marie</t>
-  </si>
-  <si>
-    <t>18/03/1979</t>
-  </si>
-  <si>
-    <t>25/11/2025</t>
-  </si>
-  <si>
-    <t>MADALENA</t>
-  </si>
-  <si>
-    <t>Lidia</t>
-  </si>
-  <si>
-    <t>29/05/2018</t>
-  </si>
-  <si>
-    <t>14/11/2025</t>
-  </si>
-  <si>
-    <t>MATETA</t>
-  </si>
-  <si>
-    <t>Gloria</t>
-  </si>
-  <si>
-    <t>30/07/1994</t>
-  </si>
-  <si>
-    <t>NGELI</t>
-  </si>
-  <si>
-    <t>Yolande</t>
-  </si>
-  <si>
-    <t>06/12/1980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLIVEIRA </t>
-  </si>
-  <si>
-    <t>Laura</t>
-  </si>
-  <si>
-    <t>14/12/1986</t>
-  </si>
-  <si>
-    <t>02/06/2024</t>
-  </si>
-  <si>
-    <t>RIAHI</t>
-  </si>
-  <si>
-    <t>Souhail</t>
-  </si>
-  <si>
-    <t>13/11/1992</t>
-  </si>
-  <si>
-    <t>Tunisie</t>
-  </si>
-  <si>
-    <t>TIENE</t>
-  </si>
-  <si>
-    <t>Nawa</t>
-  </si>
-  <si>
-    <t>15/11/1996</t>
-  </si>
-  <si>
-    <t>Côte d'Ivoire</t>
-  </si>
-  <si>
-    <t>TINIKASCHVILI</t>
-  </si>
-  <si>
-    <t>Maka</t>
-  </si>
-  <si>
-    <t>21/09/1983</t>
-  </si>
-  <si>
-    <t>12/10/2021</t>
-  </si>
-  <si>
-    <t>TONOYAN</t>
-  </si>
-  <si>
-    <t>Alvard</t>
-  </si>
-  <si>
-    <t>10/01/1963</t>
-  </si>
-  <si>
-    <t>12/01/2016</t>
-  </si>
-  <si>
-    <t>VIUCHE GIRON</t>
-  </si>
-  <si>
-    <t>Sanyi</t>
-  </si>
-  <si>
-    <t>21/05/1995</t>
-  </si>
-  <si>
-    <t>Colombie</t>
-  </si>
-  <si>
-    <t>06/03/2025</t>
-  </si>
-  <si>
-    <t>Jean PITORIN / Jean-Luc HOUDAYER</t>
-  </si>
-  <si>
-    <t>BABALOLA</t>
-  </si>
-  <si>
-    <t>Elizabeth</t>
-  </si>
-  <si>
-    <t>10/11/1973</t>
-  </si>
-  <si>
-    <t>AFRIQUE</t>
-  </si>
-  <si>
-    <t>06/09/2022</t>
-  </si>
-  <si>
-    <t>01/12/2025</t>
-  </si>
-  <si>
-    <t>BARSEGHIAN</t>
-  </si>
-  <si>
-    <t>Norik</t>
-  </si>
-  <si>
-    <t>07/07/2006</t>
-  </si>
-  <si>
-    <t>CARBONO FERNANDEZ</t>
-  </si>
-  <si>
-    <t>Carolina</t>
-  </si>
-  <si>
-    <t>16/01/2025</t>
-  </si>
-  <si>
-    <t>CHEGGARI</t>
-  </si>
-  <si>
-    <t>Nour Eddin</t>
-  </si>
-  <si>
-    <t>23/10/1994</t>
-  </si>
-  <si>
-    <t>31/05/2023</t>
-  </si>
-  <si>
-    <t>HALILAJ</t>
-  </si>
-  <si>
-    <t>Lindita</t>
-  </si>
-  <si>
-    <t>23/02/1979</t>
-  </si>
-  <si>
-    <t>09/11/2023</t>
-  </si>
-  <si>
-    <t>KIAKU</t>
-  </si>
-  <si>
-    <t>Ana Marcela</t>
-  </si>
-  <si>
-    <t>19/02/1992</t>
-  </si>
-  <si>
-    <t>20/09/2023</t>
-  </si>
-  <si>
-    <t>LMABROUK</t>
-  </si>
-  <si>
-    <t>Oussama</t>
-  </si>
-  <si>
-    <t>01/02/2025</t>
-  </si>
-  <si>
-    <t>MANGAY</t>
-  </si>
-  <si>
-    <t>Paul</t>
-  </si>
-  <si>
-    <t>25/06/1990</t>
-  </si>
-  <si>
-    <t>MENAYAME NGOMA</t>
-  </si>
-  <si>
-    <t>Mera</t>
-  </si>
-  <si>
-    <t>05/05/1994</t>
-  </si>
-  <si>
-    <t>MUSTAFAYEVA</t>
-  </si>
-  <si>
-    <t>Gulkanim</t>
-  </si>
-  <si>
-    <t>17/09/1990</t>
-  </si>
-  <si>
-    <t>26/06/2019</t>
-  </si>
-  <si>
-    <t>NYINAWUMUNTU</t>
-  </si>
-  <si>
-    <t>Marie-Louise</t>
-  </si>
-  <si>
-    <t>Rwanda</t>
-  </si>
-  <si>
-    <t>19/09/2024</t>
-  </si>
-  <si>
-    <t>OYEKAN</t>
-  </si>
-  <si>
-    <t>Patrick</t>
-  </si>
-  <si>
-    <t>17/01/1976</t>
-  </si>
-  <si>
-    <t>REYES OTERO</t>
-  </si>
-  <si>
-    <t>Victor Hugo</t>
-  </si>
-  <si>
-    <t>29/05/1986</t>
-  </si>
-  <si>
-    <t>06/05/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAUCEDO  FERNANDEZ</t>
-  </si>
-  <si>
-    <t>Verselia</t>
-  </si>
-  <si>
-    <t>03/07/1989</t>
-  </si>
-  <si>
-    <t>CMOI</t>
-  </si>
-  <si>
-    <t>Sélectionner un item...</t>
-  </si>
-  <si>
-    <t>Samedi</t>
-  </si>
-  <si>
-    <t>Louise-Anne</t>
-  </si>
-  <si>
-    <t>ABAKAR ADAM</t>
-  </si>
-  <si>
-    <t>Seida</t>
-  </si>
-  <si>
-    <t>Soudan du Sud</t>
-  </si>
-  <si>
-    <t>ADDOUT SOULEMAN</t>
+    <t>Panama</t>
+  </si>
+  <si>
+    <t>Amérique du Nord</t>
+  </si>
+  <si>
+    <t>01/01/2025</t>
+  </si>
+  <si>
+    <t>01/01/2030</t>
   </si>
   <si>
     <t xml:space="preserve">AHMED MOHAMED </t>
@@ -1446,7 +1431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J132"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.323410987854" customWidth="1"/>
@@ -1454,8 +1439,8 @@
     <col min="3" max="3" width="26.2138481140137" customWidth="1"/>
     <col min="4" max="4" width="20.5225353240967" customWidth="1"/>
     <col min="5" max="5" width="22.1085662841797" customWidth="1"/>
-    <col min="6" max="6" width="21.3051795959473" customWidth="1"/>
-    <col min="7" max="7" width="21.3051795959473" customWidth="1"/>
+    <col min="6" max="6" width="14.4772424697876" customWidth="1"/>
+    <col min="7" max="7" width="17.7080821990967" customWidth="1"/>
     <col min="8" max="8" width="9.77960538864136" customWidth="1"/>
     <col min="9" max="9" width="22.4257164001465" customWidth="1"/>
     <col min="10" max="10" width="14.8274097442627" customWidth="1"/>
@@ -1513,16 +1498,16 @@
         <v>15</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -1533,28 +1518,28 @@
         <v>11</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -1565,28 +1550,28 @@
         <v>11</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -1597,28 +1582,28 @@
         <v>11</v>
       </c>
       <c r="C5" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>33</v>
-      </c>
       <c r="H5" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I5" s="0" t="s">
         <v>34</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -1638,19 +1623,19 @@
         <v>37</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -1661,28 +1646,28 @@
         <v>11</v>
       </c>
       <c r="C7" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="0" t="s">
+      <c r="H7" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>44</v>
-      </c>
       <c r="J7" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -1693,7 +1678,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>45</v>
@@ -1702,51 +1687,51 @@
         <v>46</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="s">
-        <v>10</v>
+      <c r="A9" s="0">
+        <v>1</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -1754,31 +1739,31 @@
         <v>1</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -1786,31 +1771,31 @@
         <v>1</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -1818,31 +1803,31 @@
         <v>1</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -1850,31 +1835,31 @@
         <v>1</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -1882,31 +1867,31 @@
         <v>1</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -1914,31 +1899,31 @@
         <v>1</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F15" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="0" t="s">
-        <v>78</v>
-      </c>
       <c r="J15" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -1946,31 +1931,31 @@
         <v>1</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -1978,31 +1963,31 @@
         <v>1</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -2010,31 +1995,31 @@
         <v>1</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="J18" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -2042,95 +2027,95 @@
         <v>1</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="J20" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="J21" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -2138,31 +2123,31 @@
         <v>2</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -2170,31 +2155,31 @@
         <v>2</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>109</v>
+        <v>19</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -2202,31 +2187,31 @@
         <v>2</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -2234,31 +2219,31 @@
         <v>2</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>115</v>
       </c>
       <c r="D25" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="0" t="s">
         <v>116</v>
       </c>
-      <c r="E25" s="0" t="s">
-        <v>14</v>
-      </c>
       <c r="F25" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G25" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="0" t="s">
         <v>117</v>
       </c>
-      <c r="G25" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I25" s="0" t="s">
-        <v>44</v>
-      </c>
       <c r="J25" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
@@ -2266,31 +2251,31 @@
         <v>2</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C26" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" s="0" t="s">
         <v>118</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="E26" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="E26" s="0" t="s">
+      <c r="F26" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="0" t="s">
         <v>120</v>
       </c>
-      <c r="F26" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="G26" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="H26" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I26" s="0" t="s">
-        <v>56</v>
-      </c>
       <c r="J26" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
@@ -2298,31 +2283,31 @@
         <v>2</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>121</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="J27" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
@@ -2330,31 +2315,31 @@
         <v>2</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="J28" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
@@ -2362,31 +2347,31 @@
         <v>2</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="J29" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -2394,31 +2379,31 @@
         <v>2</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>130</v>
+        <v>2</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>44</v>
+        <v>136</v>
       </c>
       <c r="J30" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
@@ -2426,31 +2411,31 @@
         <v>2</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J31" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
@@ -2458,31 +2443,31 @@
         <v>2</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>2</v>
+        <v>141</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J32" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
@@ -2490,31 +2475,31 @@
         <v>2</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="J33" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
@@ -2522,31 +2507,31 @@
         <v>2</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>150</v>
+        <v>23</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>151</v>
+        <v>41</v>
       </c>
       <c r="J34" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
@@ -2554,7 +2539,7 @@
         <v>2</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>152</v>
@@ -2566,19 +2551,19 @@
         <v>154</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="J35" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
@@ -2586,7 +2571,7 @@
         <v>2</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>155</v>
@@ -2598,115 +2583,115 @@
         <v>157</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>44</v>
+        <v>158</v>
       </c>
       <c r="J36" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="J37" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>55</v>
+        <v>167</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J38" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="J39" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
@@ -2714,31 +2699,31 @@
         <v>3</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>173</v>
+        <v>52</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="J40" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
@@ -2746,31 +2731,31 @@
         <v>3</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J41" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42">
@@ -2778,31 +2763,31 @@
         <v>3</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J42" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
@@ -2810,31 +2795,31 @@
         <v>3</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J43" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44">
@@ -2842,31 +2827,31 @@
         <v>3</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>190</v>
+        <v>52</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="J44" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
@@ -2874,31 +2859,31 @@
         <v>3</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J45" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
@@ -2906,31 +2891,31 @@
         <v>3</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J46" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
@@ -2938,31 +2923,31 @@
         <v>3</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="J47" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
@@ -2970,31 +2955,31 @@
         <v>3</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>72</v>
+        <v>207</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J48" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
@@ -3002,31 +2987,31 @@
         <v>3</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>72</v>
+        <v>212</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="J49" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
@@ -3034,31 +3019,31 @@
         <v>3</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="J50" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
@@ -3066,31 +3051,31 @@
         <v>3</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="J51" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">
@@ -3098,31 +3083,31 @@
         <v>3</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J52" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53">
@@ -3130,31 +3115,31 @@
         <v>3</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>151</v>
+        <v>230</v>
       </c>
       <c r="J53" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
@@ -3162,31 +3147,31 @@
         <v>3</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>230</v>
+        <v>15</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>231</v>
+        <v>168</v>
       </c>
       <c r="J54" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55">
@@ -3194,31 +3179,31 @@
         <v>3</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>235</v>
+        <v>81</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>236</v>
+        <v>88</v>
       </c>
       <c r="J55" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56">
@@ -3226,7 +3211,7 @@
         <v>3</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C56" s="0" t="s">
         <v>237</v>
@@ -3238,19 +3223,19 @@
         <v>239</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>87</v>
+        <v>240</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>43</v>
+        <v>241</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>240</v>
+        <v>145</v>
       </c>
       <c r="J56" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57">
@@ -3258,31 +3243,31 @@
         <v>3</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="J57" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58">
@@ -3290,31 +3275,31 @@
         <v>3</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>87</v>
+        <v>248</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="J58" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59">
@@ -3322,31 +3307,31 @@
         <v>3</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>251</v>
+        <v>39</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>151</v>
+        <v>253</v>
       </c>
       <c r="J59" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
@@ -3354,127 +3339,127 @@
         <v>3</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="J60" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>169</v>
+        <v>257</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>258</v>
+        <v>52</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="J61" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>169</v>
+        <v>257</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>263</v>
+        <v>145</v>
       </c>
       <c r="J62" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>169</v>
+        <v>257</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>182</v>
+        <v>268</v>
       </c>
       <c r="J63" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64">
@@ -3482,31 +3467,31 @@
         <v>4</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>68</v>
+        <v>272</v>
       </c>
       <c r="J64" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65">
@@ -3514,31 +3499,31 @@
         <v>4</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>274</v>
+        <v>212</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="J65" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66">
@@ -3546,31 +3531,31 @@
         <v>4</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J66" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67">
@@ -3578,31 +3563,31 @@
         <v>4</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>282</v>
+        <v>100</v>
       </c>
       <c r="J67" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68">
@@ -3610,7 +3595,7 @@
         <v>4</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C68" s="0" t="s">
         <v>283</v>
@@ -3619,22 +3604,22 @@
         <v>284</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="J68" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69">
@@ -3642,31 +3627,31 @@
         <v>4</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C69" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="D69" s="0" t="s">
         <v>286</v>
       </c>
-      <c r="D69" s="0" t="s">
+      <c r="E69" s="0" t="s">
         <v>287</v>
       </c>
-      <c r="E69" s="0" t="s">
-        <v>288</v>
-      </c>
       <c r="F69" s="0" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="J69" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
@@ -3674,31 +3659,31 @@
         <v>4</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C70" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="D70" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="E70" s="0" t="s">
         <v>290</v>
       </c>
-      <c r="D70" s="0" t="s">
+      <c r="F70" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="G70" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H70" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I70" s="0" t="s">
         <v>291</v>
       </c>
-      <c r="E70" s="0" t="s">
-        <v>292</v>
-      </c>
-      <c r="F70" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="G70" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="H70" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I70" s="0" t="s">
-        <v>106</v>
-      </c>
       <c r="J70" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71">
@@ -3706,31 +3691,31 @@
         <v>4</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C71" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="D71" s="0" t="s">
         <v>293</v>
       </c>
-      <c r="D71" s="0" t="s">
+      <c r="E71" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G71" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H71" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I71" s="0" t="s">
         <v>294</v>
       </c>
-      <c r="E71" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="F71" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="G71" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="H71" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I71" s="0" t="s">
-        <v>44</v>
-      </c>
       <c r="J71" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72">
@@ -3738,7 +3723,7 @@
         <v>4</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C72" s="0" t="s">
         <v>295</v>
@@ -3750,19 +3735,19 @@
         <v>297</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>282</v>
+        <v>77</v>
       </c>
       <c r="J72" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73">
@@ -3770,7 +3755,7 @@
         <v>4</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C73" s="0" t="s">
         <v>298</v>
@@ -3782,19 +3767,19 @@
         <v>300</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>190</v>
+        <v>301</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J73" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74">
@@ -3802,31 +3787,31 @@
         <v>4</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>14</v>
+        <v>305</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>27</v>
+        <v>225</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>304</v>
+        <v>41</v>
       </c>
       <c r="J74" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75">
@@ -3834,31 +3819,31 @@
         <v>4</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="J75" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76">
@@ -3866,31 +3851,31 @@
         <v>4</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>43</v>
+        <v>241</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J76" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77">
@@ -3898,31 +3883,31 @@
         <v>4</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>235</v>
+        <v>66</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="J77" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78">
@@ -3930,31 +3915,31 @@
         <v>4</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="J78" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79">
@@ -3962,31 +3947,31 @@
         <v>4</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>322</v>
+        <v>23</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>251</v>
+        <v>16</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I79" s="0" t="s">
         <v>323</v>
       </c>
       <c r="J79" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80">
@@ -3994,7 +3979,7 @@
         <v>4</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C80" s="0" t="s">
         <v>324</v>
@@ -4006,19 +3991,19 @@
         <v>326</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>146</v>
+        <v>327</v>
       </c>
       <c r="J80" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81">
@@ -4026,31 +4011,31 @@
         <v>4</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C81" s="0" t="s">
+        <v>328</v>
+      </c>
+      <c r="D81" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="E81" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="F81" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G81" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H81" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I81" s="0" t="s">
         <v>327</v>
       </c>
-      <c r="D81" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="E81" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="F81" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="G81" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="H81" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I81" s="0" t="s">
-        <v>123</v>
-      </c>
       <c r="J81" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82">
@@ -4058,31 +4043,31 @@
         <v>4</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>333</v>
+        <v>62</v>
       </c>
       <c r="J82" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83">
@@ -4090,7 +4075,7 @@
         <v>4</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C83" s="0" t="s">
         <v>334</v>
@@ -4102,19 +4087,19 @@
         <v>336</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I83" s="0" t="s">
         <v>337</v>
       </c>
       <c r="J83" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84">
@@ -4122,7 +4107,7 @@
         <v>4</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C84" s="0" t="s">
         <v>338</v>
@@ -4134,19 +4119,19 @@
         <v>340</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>27</v>
+        <v>341</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>337</v>
+        <v>41</v>
       </c>
       <c r="J84" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85">
@@ -4154,31 +4139,31 @@
         <v>4</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>27</v>
+        <v>345</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>68</v>
+        <v>189</v>
       </c>
       <c r="J85" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86">
@@ -4186,31 +4171,31 @@
         <v>4</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J86" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87">
@@ -4218,31 +4203,31 @@
         <v>4</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>351</v>
+        <v>81</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>44</v>
+        <v>353</v>
       </c>
       <c r="J87" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88">
@@ -4250,127 +4235,127 @@
         <v>4</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>199</v>
+        <v>358</v>
       </c>
       <c r="J88" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>267</v>
+        <v>359</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>55</v>
+        <v>225</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>33</v>
+        <v>363</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="J89" s="0" t="s">
-        <v>14</v>
+        <v>365</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>267</v>
+        <v>359</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="J90" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>267</v>
+        <v>359</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>366</v>
+        <v>19</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="J91" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92">
@@ -4378,31 +4363,31 @@
         <v>5</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>373</v>
+        <v>16</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J92" s="0" t="s">
-        <v>375</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93">
@@ -4410,31 +4395,31 @@
         <v>5</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>32</v>
+        <v>301</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>168</v>
+        <v>380</v>
       </c>
       <c r="J93" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94">
@@ -4442,31 +4427,31 @@
         <v>5</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>14</v>
+        <v>383</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>367</v>
+        <v>66</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>251</v>
+        <v>16</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="J94" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95">
@@ -4474,31 +4459,31 @@
         <v>5</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>384</v>
+        <v>233</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J95" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96">
@@ -4506,31 +4491,31 @@
         <v>5</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>311</v>
+        <v>23</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>389</v>
+        <v>41</v>
       </c>
       <c r="J96" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97">
@@ -4538,31 +4523,31 @@
         <v>5</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>393</v>
+        <v>18</v>
       </c>
       <c r="J97" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98">
@@ -4570,7 +4555,7 @@
         <v>5</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C98" s="0" t="s">
         <v>394</v>
@@ -4579,22 +4564,22 @@
         <v>395</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>243</v>
+        <v>396</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>190</v>
+        <v>127</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J98" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99">
@@ -4602,31 +4587,31 @@
         <v>5</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>399</v>
+        <v>233</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>27</v>
+        <v>400</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>44</v>
+        <v>401</v>
       </c>
       <c r="J99" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100">
@@ -4634,31 +4619,31 @@
         <v>5</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>27</v>
+        <v>225</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
       <c r="J100" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101">
@@ -4666,31 +4651,31 @@
         <v>5</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>133</v>
+        <v>357</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>33</v>
+        <v>241</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J101" s="0" t="s">
-        <v>14</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102">
@@ -4698,71 +4683,71 @@
         <v>5</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E102" s="0" t="s">
-        <v>243</v>
+        <v>411</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>409</v>
+        <v>240</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>410</v>
+        <v>372</v>
       </c>
       <c r="J102" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="0">
-        <v>5</v>
+      <c r="A103" s="0" t="s">
+        <v>412</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>369</v>
+        <v>413</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D103" s="0" t="s">
+        <v>415</v>
+      </c>
+      <c r="E103" s="0" t="s">
+        <v>179</v>
+      </c>
+      <c r="F103" s="0" t="s">
+        <v>416</v>
+      </c>
+      <c r="G103" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H103" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I103" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="J103" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="s">
         <v>412</v>
       </c>
-      <c r="E103" s="0" t="s">
+      <c r="B104" s="0" t="s">
         <v>413</v>
-      </c>
-      <c r="F103" s="0" t="s">
-        <v>235</v>
-      </c>
-      <c r="G103" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="H103" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I103" s="0" t="s">
-        <v>178</v>
-      </c>
-      <c r="J103" s="0" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="0">
-        <v>5</v>
-      </c>
-      <c r="B104" s="0" t="s">
-        <v>369</v>
       </c>
       <c r="C104" s="0" t="s">
         <v>414</v>
@@ -4771,126 +4756,126 @@
         <v>415</v>
       </c>
       <c r="E104" s="0" t="s">
-        <v>416</v>
+        <v>179</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>251</v>
+        <v>16</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I104" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="J104" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="s">
+        <v>412</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>413</v>
+      </c>
+      <c r="C105" s="0" t="s">
         <v>417</v>
       </c>
-      <c r="J104" s="0" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="0">
-        <v>5</v>
-      </c>
-      <c r="B105" s="0" t="s">
-        <v>369</v>
-      </c>
-      <c r="C105" s="0" t="s">
+      <c r="D105" s="0" t="s">
         <v>418</v>
       </c>
-      <c r="D105" s="0" t="s">
-        <v>419</v>
-      </c>
       <c r="E105" s="0" t="s">
-        <v>420</v>
+        <v>19</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>250</v>
+        <v>15</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>251</v>
+        <v>16</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>381</v>
+        <v>19</v>
       </c>
       <c r="J105" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>15</v>
+        <v>413</v>
       </c>
       <c r="C106" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="D106" s="0" t="s">
+        <v>418</v>
+      </c>
+      <c r="E106" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="F106" s="0" t="s">
+        <v>420</v>
+      </c>
+      <c r="G106" s="0" t="s">
         <v>421</v>
       </c>
-      <c r="D106" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="E106" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="F106" s="0" t="s">
+      <c r="H106" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="I106" s="0" t="s">
         <v>422</v>
       </c>
-      <c r="G106" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="H106" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I106" s="0" t="s">
-        <v>142</v>
-      </c>
       <c r="J106" s="0" t="s">
-        <v>14</v>
+        <v>423</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B107" s="0" t="s">
+        <v>413</v>
+      </c>
+      <c r="C107" s="0" t="s">
         <v>424</v>
       </c>
-      <c r="C107" s="0" t="s">
-        <v>425</v>
-      </c>
       <c r="D107" s="0" t="s">
-        <v>426</v>
+        <v>13</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>189</v>
+        <v>14</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>427</v>
+        <v>15</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="J107" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C108" s="0" t="s">
         <v>425</v>
@@ -4899,158 +4884,158 @@
         <v>426</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>189</v>
+        <v>19</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>20</v>
+        <v>427</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="J108" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C109" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="D109" s="0" t="s">
         <v>428</v>
       </c>
-      <c r="D109" s="0" t="s">
-        <v>13</v>
-      </c>
       <c r="E109" s="0" t="s">
-        <v>14</v>
+        <v>271</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>14</v>
+        <v>272</v>
       </c>
       <c r="J109" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C110" s="0" t="s">
         <v>429</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>18</v>
+        <v>430</v>
       </c>
       <c r="E110" s="0" t="s">
         <v>19</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>20</v>
+        <v>264</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J110" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E111" s="0" t="s">
-        <v>14</v>
+        <v>433</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>432</v>
+        <v>66</v>
       </c>
       <c r="G111" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="J111" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>433</v>
+        <v>284</v>
       </c>
       <c r="E112" s="0" t="s">
-        <v>281</v>
+        <v>19</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>282</v>
+        <v>41</v>
       </c>
       <c r="J112" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C113" s="0" t="s">
         <v>434</v>
@@ -5059,634 +5044,538 @@
         <v>435</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>274</v>
+        <v>427</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J113" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C114" s="0" t="s">
+        <v>434</v>
+      </c>
+      <c r="D114" s="0" t="s">
         <v>436</v>
       </c>
-      <c r="D114" s="0" t="s">
-        <v>437</v>
-      </c>
       <c r="E114" s="0" t="s">
-        <v>438</v>
+        <v>19</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>72</v>
+        <v>427</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="J114" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>20</v>
+        <v>264</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="J115" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C116" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="D116" s="0" t="s">
         <v>439</v>
       </c>
-      <c r="D116" s="0" t="s">
+      <c r="E116" s="0" t="s">
         <v>440</v>
       </c>
-      <c r="E116" s="0" t="s">
-        <v>14</v>
-      </c>
       <c r="F116" s="0" t="s">
-        <v>432</v>
+        <v>71</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>14</v>
+        <v>441</v>
       </c>
       <c r="J116" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>432</v>
+        <v>61</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J117" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>442</v>
+        <v>317</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>14</v>
+        <v>319</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>274</v>
+        <v>144</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>14</v>
+        <v>117</v>
       </c>
       <c r="J118" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>445</v>
+        <v>19</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>446</v>
+        <v>19</v>
       </c>
       <c r="J119" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C120" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="D120" s="0" t="s">
         <v>447</v>
       </c>
-      <c r="D120" s="0" t="s">
-        <v>448</v>
-      </c>
       <c r="E120" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>67</v>
+        <v>163</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J120" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>327</v>
+        <v>448</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>328</v>
+        <v>449</v>
       </c>
       <c r="E121" s="0" t="s">
-        <v>329</v>
+        <v>19</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>150</v>
+        <v>61</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="J121" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>449</v>
+        <v>68</v>
       </c>
       <c r="D122" s="0" t="s">
         <v>450</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J122" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>451</v>
+        <v>231</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>452</v>
+        <v>232</v>
       </c>
       <c r="E123" s="0" t="s">
-        <v>14</v>
+        <v>233</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>173</v>
+        <v>15</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>14</v>
+        <v>168</v>
       </c>
       <c r="J123" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>454</v>
+        <v>266</v>
       </c>
       <c r="E124" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J124" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>74</v>
+        <v>245</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>455</v>
+        <v>246</v>
       </c>
       <c r="E125" s="0" t="s">
-        <v>14</v>
+        <v>247</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>77</v>
+        <v>248</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="J125" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>241</v>
+        <v>89</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>242</v>
+        <v>90</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>243</v>
+        <v>91</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="J126" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>456</v>
+        <v>152</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>276</v>
+        <v>153</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="G127" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="J127" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>255</v>
+        <v>452</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>256</v>
+        <v>453</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>258</v>
+        <v>454</v>
       </c>
       <c r="G128" s="0" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="J128" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C129" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="D129" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="E129" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="F129" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="D129" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="E129" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="F129" s="0" t="s">
-        <v>77</v>
-      </c>
       <c r="G129" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="J129" s="0" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="0" t="s">
-        <v>423</v>
-      </c>
-      <c r="B130" s="0" t="s">
-        <v>424</v>
-      </c>
-      <c r="C130" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="D130" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="E130" s="0" t="s">
-        <v>160</v>
-      </c>
-      <c r="F130" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="G130" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="H130" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I130" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="J130" s="0" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="0" t="s">
-        <v>423</v>
-      </c>
-      <c r="B131" s="0" t="s">
-        <v>424</v>
-      </c>
-      <c r="C131" s="0" t="s">
-        <v>457</v>
-      </c>
-      <c r="D131" s="0" t="s">
-        <v>458</v>
-      </c>
-      <c r="E131" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="F131" s="0" t="s">
-        <v>459</v>
-      </c>
-      <c r="G131" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="H131" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="I131" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J131" s="0" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="0" t="s">
-        <v>423</v>
-      </c>
-      <c r="B132" s="0" t="s">
-        <v>424</v>
-      </c>
-      <c r="C132" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="D132" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="E132" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="F132" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="G132" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="H132" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I132" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="J132" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J132"/>
+  <autoFilter ref="A1:J129"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/Excel/liste_complete.xlsx
+++ b/Excel/liste_complete.xlsx
@@ -8,14 +8,14 @@
     <sheet name="Export" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Export'!$A$1:$J$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Export'!$A$1:$J$134</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="459">
   <si>
     <t>GROUPE</t>
   </si>
@@ -53,6 +53,45 @@
     <t>Marie-Joëlle / Nicolette LECOQ</t>
   </si>
   <si>
+    <t>ABDALLA MIRGHANI</t>
+  </si>
+  <si>
+    <t>Zainab</t>
+  </si>
+  <si>
+    <t>01/01/1964</t>
+  </si>
+  <si>
+    <t>Soudan</t>
+  </si>
+  <si>
+    <t>Afrique</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>19/09/2024</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
+  </si>
+  <si>
+    <t>AHMED</t>
+  </si>
+  <si>
+    <t>Ibrahim</t>
+  </si>
+  <si>
+    <t>31/12/1899</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
     <t>AHMED MOHAMED OSMAN</t>
   </si>
   <si>
@@ -62,21 +101,9 @@
     <t>01/01/1987</t>
   </si>
   <si>
-    <t>Soudan</t>
-  </si>
-  <si>
-    <t>Afrique</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
     <t>25/09/2025</t>
   </si>
   <si>
-    <t>01/01/1900</t>
-  </si>
-  <si>
     <t>MPUTU</t>
   </si>
   <si>
@@ -86,7 +113,7 @@
     <t>20/05/1998</t>
   </si>
   <si>
-    <t>RDC</t>
+    <t>République démocratique du Congo</t>
   </si>
   <si>
     <t>04/11/2025</t>
@@ -137,9 +164,6 @@
     <t>Europe</t>
   </si>
   <si>
-    <t>M</t>
-  </si>
-  <si>
     <t>16/09/2025</t>
   </si>
   <si>
@@ -164,6 +188,66 @@
     <t>Hélène Tharaud / Christiane PETIT</t>
   </si>
   <si>
+    <t>AHMAD</t>
+  </si>
+  <si>
+    <t>Nafyad</t>
+  </si>
+  <si>
+    <t>11/06/1999</t>
+  </si>
+  <si>
+    <t>Éthiopie</t>
+  </si>
+  <si>
+    <t>23/09/2025</t>
+  </si>
+  <si>
+    <t>AUGUSTO ANTONIO</t>
+  </si>
+  <si>
+    <t>Elizandre Maria</t>
+  </si>
+  <si>
+    <t>12/02/2006</t>
+  </si>
+  <si>
+    <t>Angola</t>
+  </si>
+  <si>
+    <t>09/10/2025</t>
+  </si>
+  <si>
+    <t>KARMA</t>
+  </si>
+  <si>
+    <t>Guyrme</t>
+  </si>
+  <si>
+    <t>08/02/1997</t>
+  </si>
+  <si>
+    <t>Tibet</t>
+  </si>
+  <si>
+    <t>08/10/2025</t>
+  </si>
+  <si>
+    <t>KVARATSHIVILI</t>
+  </si>
+  <si>
+    <t>Abo</t>
+  </si>
+  <si>
+    <t>29/11/2006</t>
+  </si>
+  <si>
+    <t>Géorgie</t>
+  </si>
+  <si>
+    <t>06/11/2025</t>
+  </si>
+  <si>
     <t>KVARATSKHEILIA</t>
   </si>
   <si>
@@ -173,12 +257,6 @@
     <t>13/03/2022</t>
   </si>
   <si>
-    <t>Géorgie</t>
-  </si>
-  <si>
-    <t>06/11/2025</t>
-  </si>
-  <si>
     <t>MAKSHARPOV</t>
   </si>
   <si>
@@ -215,9 +293,6 @@
     <t>10/05/1959</t>
   </si>
   <si>
-    <t>Angola</t>
-  </si>
-  <si>
     <t>25/02/2025</t>
   </si>
   <si>
@@ -230,9 +305,6 @@
     <t>02/07/1991</t>
   </si>
   <si>
-    <t>Tibet</t>
-  </si>
-  <si>
     <t>07/10/2025</t>
   </si>
   <si>
@@ -248,9 +320,6 @@
     <t>Turquie</t>
   </si>
   <si>
-    <t>09/10/2025</t>
-  </si>
-  <si>
     <t>POHOSIAN</t>
   </si>
   <si>
@@ -308,6 +377,24 @@
     <t>Sylvie LABBE / Chantal PREVOST</t>
   </si>
   <si>
+    <t>ABAKAR ADAM</t>
+  </si>
+  <si>
+    <t>Seida</t>
+  </si>
+  <si>
+    <t>01/01/1983</t>
+  </si>
+  <si>
+    <t>ABDRAMAN IBRAHIM</t>
+  </si>
+  <si>
+    <t>Saladin</t>
+  </si>
+  <si>
+    <t>01/09/2025</t>
+  </si>
+  <si>
     <t>ABIA</t>
   </si>
   <si>
@@ -317,9 +404,6 @@
     <t>19/08/2000</t>
   </si>
   <si>
-    <t>23/09/2025</t>
-  </si>
-  <si>
     <t>AVAGYAN</t>
   </si>
   <si>
@@ -350,9 +434,6 @@
     <t>Wakgari</t>
   </si>
   <si>
-    <t>Ethiopie</t>
-  </si>
-  <si>
     <t>JISHKARIANI</t>
   </si>
   <si>
@@ -416,18 +497,6 @@
     <t>15/11/2022</t>
   </si>
   <si>
-    <t>Prénom</t>
-  </si>
-  <si>
-    <t>02/03/1960</t>
-  </si>
-  <si>
-    <t>Andorre</t>
-  </si>
-  <si>
-    <t>02/05/2026</t>
-  </si>
-  <si>
     <t>PETUKHOVA</t>
   </si>
   <si>
@@ -452,9 +521,6 @@
     <t>Algérie</t>
   </si>
   <si>
-    <t>01/09/2025</t>
-  </si>
-  <si>
     <t>SELIMAN</t>
   </si>
   <si>
@@ -494,871 +560,817 @@
     <t>28/05/2024</t>
   </si>
   <si>
+    <t>WRETA</t>
+  </si>
+  <si>
+    <t>Abeje</t>
+  </si>
+  <si>
+    <t>05/05/1997</t>
+  </si>
+  <si>
+    <t>11/09/2025</t>
+  </si>
+  <si>
     <t>Monique LAVANANT / Chantal MEREL / Mariannic'k GODIN</t>
   </si>
   <si>
-    <t>ABDRAMAN IBRAHIM</t>
-  </si>
-  <si>
-    <t>Saladin</t>
-  </si>
-  <si>
-    <t>05/07/1950</t>
+    <t>AMRANI</t>
+  </si>
+  <si>
+    <t>Abdulkadir Mohamed</t>
+  </si>
+  <si>
+    <t>04/04/1975</t>
+  </si>
+  <si>
+    <t>Tanzannie</t>
+  </si>
+  <si>
+    <t>17/09/2024</t>
+  </si>
+  <si>
+    <t>BATOL</t>
+  </si>
+  <si>
+    <t>Hassan</t>
+  </si>
+  <si>
+    <t>15/05/1997</t>
+  </si>
+  <si>
+    <t>01/09/2024</t>
+  </si>
+  <si>
+    <t>BEZHANISHVILI</t>
+  </si>
+  <si>
+    <t>Zurab</t>
+  </si>
+  <si>
+    <t>30/06/1974</t>
+  </si>
+  <si>
+    <t>06/02/2025</t>
+  </si>
+  <si>
+    <t>BOUZID</t>
+  </si>
+  <si>
+    <t>Bouchra</t>
+  </si>
+  <si>
+    <t>Maroc</t>
+  </si>
+  <si>
+    <t>24/03/2023</t>
+  </si>
+  <si>
+    <t>KALANDIA</t>
+  </si>
+  <si>
+    <t>Tamar</t>
+  </si>
+  <si>
+    <t>09/10/1979</t>
+  </si>
+  <si>
+    <t>22/05/2024</t>
+  </si>
+  <si>
+    <t>KHACHATRYAN</t>
+  </si>
+  <si>
+    <t>Rita</t>
+  </si>
+  <si>
+    <t>21/01/1973</t>
+  </si>
+  <si>
+    <t>01/10/2024</t>
+  </si>
+  <si>
+    <t>KHUTSISHVILI</t>
+  </si>
+  <si>
+    <t>Rusudan</t>
+  </si>
+  <si>
+    <t>08/11/1987</t>
+  </si>
+  <si>
+    <t>LENGO</t>
+  </si>
+  <si>
+    <t>Lucoqui</t>
+  </si>
+  <si>
+    <t>07/11/1984</t>
+  </si>
+  <si>
+    <t>24/04/2025</t>
+  </si>
+  <si>
+    <t>MAMBA</t>
+  </si>
+  <si>
+    <t>Benayi</t>
+  </si>
+  <si>
+    <t>15/07/1985</t>
+  </si>
+  <si>
+    <t>12/09/2024</t>
+  </si>
+  <si>
+    <t>MANTUIKA</t>
+  </si>
+  <si>
+    <t>Sara</t>
+  </si>
+  <si>
+    <t>15/12/1999</t>
+  </si>
+  <si>
+    <t>MEHMOOD</t>
+  </si>
+  <si>
+    <t>Aamir</t>
+  </si>
+  <si>
+    <t>15/05/1990</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>12/01/2025</t>
+  </si>
+  <si>
+    <t>MIAH</t>
+  </si>
+  <si>
+    <t>Mowab</t>
+  </si>
+  <si>
+    <t>28/05/1995</t>
+  </si>
+  <si>
+    <t>Bangladesh</t>
+  </si>
+  <si>
+    <t>01/09/2023</t>
+  </si>
+  <si>
+    <t>MOHAMED EL NOUR</t>
+  </si>
+  <si>
+    <t>Abdel</t>
+  </si>
+  <si>
+    <t>19/01/1977</t>
+  </si>
+  <si>
+    <t>MOHD</t>
+  </si>
+  <si>
+    <t>Azeem Pacha</t>
+  </si>
+  <si>
+    <t>04/04/1991</t>
+  </si>
+  <si>
+    <t>Inde</t>
+  </si>
+  <si>
+    <t>21/01/2025</t>
+  </si>
+  <si>
+    <t>NDUGBE</t>
+  </si>
+  <si>
+    <t>Josiah</t>
+  </si>
+  <si>
+    <t>10/10/1982</t>
+  </si>
+  <si>
+    <t>Nigéria</t>
+  </si>
+  <si>
+    <t>19/11/2023</t>
+  </si>
+  <si>
+    <t>NEHREBA</t>
+  </si>
+  <si>
+    <t>Iryna</t>
+  </si>
+  <si>
+    <t>28/02/1987</t>
+  </si>
+  <si>
+    <t>21/11/2024</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>Mohammed</t>
+  </si>
+  <si>
+    <t>01/01/1994</t>
+  </si>
+  <si>
+    <t>OVERCHENKO</t>
+  </si>
+  <si>
+    <t>Aleksandrova</t>
+  </si>
+  <si>
+    <t>30/09/1971</t>
+  </si>
+  <si>
+    <t>PINTO</t>
+  </si>
+  <si>
+    <t>Janet</t>
+  </si>
+  <si>
+    <t>23/02/1971</t>
+  </si>
+  <si>
+    <t>Pérou</t>
+  </si>
+  <si>
+    <t>Amérique du Sud</t>
+  </si>
+  <si>
+    <t>POPLEE</t>
+  </si>
+  <si>
+    <t>Daleep</t>
+  </si>
+  <si>
+    <t>01/09/1984</t>
+  </si>
+  <si>
+    <t>SHARIF IBRAHIM</t>
+  </si>
+  <si>
+    <t>Ahmed</t>
+  </si>
+  <si>
+    <t>01/01/1998</t>
+  </si>
+  <si>
+    <t>Somalie</t>
+  </si>
+  <si>
+    <t>SISSANI TORQUI</t>
+  </si>
+  <si>
+    <t>Malika</t>
+  </si>
+  <si>
+    <t>01/09/1956</t>
+  </si>
+  <si>
+    <t>Espagne</t>
+  </si>
+  <si>
+    <t>16/11/2023</t>
+  </si>
+  <si>
+    <t>YLDIRIM DOGAN</t>
+  </si>
+  <si>
+    <t>Ozgun</t>
+  </si>
+  <si>
+    <t>01/07/1979</t>
+  </si>
+  <si>
+    <t>Jocelyne PRECIADO / Véronique JANNES</t>
+  </si>
+  <si>
+    <t>ABAIDZE</t>
+  </si>
+  <si>
+    <t>Mariami</t>
+  </si>
+  <si>
+    <t>23/08/1991</t>
+  </si>
+  <si>
+    <t>ABDOU</t>
+  </si>
+  <si>
+    <t>Houfranie</t>
+  </si>
+  <si>
+    <t>31/12/1978</t>
+  </si>
+  <si>
+    <t>Comores</t>
+  </si>
+  <si>
+    <t>AHED MOHAMED</t>
+  </si>
+  <si>
+    <t>Mohamed</t>
+  </si>
+  <si>
+    <t>22/07/1993</t>
+  </si>
+  <si>
+    <t>01/05/2024</t>
+  </si>
+  <si>
+    <t>ALHAJ</t>
+  </si>
+  <si>
+    <t>Mudother</t>
+  </si>
+  <si>
+    <t>08/04/1999</t>
+  </si>
+  <si>
+    <t>25/11/2024</t>
+  </si>
+  <si>
+    <t>BEGUM</t>
+  </si>
+  <si>
+    <t>Lima</t>
+  </si>
+  <si>
+    <t>10/12/1990</t>
+  </si>
+  <si>
+    <t>CHKHAPELIA</t>
+  </si>
+  <si>
+    <t>Tamta</t>
+  </si>
+  <si>
+    <t>01/04/1992</t>
+  </si>
+  <si>
+    <t>01/01/2022</t>
+  </si>
+  <si>
+    <t>DIAMPITISA</t>
+  </si>
+  <si>
+    <t>Madalena</t>
+  </si>
+  <si>
+    <t>02/11/1967</t>
+  </si>
+  <si>
+    <t>EBRAHIM DUD</t>
+  </si>
+  <si>
+    <t>Nabil</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>Kiala Baptista</t>
+  </si>
+  <si>
+    <t>31/12/1994</t>
+  </si>
+  <si>
+    <t>ELIDRISSI BOUANANI</t>
+  </si>
+  <si>
+    <t>Fatima</t>
+  </si>
+  <si>
+    <t>01/01/1959</t>
+  </si>
+  <si>
+    <t>15/09/2022</t>
+  </si>
+  <si>
+    <t>FURAH KITAMBALA</t>
+  </si>
+  <si>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>26/11/2025</t>
+  </si>
+  <si>
+    <t>HASHEMI</t>
+  </si>
+  <si>
+    <t>Asghar</t>
+  </si>
+  <si>
+    <t>28/02/1999</t>
+  </si>
+  <si>
+    <t>IMERI</t>
+  </si>
+  <si>
+    <t>Mirela</t>
+  </si>
+  <si>
+    <t>30/05/1977</t>
+  </si>
+  <si>
+    <t>Albanie</t>
+  </si>
+  <si>
+    <t>10/05/2022</t>
+  </si>
+  <si>
+    <t>IREDIA</t>
+  </si>
+  <si>
+    <t>Tracy</t>
+  </si>
+  <si>
+    <t>27/07/1982</t>
+  </si>
+  <si>
+    <t>ISOMI</t>
+  </si>
+  <si>
+    <t>Febe</t>
+  </si>
+  <si>
+    <t>05/03/2001</t>
+  </si>
+  <si>
+    <t>JARA</t>
+  </si>
+  <si>
+    <t>Mario</t>
+  </si>
+  <si>
+    <t>19/01/2003</t>
+  </si>
+  <si>
+    <t>Chili</t>
+  </si>
+  <si>
+    <t>18/09/2025</t>
+  </si>
+  <si>
+    <t>KINAVUIDI</t>
+  </si>
+  <si>
+    <t>Viviane</t>
+  </si>
+  <si>
+    <t>29/06/1988</t>
+  </si>
+  <si>
+    <t>LAGOUNE</t>
+  </si>
+  <si>
+    <t>Ilham</t>
+  </si>
+  <si>
+    <t>15/08/2002</t>
+  </si>
+  <si>
+    <t>LUMBE OMOWO</t>
+  </si>
+  <si>
+    <t>Anne-Marie</t>
+  </si>
+  <si>
+    <t>18/03/1979</t>
+  </si>
+  <si>
+    <t>25/11/2025</t>
+  </si>
+  <si>
+    <t>MADALENA</t>
+  </si>
+  <si>
+    <t>Lidia</t>
+  </si>
+  <si>
+    <t>29/05/2018</t>
+  </si>
+  <si>
+    <t>14/11/2025</t>
+  </si>
+  <si>
+    <t>MATETA</t>
+  </si>
+  <si>
+    <t>Gloria</t>
+  </si>
+  <si>
+    <t>30/07/1994</t>
+  </si>
+  <si>
+    <t>NGELI</t>
+  </si>
+  <si>
+    <t>Yolande</t>
+  </si>
+  <si>
+    <t>06/12/1980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLIVEIRA </t>
+  </si>
+  <si>
+    <t>Laura</t>
+  </si>
+  <si>
+    <t>14/12/1986</t>
+  </si>
+  <si>
+    <t>02/06/2024</t>
+  </si>
+  <si>
+    <t>RIAHI</t>
+  </si>
+  <si>
+    <t>Souhail</t>
+  </si>
+  <si>
+    <t>13/11/1992</t>
+  </si>
+  <si>
+    <t>Tunisie</t>
+  </si>
+  <si>
+    <t>TIENE</t>
+  </si>
+  <si>
+    <t>Nawa</t>
+  </si>
+  <si>
+    <t>15/11/1996</t>
+  </si>
+  <si>
+    <t>Côte d'Ivoire</t>
+  </si>
+  <si>
+    <t>TINIKASCHVILI</t>
+  </si>
+  <si>
+    <t>Maka</t>
+  </si>
+  <si>
+    <t>21/09/1983</t>
+  </si>
+  <si>
+    <t>12/10/2021</t>
+  </si>
+  <si>
+    <t>TONOYAN</t>
+  </si>
+  <si>
+    <t>Alvard</t>
+  </si>
+  <si>
+    <t>10/01/1963</t>
+  </si>
+  <si>
+    <t>12/01/2016</t>
+  </si>
+  <si>
+    <t>VIUCHE GIRON</t>
+  </si>
+  <si>
+    <t>Sanyi</t>
+  </si>
+  <si>
+    <t>21/05/1995</t>
+  </si>
+  <si>
+    <t>Colombie</t>
+  </si>
+  <si>
+    <t>06/03/2025</t>
+  </si>
+  <si>
+    <t>Jean PITORIN / Jean-Luc HOUDAYER</t>
+  </si>
+  <si>
+    <t>BABALOLA</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
+    <t>10/11/1973</t>
+  </si>
+  <si>
+    <t>06/09/2022</t>
+  </si>
+  <si>
+    <t>01/12/2025</t>
+  </si>
+  <si>
+    <t>BARSEGHIAN</t>
+  </si>
+  <si>
+    <t>Norik</t>
+  </si>
+  <si>
+    <t>07/07/2006</t>
+  </si>
+  <si>
+    <t>CARBONO FERNANDEZ</t>
+  </si>
+  <si>
+    <t>Carolina</t>
+  </si>
+  <si>
+    <t>16/01/2025</t>
+  </si>
+  <si>
+    <t>CHEGGARI</t>
+  </si>
+  <si>
+    <t>Nour Eddin</t>
+  </si>
+  <si>
+    <t>23/10/1994</t>
+  </si>
+  <si>
+    <t>31/05/2023</t>
+  </si>
+  <si>
+    <t>HALILAJ</t>
+  </si>
+  <si>
+    <t>Lindita</t>
+  </si>
+  <si>
+    <t>23/02/1979</t>
+  </si>
+  <si>
+    <t>09/11/2023</t>
+  </si>
+  <si>
+    <t>KIAKU</t>
+  </si>
+  <si>
+    <t>Ana Marcela</t>
+  </si>
+  <si>
+    <t>19/02/1992</t>
+  </si>
+  <si>
+    <t>20/09/2023</t>
+  </si>
+  <si>
+    <t>LMABROUK</t>
+  </si>
+  <si>
+    <t>Oussama</t>
+  </si>
+  <si>
+    <t>01/02/2025</t>
+  </si>
+  <si>
+    <t>MANGAY</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>25/06/1990</t>
+  </si>
+  <si>
+    <t>MENAYAME NGOMA</t>
+  </si>
+  <si>
+    <t>Mera</t>
+  </si>
+  <si>
+    <t>05/05/1994</t>
+  </si>
+  <si>
+    <t>MUSTAFAYEVA</t>
+  </si>
+  <si>
+    <t>Gulkanim</t>
+  </si>
+  <si>
+    <t>17/09/1990</t>
+  </si>
+  <si>
+    <t>26/06/2019</t>
+  </si>
+  <si>
+    <t>NYINAWUMUNTU</t>
+  </si>
+  <si>
+    <t>Marie-Louise</t>
+  </si>
+  <si>
+    <t>Rwanda</t>
+  </si>
+  <si>
+    <t>OYEKAN</t>
+  </si>
+  <si>
+    <t>Patrick</t>
+  </si>
+  <si>
+    <t>17/01/1976</t>
+  </si>
+  <si>
+    <t>REYES OTERO</t>
+  </si>
+  <si>
+    <t>Victor Hugo</t>
+  </si>
+  <si>
+    <t>29/05/1986</t>
+  </si>
+  <si>
+    <t>06/05/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAUCEDO  FERNANDEZ</t>
+  </si>
+  <si>
+    <t>Verselia</t>
+  </si>
+  <si>
+    <t>03/07/1989</t>
+  </si>
+  <si>
+    <t>Samedi</t>
+  </si>
+  <si>
+    <t>Louise-Anne</t>
+  </si>
+  <si>
+    <t>ADDOUT SOULEMAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHMED MOHAMED </t>
+  </si>
+  <si>
+    <t>AJAYI</t>
+  </si>
+  <si>
+    <t>Matthew</t>
+  </si>
+  <si>
+    <t>Mudather</t>
+  </si>
+  <si>
+    <t>ANTURIA</t>
+  </si>
+  <si>
+    <t>Saïd Bacar</t>
+  </si>
+  <si>
+    <t>Elizandra Maria</t>
+  </si>
+  <si>
+    <t>EGBOYE</t>
+  </si>
+  <si>
+    <t>Bridget</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>HACHIM</t>
+  </si>
+  <si>
+    <t>Gyurme</t>
+  </si>
+  <si>
+    <t>KHAROT</t>
+  </si>
+  <si>
+    <t>Zadihullah</t>
+  </si>
+  <si>
+    <t>MOUSSA BABAY</t>
+  </si>
+  <si>
+    <t>Abdelgasim</t>
+  </si>
+  <si>
+    <t>MUHIA</t>
+  </si>
+  <si>
+    <t>Virginia</t>
   </si>
   <si>
     <t>Kenya</t>
-  </si>
-  <si>
-    <t>AMRANI</t>
-  </si>
-  <si>
-    <t>Abdulkadir Mohamed</t>
-  </si>
-  <si>
-    <t>04/04/1975</t>
-  </si>
-  <si>
-    <t>Tanzannie</t>
-  </si>
-  <si>
-    <t>17/09/2024</t>
-  </si>
-  <si>
-    <t>BATOL</t>
-  </si>
-  <si>
-    <t>Hassan</t>
-  </si>
-  <si>
-    <t>15/05/1997</t>
-  </si>
-  <si>
-    <t>01/09/2024</t>
-  </si>
-  <si>
-    <t>BEZHANISHVILI</t>
-  </si>
-  <si>
-    <t>Zurab</t>
-  </si>
-  <si>
-    <t>30/06/1974</t>
-  </si>
-  <si>
-    <t>06/02/2025</t>
-  </si>
-  <si>
-    <t>BOUZID</t>
-  </si>
-  <si>
-    <t>Bouchra</t>
-  </si>
-  <si>
-    <t>01/01/1983</t>
-  </si>
-  <si>
-    <t>Maroc</t>
-  </si>
-  <si>
-    <t>24/03/2023</t>
-  </si>
-  <si>
-    <t>KALANDIA</t>
-  </si>
-  <si>
-    <t>Tamar</t>
-  </si>
-  <si>
-    <t>09/10/1979</t>
-  </si>
-  <si>
-    <t>22/05/2024</t>
-  </si>
-  <si>
-    <t>KHACHATRYAN</t>
-  </si>
-  <si>
-    <t>Rita</t>
-  </si>
-  <si>
-    <t>21/01/1973</t>
-  </si>
-  <si>
-    <t>01/10/2024</t>
-  </si>
-  <si>
-    <t>KHUTSISHVILI</t>
-  </si>
-  <si>
-    <t>Rusudan</t>
-  </si>
-  <si>
-    <t>08/11/1987</t>
-  </si>
-  <si>
-    <t>LENGO</t>
-  </si>
-  <si>
-    <t>Lucoqui</t>
-  </si>
-  <si>
-    <t>07/11/1984</t>
-  </si>
-  <si>
-    <t>24/04/2025</t>
-  </si>
-  <si>
-    <t>MAMBA</t>
-  </si>
-  <si>
-    <t>Benayi</t>
-  </si>
-  <si>
-    <t>15/07/1985</t>
-  </si>
-  <si>
-    <t>12/09/2024</t>
-  </si>
-  <si>
-    <t>MANTUIKA</t>
-  </si>
-  <si>
-    <t>Sara</t>
-  </si>
-  <si>
-    <t>15/12/1999</t>
-  </si>
-  <si>
-    <t>MEHMOOD</t>
-  </si>
-  <si>
-    <t>Aamir</t>
-  </si>
-  <si>
-    <t>15/05/1990</t>
-  </si>
-  <si>
-    <t>Pakistan</t>
-  </si>
-  <si>
-    <t>12/01/2025</t>
-  </si>
-  <si>
-    <t>MIAH</t>
-  </si>
-  <si>
-    <t>Mowab</t>
-  </si>
-  <si>
-    <t>28/05/1995</t>
-  </si>
-  <si>
-    <t>Bangladesh</t>
-  </si>
-  <si>
-    <t>01/09/2023</t>
-  </si>
-  <si>
-    <t>MOHAMED EL NOUR</t>
-  </si>
-  <si>
-    <t>Abdel</t>
-  </si>
-  <si>
-    <t>19/01/1977</t>
-  </si>
-  <si>
-    <t>MOHD</t>
-  </si>
-  <si>
-    <t>Azeem Pacha</t>
-  </si>
-  <si>
-    <t>04/04/1991</t>
-  </si>
-  <si>
-    <t>Inde</t>
-  </si>
-  <si>
-    <t>21/01/2025</t>
-  </si>
-  <si>
-    <t>NDUGBE</t>
-  </si>
-  <si>
-    <t>Josiah</t>
-  </si>
-  <si>
-    <t>10/10/1982</t>
-  </si>
-  <si>
-    <t>Nigéria</t>
-  </si>
-  <si>
-    <t>19/11/2023</t>
-  </si>
-  <si>
-    <t>NEHREBA</t>
-  </si>
-  <si>
-    <t>Iryna</t>
-  </si>
-  <si>
-    <t>28/02/1987</t>
-  </si>
-  <si>
-    <t>21/11/2024</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>Mohammed</t>
-  </si>
-  <si>
-    <t>01/01/1994</t>
-  </si>
-  <si>
-    <t>OVERCHENKO</t>
-  </si>
-  <si>
-    <t>Aleksandrova</t>
-  </si>
-  <si>
-    <t>30/09/1971</t>
-  </si>
-  <si>
-    <t>PINTO</t>
-  </si>
-  <si>
-    <t>Janet</t>
-  </si>
-  <si>
-    <t>23/02/1971</t>
-  </si>
-  <si>
-    <t>Pérou</t>
-  </si>
-  <si>
-    <t>Amérique du Sud</t>
-  </si>
-  <si>
-    <t>POPLEE</t>
-  </si>
-  <si>
-    <t>Daleep</t>
-  </si>
-  <si>
-    <t>01/09/1984</t>
-  </si>
-  <si>
-    <t>SHARIF IBRAHIM</t>
-  </si>
-  <si>
-    <t>Ahmed</t>
-  </si>
-  <si>
-    <t>01/01/1998</t>
-  </si>
-  <si>
-    <t>Somalie</t>
-  </si>
-  <si>
-    <t>SISSANI TORQUI</t>
-  </si>
-  <si>
-    <t>Malika</t>
-  </si>
-  <si>
-    <t>01/09/1956</t>
-  </si>
-  <si>
-    <t>Espagne</t>
-  </si>
-  <si>
-    <t>16/11/2023</t>
-  </si>
-  <si>
-    <t>YLDIRIM DOGAN</t>
-  </si>
-  <si>
-    <t>Ozgun</t>
-  </si>
-  <si>
-    <t>01/07/1979</t>
-  </si>
-  <si>
-    <t>Jocelyne PRECIADO / Véronique JANNES</t>
-  </si>
-  <si>
-    <t>ABAIDZE</t>
-  </si>
-  <si>
-    <t>Mariami</t>
-  </si>
-  <si>
-    <t>23/08/1991</t>
-  </si>
-  <si>
-    <t>ABDOU</t>
-  </si>
-  <si>
-    <t>Houfranie</t>
-  </si>
-  <si>
-    <t>31/12/1978</t>
-  </si>
-  <si>
-    <t>Comores</t>
-  </si>
-  <si>
-    <t>AHED MOHAMED</t>
-  </si>
-  <si>
-    <t>Mohamed</t>
-  </si>
-  <si>
-    <t>22/07/1993</t>
-  </si>
-  <si>
-    <t>01/05/2024</t>
-  </si>
-  <si>
-    <t>ALHAJ</t>
-  </si>
-  <si>
-    <t>Mudother</t>
-  </si>
-  <si>
-    <t>08/04/1999</t>
-  </si>
-  <si>
-    <t>25/11/2024</t>
-  </si>
-  <si>
-    <t>BEGUM</t>
-  </si>
-  <si>
-    <t>Lima</t>
-  </si>
-  <si>
-    <t>10/12/1990</t>
-  </si>
-  <si>
-    <t>CHKHAPELIA</t>
-  </si>
-  <si>
-    <t>Tamta</t>
-  </si>
-  <si>
-    <t>01/04/1992</t>
-  </si>
-  <si>
-    <t>01/01/2022</t>
-  </si>
-  <si>
-    <t>DIAMPITISA</t>
-  </si>
-  <si>
-    <t>Madalena</t>
-  </si>
-  <si>
-    <t>02/11/1967</t>
-  </si>
-  <si>
-    <t>EBRAHIM DUD</t>
-  </si>
-  <si>
-    <t>Nabil</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>Kiala Baptista</t>
-  </si>
-  <si>
-    <t>31/12/1994</t>
-  </si>
-  <si>
-    <t>ELIDRISSI BOUANANI</t>
-  </si>
-  <si>
-    <t>Fatima</t>
-  </si>
-  <si>
-    <t>01/01/1959</t>
-  </si>
-  <si>
-    <t>15/09/2022</t>
-  </si>
-  <si>
-    <t>FURAH KITAMBALA</t>
-  </si>
-  <si>
-    <t>Patricia</t>
-  </si>
-  <si>
-    <t>26/11/2025</t>
-  </si>
-  <si>
-    <t>HASHEMI</t>
-  </si>
-  <si>
-    <t>Asghar</t>
-  </si>
-  <si>
-    <t>28/02/1999</t>
-  </si>
-  <si>
-    <t>IMERI</t>
-  </si>
-  <si>
-    <t>Mirela</t>
-  </si>
-  <si>
-    <t>30/05/1977</t>
-  </si>
-  <si>
-    <t>Albanie</t>
-  </si>
-  <si>
-    <t>10/05/2022</t>
-  </si>
-  <si>
-    <t>IREDIA</t>
-  </si>
-  <si>
-    <t>Tracy</t>
-  </si>
-  <si>
-    <t>27/07/1982</t>
-  </si>
-  <si>
-    <t>ISOMI</t>
-  </si>
-  <si>
-    <t>Febe</t>
-  </si>
-  <si>
-    <t>05/03/2001</t>
-  </si>
-  <si>
-    <t>JARA</t>
-  </si>
-  <si>
-    <t>Mario</t>
-  </si>
-  <si>
-    <t>19/01/2003</t>
-  </si>
-  <si>
-    <t>Chili</t>
-  </si>
-  <si>
-    <t>18/09/2025</t>
-  </si>
-  <si>
-    <t>KINAVUIDI</t>
-  </si>
-  <si>
-    <t>Viviane</t>
-  </si>
-  <si>
-    <t>29/06/1988</t>
-  </si>
-  <si>
-    <t>LAGOUNE</t>
-  </si>
-  <si>
-    <t>Ilham</t>
-  </si>
-  <si>
-    <t>15/08/2002</t>
-  </si>
-  <si>
-    <t>LUMBE OMOWO</t>
-  </si>
-  <si>
-    <t>Anne-Marie</t>
-  </si>
-  <si>
-    <t>18/03/1979</t>
-  </si>
-  <si>
-    <t>25/11/2025</t>
-  </si>
-  <si>
-    <t>MADALENA</t>
-  </si>
-  <si>
-    <t>Lidia</t>
-  </si>
-  <si>
-    <t>29/05/2018</t>
-  </si>
-  <si>
-    <t>14/11/2025</t>
-  </si>
-  <si>
-    <t>MATETA</t>
-  </si>
-  <si>
-    <t>Gloria</t>
-  </si>
-  <si>
-    <t>30/07/1994</t>
-  </si>
-  <si>
-    <t>NGELI</t>
-  </si>
-  <si>
-    <t>Yolande</t>
-  </si>
-  <si>
-    <t>06/12/1980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLIVEIRA </t>
-  </si>
-  <si>
-    <t>Laura</t>
-  </si>
-  <si>
-    <t>14/12/1986</t>
-  </si>
-  <si>
-    <t>02/06/2024</t>
-  </si>
-  <si>
-    <t>RIAHI</t>
-  </si>
-  <si>
-    <t>Souhail</t>
-  </si>
-  <si>
-    <t>13/11/1992</t>
-  </si>
-  <si>
-    <t>Tunisie</t>
-  </si>
-  <si>
-    <t>TIENE</t>
-  </si>
-  <si>
-    <t>Nawa</t>
-  </si>
-  <si>
-    <t>15/11/1996</t>
-  </si>
-  <si>
-    <t>Côte d'Ivoire</t>
-  </si>
-  <si>
-    <t>TINIKASCHVILI</t>
-  </si>
-  <si>
-    <t>Maka</t>
-  </si>
-  <si>
-    <t>21/09/1983</t>
-  </si>
-  <si>
-    <t>12/10/2021</t>
-  </si>
-  <si>
-    <t>TONOYAN</t>
-  </si>
-  <si>
-    <t>Alvard</t>
-  </si>
-  <si>
-    <t>10/01/1963</t>
-  </si>
-  <si>
-    <t>12/01/2016</t>
-  </si>
-  <si>
-    <t>VIUCHE GIRON</t>
-  </si>
-  <si>
-    <t>Sanyi</t>
-  </si>
-  <si>
-    <t>21/05/1995</t>
-  </si>
-  <si>
-    <t>Colombie</t>
-  </si>
-  <si>
-    <t>06/03/2025</t>
-  </si>
-  <si>
-    <t>Jean PITORIN / Jean-Luc HOUDAYER</t>
-  </si>
-  <si>
-    <t>BABALOLA</t>
-  </si>
-  <si>
-    <t>Elizabeth</t>
-  </si>
-  <si>
-    <t>10/11/1973</t>
-  </si>
-  <si>
-    <t>AFRIQUE</t>
-  </si>
-  <si>
-    <t>06/09/2022</t>
-  </si>
-  <si>
-    <t>01/12/2025</t>
-  </si>
-  <si>
-    <t>BARSEGHIAN</t>
-  </si>
-  <si>
-    <t>Norik</t>
-  </si>
-  <si>
-    <t>07/07/2006</t>
-  </si>
-  <si>
-    <t>11/09/2025</t>
-  </si>
-  <si>
-    <t>CARBONO FERNANDEZ</t>
-  </si>
-  <si>
-    <t>Carolina</t>
-  </si>
-  <si>
-    <t>16/01/2025</t>
-  </si>
-  <si>
-    <t>CHEGGARI</t>
-  </si>
-  <si>
-    <t>Nour Eddin</t>
-  </si>
-  <si>
-    <t>23/10/1994</t>
-  </si>
-  <si>
-    <t>31/05/2023</t>
-  </si>
-  <si>
-    <t>HALILAJ</t>
-  </si>
-  <si>
-    <t>Lindita</t>
-  </si>
-  <si>
-    <t>23/02/1979</t>
-  </si>
-  <si>
-    <t>09/11/2023</t>
-  </si>
-  <si>
-    <t>KIAKU</t>
-  </si>
-  <si>
-    <t>Ana Marcela</t>
-  </si>
-  <si>
-    <t>19/02/1992</t>
-  </si>
-  <si>
-    <t>20/09/2023</t>
-  </si>
-  <si>
-    <t>LMABROUK</t>
-  </si>
-  <si>
-    <t>Oussama</t>
-  </si>
-  <si>
-    <t>01/02/2025</t>
-  </si>
-  <si>
-    <t>MANGAY</t>
-  </si>
-  <si>
-    <t>Paul</t>
-  </si>
-  <si>
-    <t>25/06/1990</t>
-  </si>
-  <si>
-    <t>MENAYAME NGOMA</t>
-  </si>
-  <si>
-    <t>Mera</t>
-  </si>
-  <si>
-    <t>05/05/1994</t>
-  </si>
-  <si>
-    <t>MUSTAFAYEVA</t>
-  </si>
-  <si>
-    <t>Gulkanim</t>
-  </si>
-  <si>
-    <t>17/09/1990</t>
-  </si>
-  <si>
-    <t>26/06/2019</t>
-  </si>
-  <si>
-    <t>NYINAWUMUNTU</t>
-  </si>
-  <si>
-    <t>Marie-Louise</t>
-  </si>
-  <si>
-    <t>Rwanda</t>
-  </si>
-  <si>
-    <t>19/09/2024</t>
-  </si>
-  <si>
-    <t>OYEKAN</t>
-  </si>
-  <si>
-    <t>Patrick</t>
-  </si>
-  <si>
-    <t>17/01/1976</t>
-  </si>
-  <si>
-    <t>REYES OTERO</t>
-  </si>
-  <si>
-    <t>Victor Hugo</t>
-  </si>
-  <si>
-    <t>29/05/1986</t>
-  </si>
-  <si>
-    <t>06/05/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAUCEDO  FERNANDEZ</t>
-  </si>
-  <si>
-    <t>Verselia</t>
-  </si>
-  <si>
-    <t>03/07/1989</t>
-  </si>
-  <si>
-    <t>Samedi</t>
-  </si>
-  <si>
-    <t>Louise-Anne</t>
-  </si>
-  <si>
-    <t>ABAKAR ADAM</t>
-  </si>
-  <si>
-    <t>Seida</t>
-  </si>
-  <si>
-    <t>Soudan du Sud</t>
-  </si>
-  <si>
-    <t>ADDOUT SOULEMAN</t>
-  </si>
-  <si>
-    <t>Ibrahim</t>
-  </si>
-  <si>
-    <t>AHMED</t>
-  </si>
-  <si>
-    <t>Panama</t>
-  </si>
-  <si>
-    <t>Amérique du Nord</t>
-  </si>
-  <si>
-    <t>01/01/2025</t>
-  </si>
-  <si>
-    <t>01/01/2030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHMED MOHAMED </t>
-  </si>
-  <si>
-    <t>AJAYI</t>
-  </si>
-  <si>
-    <t>Matthew</t>
-  </si>
-  <si>
-    <t>Nigeria</t>
-  </si>
-  <si>
-    <t>Mudather</t>
-  </si>
-  <si>
-    <t>ANTURIA</t>
-  </si>
-  <si>
-    <t>Saïd Bacar</t>
-  </si>
-  <si>
-    <t>AUGUSTO ANTONIO</t>
-  </si>
-  <si>
-    <t>Elizandra Maria</t>
-  </si>
-  <si>
-    <t>12/02/2006</t>
-  </si>
-  <si>
-    <t>EGBOYE</t>
-  </si>
-  <si>
-    <t>Bridget</t>
-  </si>
-  <si>
-    <t>Michael</t>
-  </si>
-  <si>
-    <t>HACHIM</t>
-  </si>
-  <si>
-    <t>KARMA</t>
-  </si>
-  <si>
-    <t>Gyurme</t>
-  </si>
-  <si>
-    <t>08/02/1997</t>
-  </si>
-  <si>
-    <t>08/10/2025</t>
-  </si>
-  <si>
-    <t>KHAROT</t>
-  </si>
-  <si>
-    <t>Zadihullah</t>
-  </si>
-  <si>
-    <t>MOUSSA BABAY</t>
-  </si>
-  <si>
-    <t>Abdelgasim</t>
-  </si>
-  <si>
-    <t>MUHIA</t>
-  </si>
-  <si>
-    <t>Virginia</t>
   </si>
   <si>
     <t>MUKHTAR KHIL</t>
@@ -1431,7 +1443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:J134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.323410987854" customWidth="1"/>
@@ -1439,8 +1451,8 @@
     <col min="3" max="3" width="26.2138481140137" customWidth="1"/>
     <col min="4" max="4" width="20.5225353240967" customWidth="1"/>
     <col min="5" max="5" width="22.1085662841797" customWidth="1"/>
-    <col min="6" max="6" width="14.4772424697876" customWidth="1"/>
-    <col min="7" max="7" width="17.7080821990967" customWidth="1"/>
+    <col min="6" max="6" width="33.0243949890137" customWidth="1"/>
+    <col min="7" max="7" width="16.5499725341797" customWidth="1"/>
     <col min="8" max="8" width="9.77960538864136" customWidth="1"/>
     <col min="9" max="9" width="22.4257164001465" customWidth="1"/>
     <col min="10" max="10" width="14.8274097442627" customWidth="1"/>
@@ -1530,13 +1542,13 @@
         <v>23</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J3" s="0" t="s">
         <v>19</v>
@@ -1559,16 +1571,16 @@
         <v>27</v>
       </c>
       <c r="F4" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="0" t="s">
         <v>28</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="0" t="s">
-        <v>30</v>
       </c>
       <c r="J4" s="0" t="s">
         <v>19</v>
@@ -1582,25 +1594,25 @@
         <v>11</v>
       </c>
       <c r="C5" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="F5" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="G5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="0" t="s">
         <v>33</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="0" t="s">
-        <v>34</v>
       </c>
       <c r="J5" s="0" t="s">
         <v>19</v>
@@ -1614,25 +1626,25 @@
         <v>11</v>
       </c>
       <c r="C6" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="E6" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="F6" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="G6" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="H6" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="0" t="s">
         <v>39</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" s="0" t="s">
-        <v>41</v>
       </c>
       <c r="J6" s="0" t="s">
         <v>19</v>
@@ -1646,25 +1658,25 @@
         <v>11</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D7" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="F7" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="0" t="s">
         <v>43</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>41</v>
       </c>
       <c r="J7" s="0" t="s">
         <v>19</v>
@@ -1687,30 +1699,30 @@
         <v>46</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J8" s="0" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0">
-        <v>1</v>
+      <c r="A9" s="0" t="s">
+        <v>10</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>50</v>
@@ -1719,48 +1731,48 @@
         <v>51</v>
       </c>
       <c r="F9" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="I9" s="0" t="s">
+      <c r="D10" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="J9" s="0" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0">
-        <v>1</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="0" t="s">
+      <c r="E10" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="F10" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="0" t="s">
         <v>55</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" s="0" t="s">
-        <v>58</v>
       </c>
       <c r="J10" s="0" t="s">
         <v>19</v>
@@ -1771,28 +1783,28 @@
         <v>1</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C11" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="F11" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="0" t="s">
+      <c r="G11" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="0" t="s">
         <v>61</v>
-      </c>
-      <c r="G11" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="I11" s="0" t="s">
-        <v>62</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>19</v>
@@ -1803,28 +1815,28 @@
         <v>1</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C12" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="E12" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="F12" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="G12" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="0" t="s">
         <v>66</v>
-      </c>
-      <c r="G12" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="H12" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="0" t="s">
-        <v>67</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>19</v>
@@ -1835,28 +1847,28 @@
         <v>1</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C13" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="E13" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="F13" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="G13" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="0" t="s">
         <v>71</v>
-      </c>
-      <c r="G13" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="H13" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="I13" s="0" t="s">
-        <v>72</v>
       </c>
       <c r="J13" s="0" t="s">
         <v>19</v>
@@ -1867,28 +1879,28 @@
         <v>1</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C14" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="E14" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="F14" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="G14" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="0" t="s">
         <v>76</v>
-      </c>
-      <c r="G14" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="H14" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="I14" s="0" t="s">
-        <v>77</v>
       </c>
       <c r="J14" s="0" t="s">
         <v>19</v>
@@ -1899,28 +1911,28 @@
         <v>1</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C15" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="E15" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="0" t="s">
-        <v>80</v>
-      </c>
       <c r="F15" s="0" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J15" s="0" t="s">
         <v>19</v>
@@ -1931,28 +1943,28 @@
         <v>1</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C16" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="F16" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="G16" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="0" t="s">
         <v>84</v>
-      </c>
-      <c r="F16" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="H16" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="I16" s="0" t="s">
-        <v>53</v>
       </c>
       <c r="J16" s="0" t="s">
         <v>19</v>
@@ -1963,7 +1975,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>85</v>
@@ -1972,16 +1984,16 @@
         <v>86</v>
       </c>
       <c r="E17" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="0" t="s">
         <v>87</v>
       </c>
-      <c r="F17" s="0" t="s">
-        <v>52</v>
-      </c>
       <c r="G17" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I17" s="0" t="s">
         <v>88</v>
@@ -1995,7 +2007,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>89</v>
@@ -2007,16 +2019,16 @@
         <v>91</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="J18" s="0" t="s">
         <v>19</v>
@@ -2027,28 +2039,28 @@
         <v>1</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="J19" s="0" t="s">
         <v>19</v>
@@ -2056,10 +2068,10 @@
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>97</v>
@@ -2071,16 +2083,16 @@
         <v>99</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="J20" s="0" t="s">
         <v>19</v>
@@ -2088,10 +2100,10 @@
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>101</v>
@@ -2103,16 +2115,16 @@
         <v>103</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="J21" s="0" t="s">
         <v>19</v>
@@ -2120,10 +2132,10 @@
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>105</v>
@@ -2135,16 +2147,16 @@
         <v>107</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="J22" s="0" t="s">
         <v>19</v>
@@ -2152,31 +2164,31 @@
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="C23" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="0" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="E23" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="E23" s="0" t="s">
-        <v>19</v>
-      </c>
       <c r="F23" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="G23" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H23" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="0" t="s">
         <v>111</v>
-      </c>
-      <c r="G23" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="H23" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="I23" s="0" t="s">
-        <v>41</v>
       </c>
       <c r="J23" s="0" t="s">
         <v>19</v>
@@ -2184,10 +2196,10 @@
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>112</v>
@@ -2199,16 +2211,16 @@
         <v>114</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="J24" s="0" t="s">
         <v>19</v>
@@ -2216,31 +2228,31 @@
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>115</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>26</v>
+        <v>116</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F25" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="G25" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" s="0" t="s">
         <v>28</v>
-      </c>
-      <c r="G25" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="H25" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="I25" s="0" t="s">
-        <v>117</v>
       </c>
       <c r="J25" s="0" t="s">
         <v>19</v>
@@ -2251,28 +2263,28 @@
         <v>2</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H26" s="0" t="s">
         <v>17</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="J26" s="0" t="s">
         <v>19</v>
@@ -2283,28 +2295,28 @@
         <v>2</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="F27" s="0" t="s">
         <v>23</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
       <c r="J27" s="0" t="s">
         <v>19</v>
@@ -2315,28 +2327,28 @@
         <v>2</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="J28" s="0" t="s">
         <v>19</v>
@@ -2347,25 +2359,25 @@
         <v>2</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>131</v>
+        <v>37</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I29" s="0" t="s">
         <v>132</v>
@@ -2379,25 +2391,25 @@
         <v>2</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>2</v>
+        <v>133</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I30" s="0" t="s">
         <v>136</v>
@@ -2411,7 +2423,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>137</v>
@@ -2420,19 +2432,19 @@
         <v>138</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="J31" s="0" t="s">
         <v>19</v>
@@ -2443,28 +2455,28 @@
         <v>2</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C32" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="E32" s="0" t="s">
         <v>141</v>
       </c>
-      <c r="D32" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="E32" s="0" t="s">
-        <v>143</v>
-      </c>
       <c r="F32" s="0" t="s">
-        <v>144</v>
+        <v>75</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>145</v>
+        <v>76</v>
       </c>
       <c r="J32" s="0" t="s">
         <v>19</v>
@@ -2475,28 +2487,28 @@
         <v>2</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H33" s="0" t="s">
         <v>17</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="J33" s="0" t="s">
         <v>19</v>
@@ -2507,28 +2519,28 @@
         <v>2</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="J34" s="0" t="s">
         <v>19</v>
@@ -2539,28 +2551,28 @@
         <v>2</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="G35" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="J35" s="0" t="s">
         <v>19</v>
@@ -2571,28 +2583,28 @@
         <v>2</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>52</v>
+        <v>154</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="J36" s="0" t="s">
         <v>19</v>
@@ -2600,31 +2612,31 @@
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B37" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="E37" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="F37" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="G37" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H37" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" s="0" t="s">
         <v>159</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>160</v>
-      </c>
-      <c r="D37" s="0" t="s">
-        <v>161</v>
-      </c>
-      <c r="E37" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="F37" s="0" t="s">
-        <v>163</v>
-      </c>
-      <c r="G37" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="H37" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="I37" s="0" t="s">
-        <v>145</v>
       </c>
       <c r="J37" s="0" t="s">
         <v>19</v>
@@ -2632,31 +2644,31 @@
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>167</v>
+        <v>104</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="J38" s="0" t="s">
         <v>19</v>
@@ -2664,31 +2676,31 @@
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>15</v>
+        <v>167</v>
       </c>
       <c r="G39" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>172</v>
+        <v>125</v>
       </c>
       <c r="J39" s="0" t="s">
         <v>19</v>
@@ -2696,31 +2708,31 @@
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>176</v>
+        <v>55</v>
       </c>
       <c r="J40" s="0" t="s">
         <v>19</v>
@@ -2728,31 +2740,31 @@
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="G41" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>181</v>
+        <v>49</v>
       </c>
       <c r="J41" s="0" t="s">
         <v>19</v>
@@ -2760,31 +2772,31 @@
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>185</v>
+        <v>49</v>
       </c>
       <c r="J42" s="0" t="s">
         <v>19</v>
@@ -2792,31 +2804,31 @@
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="J43" s="0" t="s">
         <v>19</v>
@@ -2824,31 +2836,31 @@
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="J44" s="0" t="s">
         <v>19</v>
@@ -2859,28 +2871,28 @@
         <v>3</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
       <c r="G45" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="J45" s="0" t="s">
         <v>19</v>
@@ -2891,19 +2903,19 @@
         <v>3</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="G46" s="0" t="s">
         <v>16</v>
@@ -2912,7 +2924,7 @@
         <v>17</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="J46" s="0" t="s">
         <v>19</v>
@@ -2923,28 +2935,28 @@
         <v>3</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>100</v>
+        <v>198</v>
       </c>
       <c r="J47" s="0" t="s">
         <v>19</v>
@@ -2955,28 +2967,28 @@
         <v>3</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>206</v>
+        <v>122</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="J48" s="0" t="s">
         <v>19</v>
@@ -2987,28 +2999,28 @@
         <v>3</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>212</v>
+        <v>75</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="J49" s="0" t="s">
         <v>19</v>
@@ -3019,28 +3031,28 @@
         <v>3</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>145</v>
+        <v>210</v>
       </c>
       <c r="J50" s="0" t="s">
         <v>19</v>
@@ -3051,28 +3063,28 @@
         <v>3</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>220</v>
+        <v>75</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="J51" s="0" t="s">
         <v>19</v>
@@ -3083,28 +3095,28 @@
         <v>3</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>225</v>
+        <v>65</v>
       </c>
       <c r="G52" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="J52" s="0" t="s">
         <v>19</v>
@@ -3115,28 +3127,28 @@
         <v>3</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="H53" s="0" t="s">
         <v>17</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="J53" s="0" t="s">
         <v>19</v>
@@ -3147,28 +3159,28 @@
         <v>3</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G54" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>168</v>
+        <v>61</v>
       </c>
       <c r="J54" s="0" t="s">
         <v>19</v>
@@ -3179,28 +3191,28 @@
         <v>3</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>81</v>
+        <v>228</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>88</v>
+        <v>229</v>
       </c>
       <c r="J55" s="0" t="s">
         <v>19</v>
@@ -3211,28 +3223,28 @@
         <v>3</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>241</v>
+        <v>38</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>145</v>
+        <v>234</v>
       </c>
       <c r="J56" s="0" t="s">
         <v>19</v>
@@ -3243,28 +3255,28 @@
         <v>3</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>168</v>
+        <v>125</v>
       </c>
       <c r="J57" s="0" t="s">
         <v>19</v>
@@ -3275,28 +3287,28 @@
         <v>3</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>88</v>
+        <v>242</v>
       </c>
       <c r="J58" s="0" t="s">
         <v>19</v>
@@ -3307,28 +3319,28 @@
         <v>3</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="J59" s="0" t="s">
         <v>19</v>
@@ -3339,28 +3351,28 @@
         <v>3</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="H60" s="0" t="s">
         <v>17</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>172</v>
+        <v>251</v>
       </c>
       <c r="J60" s="0" t="s">
         <v>19</v>
@@ -3368,31 +3380,31 @@
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="J61" s="0" t="s">
         <v>19</v>
@@ -3400,31 +3412,31 @@
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B62" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="D62" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="E62" s="0" t="s">
         <v>257</v>
       </c>
-      <c r="C62" s="0" t="s">
-        <v>261</v>
-      </c>
-      <c r="D62" s="0" t="s">
-        <v>262</v>
-      </c>
-      <c r="E62" s="0" t="s">
-        <v>263</v>
-      </c>
       <c r="F62" s="0" t="s">
-        <v>264</v>
+        <v>104</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="H62" s="0" t="s">
         <v>17</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="J62" s="0" t="s">
         <v>19</v>
@@ -3432,31 +3444,31 @@
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>15</v>
+        <v>261</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>16</v>
+        <v>262</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>268</v>
+        <v>125</v>
       </c>
       <c r="J63" s="0" t="s">
         <v>19</v>
@@ -3464,31 +3476,31 @@
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>272</v>
+        <v>190</v>
       </c>
       <c r="J64" s="0" t="s">
         <v>19</v>
@@ -3496,31 +3508,31 @@
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>212</v>
+        <v>269</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="J65" s="0" t="s">
         <v>19</v>
@@ -3528,31 +3540,31 @@
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>52</v>
+        <v>273</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="H66" s="0" t="s">
         <v>17</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="J66" s="0" t="s">
         <v>19</v>
@@ -3560,31 +3572,31 @@
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H67" s="0" t="s">
         <v>17</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>100</v>
+        <v>194</v>
       </c>
       <c r="J67" s="0" t="s">
         <v>19</v>
@@ -3595,28 +3607,28 @@
         <v>4</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>19</v>
+        <v>281</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="J68" s="0" t="s">
         <v>19</v>
@@ -3627,28 +3639,28 @@
         <v>4</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C69" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="D69" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="E69" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="F69" s="0" t="s">
         <v>285</v>
       </c>
-      <c r="D69" s="0" t="s">
-        <v>286</v>
-      </c>
-      <c r="E69" s="0" t="s">
-        <v>287</v>
-      </c>
-      <c r="F69" s="0" t="s">
-        <v>66</v>
-      </c>
       <c r="G69" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>272</v>
+        <v>125</v>
       </c>
       <c r="J69" s="0" t="s">
         <v>19</v>
@@ -3659,28 +3671,28 @@
         <v>4</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C70" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="D70" s="0" t="s">
+        <v>287</v>
+      </c>
+      <c r="E70" s="0" t="s">
         <v>288</v>
       </c>
-      <c r="D70" s="0" t="s">
+      <c r="F70" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G70" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H70" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I70" s="0" t="s">
         <v>289</v>
-      </c>
-      <c r="E70" s="0" t="s">
-        <v>290</v>
-      </c>
-      <c r="F70" s="0" t="s">
-        <v>180</v>
-      </c>
-      <c r="G70" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="H70" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="I70" s="0" t="s">
-        <v>291</v>
       </c>
       <c r="J70" s="0" t="s">
         <v>19</v>
@@ -3691,28 +3703,28 @@
         <v>4</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C71" s="0" t="s">
+        <v>290</v>
+      </c>
+      <c r="D71" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="E71" s="0" t="s">
         <v>292</v>
       </c>
-      <c r="D71" s="0" t="s">
+      <c r="F71" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G71" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H71" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I71" s="0" t="s">
         <v>293</v>
-      </c>
-      <c r="E71" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="F71" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="G71" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="H71" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="I71" s="0" t="s">
-        <v>294</v>
       </c>
       <c r="J71" s="0" t="s">
         <v>19</v>
@@ -3723,28 +3735,28 @@
         <v>4</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C72" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="D72" s="0" t="s">
         <v>295</v>
       </c>
-      <c r="D72" s="0" t="s">
+      <c r="E72" s="0" t="s">
         <v>296</v>
       </c>
-      <c r="E72" s="0" t="s">
-        <v>297</v>
-      </c>
       <c r="F72" s="0" t="s">
-        <v>61</v>
+        <v>233</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="J72" s="0" t="s">
         <v>19</v>
@@ -3755,28 +3767,28 @@
         <v>4</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C73" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="D73" s="0" t="s">
         <v>298</v>
       </c>
-      <c r="D73" s="0" t="s">
+      <c r="E73" s="0" t="s">
         <v>299</v>
       </c>
-      <c r="E73" s="0" t="s">
+      <c r="F73" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="G73" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H73" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I73" s="0" t="s">
         <v>300</v>
-      </c>
-      <c r="F73" s="0" t="s">
-        <v>301</v>
-      </c>
-      <c r="G73" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="H73" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="I73" s="0" t="s">
-        <v>302</v>
       </c>
       <c r="J73" s="0" t="s">
         <v>19</v>
@@ -3787,19 +3799,19 @@
         <v>4</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C74" s="0" t="s">
+        <v>301</v>
+      </c>
+      <c r="D74" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="E74" s="0" t="s">
         <v>303</v>
       </c>
-      <c r="D74" s="0" t="s">
-        <v>304</v>
-      </c>
-      <c r="E74" s="0" t="s">
-        <v>305</v>
-      </c>
       <c r="F74" s="0" t="s">
-        <v>225</v>
+        <v>65</v>
       </c>
       <c r="G74" s="0" t="s">
         <v>16</v>
@@ -3808,7 +3820,7 @@
         <v>17</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="J74" s="0" t="s">
         <v>19</v>
@@ -3819,28 +3831,28 @@
         <v>4</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="G75" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="J75" s="0" t="s">
         <v>19</v>
@@ -3851,28 +3863,28 @@
         <v>4</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>312</v>
+        <v>65</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>241</v>
+        <v>16</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="J76" s="0" t="s">
         <v>19</v>
@@ -3883,19 +3895,19 @@
         <v>4</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>66</v>
+        <v>201</v>
       </c>
       <c r="G77" s="0" t="s">
         <v>16</v>
@@ -3904,7 +3916,7 @@
         <v>17</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>140</v>
+        <v>312</v>
       </c>
       <c r="J77" s="0" t="s">
         <v>19</v>
@@ -3915,19 +3927,19 @@
         <v>4</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>319</v>
+        <v>22</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="G78" s="0" t="s">
         <v>16</v>
@@ -3936,7 +3948,7 @@
         <v>17</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>117</v>
+        <v>315</v>
       </c>
       <c r="J78" s="0" t="s">
         <v>19</v>
@@ -3947,28 +3959,28 @@
         <v>4</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>323</v>
+        <v>66</v>
       </c>
       <c r="J79" s="0" t="s">
         <v>19</v>
@@ -3979,28 +3991,28 @@
         <v>4</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>23</v>
+        <v>322</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="H80" s="0" t="s">
         <v>17</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J80" s="0" t="s">
         <v>19</v>
@@ -4011,19 +4023,19 @@
         <v>4</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>23</v>
+        <v>246</v>
       </c>
       <c r="G81" s="0" t="s">
         <v>16</v>
@@ -4032,7 +4044,7 @@
         <v>17</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>327</v>
+        <v>49</v>
       </c>
       <c r="J81" s="0" t="s">
         <v>19</v>
@@ -4043,19 +4055,19 @@
         <v>4</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="G82" s="0" t="s">
         <v>16</v>
@@ -4064,7 +4076,7 @@
         <v>17</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="J82" s="0" t="s">
         <v>19</v>
@@ -4075,28 +4087,28 @@
         <v>4</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C83" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="D83" s="0" t="s">
+        <v>331</v>
+      </c>
+      <c r="E83" s="0" t="s">
+        <v>332</v>
+      </c>
+      <c r="F83" s="0" t="s">
+        <v>333</v>
+      </c>
+      <c r="G83" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="H83" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I83" s="0" t="s">
         <v>334</v>
-      </c>
-      <c r="D83" s="0" t="s">
-        <v>335</v>
-      </c>
-      <c r="E83" s="0" t="s">
-        <v>336</v>
-      </c>
-      <c r="F83" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="G83" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="H83" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="I83" s="0" t="s">
-        <v>337</v>
       </c>
       <c r="J83" s="0" t="s">
         <v>19</v>
@@ -4107,28 +4119,28 @@
         <v>4</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>341</v>
+        <v>65</v>
       </c>
       <c r="G84" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>41</v>
+        <v>163</v>
       </c>
       <c r="J84" s="0" t="s">
         <v>19</v>
@@ -4139,19 +4151,19 @@
         <v>4</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>345</v>
+        <v>167</v>
       </c>
       <c r="G85" s="0" t="s">
         <v>16</v>
@@ -4160,7 +4172,7 @@
         <v>17</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>189</v>
+        <v>144</v>
       </c>
       <c r="J85" s="0" t="s">
         <v>19</v>
@@ -4171,28 +4183,28 @@
         <v>4</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H86" s="0" t="s">
         <v>17</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="J86" s="0" t="s">
         <v>19</v>
@@ -4203,28 +4215,28 @@
         <v>4</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="H87" s="0" t="s">
         <v>17</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="J87" s="0" t="s">
         <v>19</v>
@@ -4235,28 +4247,28 @@
         <v>4</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>357</v>
+        <v>32</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>241</v>
+        <v>16</v>
       </c>
       <c r="H88" s="0" t="s">
         <v>17</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="J88" s="0" t="s">
         <v>19</v>
@@ -4264,63 +4276,63 @@
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>359</v>
+        <v>278</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>225</v>
+        <v>32</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>363</v>
+        <v>16</v>
       </c>
       <c r="H89" s="0" t="s">
         <v>17</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>364</v>
+        <v>88</v>
       </c>
       <c r="J89" s="0" t="s">
-        <v>365</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>359</v>
+        <v>278</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="J90" s="0" t="s">
         <v>19</v>
@@ -4328,31 +4340,31 @@
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B91" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C91" s="0" t="s">
         <v>359</v>
       </c>
-      <c r="C91" s="0" t="s">
-        <v>370</v>
-      </c>
       <c r="D91" s="0" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>19</v>
+        <v>361</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>241</v>
+        <v>16</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>372</v>
+        <v>49</v>
       </c>
       <c r="J91" s="0" t="s">
         <v>19</v>
@@ -4360,22 +4372,22 @@
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>359</v>
+        <v>278</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>180</v>
+        <v>366</v>
       </c>
       <c r="G92" s="0" t="s">
         <v>16</v>
@@ -4384,7 +4396,7 @@
         <v>17</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>376</v>
+        <v>210</v>
       </c>
       <c r="J92" s="0" t="s">
         <v>19</v>
@@ -4392,31 +4404,31 @@
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>359</v>
+        <v>278</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>301</v>
+        <v>75</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H93" s="0" t="s">
         <v>17</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="J93" s="0" t="s">
         <v>19</v>
@@ -4424,31 +4436,31 @@
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>359</v>
+        <v>278</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="H94" s="0" t="s">
         <v>17</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="J94" s="0" t="s">
         <v>19</v>
@@ -4456,31 +4468,31 @@
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>359</v>
+        <v>278</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>233</v>
+        <v>377</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>180</v>
+        <v>378</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>16</v>
+        <v>262</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="J95" s="0" t="s">
         <v>19</v>
@@ -4491,31 +4503,31 @@
         <v>5</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>23</v>
+        <v>246</v>
       </c>
       <c r="G96" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>41</v>
+        <v>384</v>
       </c>
       <c r="J96" s="0" t="s">
-        <v>19</v>
+        <v>385</v>
       </c>
     </row>
     <row r="97">
@@ -4523,28 +4535,28 @@
         <v>5</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="J97" s="0" t="s">
         <v>19</v>
@@ -4555,28 +4567,28 @@
         <v>5</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>396</v>
+        <v>22</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>127</v>
+        <v>378</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="H98" s="0" t="s">
         <v>17</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="J98" s="0" t="s">
         <v>19</v>
@@ -4587,19 +4599,19 @@
         <v>5</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>233</v>
+        <v>394</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>400</v>
+        <v>201</v>
       </c>
       <c r="G99" s="0" t="s">
         <v>16</v>
@@ -4608,7 +4620,7 @@
         <v>17</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="J99" s="0" t="s">
         <v>19</v>
@@ -4619,28 +4631,28 @@
         <v>5</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>225</v>
+        <v>322</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>168</v>
+        <v>399</v>
       </c>
       <c r="J100" s="0" t="s">
         <v>19</v>
@@ -4651,31 +4663,31 @@
         <v>5</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>357</v>
+        <v>65</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>241</v>
+        <v>16</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="J101" s="0" t="s">
-        <v>365</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102">
@@ -4683,252 +4695,252 @@
         <v>5</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="C102" s="0" t="s">
+        <v>404</v>
+      </c>
+      <c r="D102" s="0" t="s">
+        <v>405</v>
+      </c>
+      <c r="E102" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="F102" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="G102" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H102" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I102" s="0" t="s">
+        <v>406</v>
+      </c>
+      <c r="J102" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0">
+        <v>5</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="C103" s="0" t="s">
+        <v>407</v>
+      </c>
+      <c r="D103" s="0" t="s">
+        <v>408</v>
+      </c>
+      <c r="E103" s="0" t="s">
         <v>409</v>
       </c>
-      <c r="D102" s="0" t="s">
+      <c r="F103" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="G103" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H103" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I103" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="J103" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0">
+        <v>5</v>
+      </c>
+      <c r="B104" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="C104" s="0" t="s">
         <v>410</v>
       </c>
-      <c r="E102" s="0" t="s">
+      <c r="D104" s="0" t="s">
         <v>411</v>
       </c>
-      <c r="F102" s="0" t="s">
-        <v>240</v>
-      </c>
-      <c r="G102" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="H102" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="I102" s="0" t="s">
-        <v>372</v>
-      </c>
-      <c r="J102" s="0" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="0" t="s">
+      <c r="E104" s="0" t="s">
         <v>412</v>
       </c>
-      <c r="B103" s="0" t="s">
+      <c r="F104" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="G104" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H104" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I104" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="J104" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0">
+        <v>5</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="C105" s="0" t="s">
         <v>413</v>
       </c>
-      <c r="C103" s="0" t="s">
+      <c r="D105" s="0" t="s">
         <v>414</v>
       </c>
-      <c r="D103" s="0" t="s">
+      <c r="E105" s="0" t="s">
         <v>415</v>
       </c>
-      <c r="E103" s="0" t="s">
-        <v>179</v>
-      </c>
-      <c r="F103" s="0" t="s">
+      <c r="F105" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="G105" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H105" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I105" s="0" t="s">
         <v>416</v>
       </c>
-      <c r="G103" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="H103" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="I103" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="J103" s="0" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="0" t="s">
-        <v>412</v>
-      </c>
-      <c r="B104" s="0" t="s">
-        <v>413</v>
-      </c>
-      <c r="C104" s="0" t="s">
-        <v>414</v>
-      </c>
-      <c r="D104" s="0" t="s">
-        <v>415</v>
-      </c>
-      <c r="E104" s="0" t="s">
-        <v>179</v>
-      </c>
-      <c r="F104" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="G104" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="H104" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="I104" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="J104" s="0" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="0" t="s">
-        <v>412</v>
-      </c>
-      <c r="B105" s="0" t="s">
-        <v>413</v>
-      </c>
-      <c r="C105" s="0" t="s">
+      <c r="J105" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0">
+        <v>5</v>
+      </c>
+      <c r="B106" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="C106" s="0" t="s">
         <v>417</v>
-      </c>
-      <c r="D105" s="0" t="s">
-        <v>418</v>
-      </c>
-      <c r="E105" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="F105" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="G105" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="H105" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="I105" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="J105" s="0" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="0" t="s">
-        <v>412</v>
-      </c>
-      <c r="B106" s="0" t="s">
-        <v>413</v>
-      </c>
-      <c r="C106" s="0" t="s">
-        <v>419</v>
       </c>
       <c r="D106" s="0" t="s">
         <v>418</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>19</v>
+        <v>254</v>
       </c>
       <c r="F106" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="G106" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H106" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I106" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="J106" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0">
+        <v>5</v>
+      </c>
+      <c r="B107" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="C107" s="0" t="s">
         <v>420</v>
       </c>
-      <c r="G106" s="0" t="s">
+      <c r="D107" s="0" t="s">
         <v>421</v>
       </c>
-      <c r="H106" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="I106" s="0" t="s">
+      <c r="E107" s="0" t="s">
         <v>422</v>
       </c>
-      <c r="J106" s="0" t="s">
+      <c r="F107" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="G107" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H107" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I107" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="J107" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0">
+        <v>5</v>
+      </c>
+      <c r="B108" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="C108" s="0" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="0" t="s">
-        <v>412</v>
-      </c>
-      <c r="B107" s="0" t="s">
-        <v>413</v>
-      </c>
-      <c r="C107" s="0" t="s">
+      <c r="D108" s="0" t="s">
         <v>424</v>
       </c>
-      <c r="D107" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E107" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="F107" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="G107" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="H107" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="I107" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="J107" s="0" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="0" t="s">
-        <v>412</v>
-      </c>
-      <c r="B108" s="0" t="s">
-        <v>413</v>
-      </c>
-      <c r="C108" s="0" t="s">
+      <c r="E108" s="0" t="s">
         <v>425</v>
       </c>
-      <c r="D108" s="0" t="s">
+      <c r="F108" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="G108" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="H108" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I108" s="0" t="s">
         <v>426</v>
       </c>
-      <c r="E108" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="F108" s="0" t="s">
+      <c r="J108" s="0" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0">
+        <v>5</v>
+      </c>
+      <c r="B109" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="C109" s="0" t="s">
         <v>427</v>
-      </c>
-      <c r="G108" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="H108" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="I108" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="J108" s="0" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="0" t="s">
-        <v>412</v>
-      </c>
-      <c r="B109" s="0" t="s">
-        <v>413</v>
-      </c>
-      <c r="C109" s="0" t="s">
-        <v>269</v>
       </c>
       <c r="D109" s="0" t="s">
         <v>428</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>271</v>
+        <v>429</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>15</v>
+        <v>261</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>16</v>
+        <v>262</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>272</v>
+        <v>391</v>
       </c>
       <c r="J109" s="0" t="s">
         <v>19</v>
@@ -4936,31 +4948,31 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>429</v>
+        <v>120</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>430</v>
+        <v>121</v>
       </c>
       <c r="E110" s="0" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>264</v>
+        <v>15</v>
       </c>
       <c r="G110" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="J110" s="0" t="s">
         <v>19</v>
@@ -4968,31 +4980,31 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>432</v>
+        <v>21</v>
       </c>
       <c r="E111" s="0" t="s">
-        <v>433</v>
+        <v>22</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="G111" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="J111" s="0" t="s">
         <v>19</v>
@@ -5000,19 +5012,19 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>283</v>
+        <v>433</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>284</v>
+        <v>26</v>
       </c>
       <c r="E112" s="0" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F112" s="0" t="s">
         <v>15</v>
@@ -5021,10 +5033,10 @@
         <v>16</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="J112" s="0" t="s">
         <v>19</v>
@@ -5032,10 +5044,10 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C113" s="0" t="s">
         <v>434</v>
@@ -5044,16 +5056,16 @@
         <v>435</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>427</v>
+        <v>246</v>
       </c>
       <c r="G113" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I113" s="0" t="s">
         <v>19</v>
@@ -5064,31 +5076,31 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>434</v>
+        <v>290</v>
       </c>
       <c r="D114" s="0" t="s">
         <v>436</v>
       </c>
       <c r="E114" s="0" t="s">
-        <v>19</v>
+        <v>292</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>427</v>
+        <v>15</v>
       </c>
       <c r="G114" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>19</v>
+        <v>293</v>
       </c>
       <c r="J114" s="0" t="s">
         <v>19</v>
@@ -5096,28 +5108,28 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C115" s="0" t="s">
         <v>437</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>266</v>
+        <v>438</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="G115" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I115" s="0" t="s">
         <v>19</v>
@@ -5128,31 +5140,31 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>438</v>
+        <v>62</v>
       </c>
       <c r="D116" s="0" t="s">
         <v>439</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>440</v>
+        <v>64</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>441</v>
+        <v>66</v>
       </c>
       <c r="J116" s="0" t="s">
         <v>19</v>
@@ -5160,31 +5172,31 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>442</v>
+        <v>304</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>443</v>
+        <v>305</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="J117" s="0" t="s">
         <v>19</v>
@@ -5192,22 +5204,22 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>317</v>
+        <v>440</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>318</v>
+        <v>441</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>319</v>
+        <v>22</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>144</v>
+        <v>246</v>
       </c>
       <c r="G118" s="0" t="s">
         <v>16</v>
@@ -5216,7 +5228,7 @@
         <v>17</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="J118" s="0" t="s">
         <v>19</v>
@@ -5224,28 +5236,28 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>15</v>
+        <v>246</v>
       </c>
       <c r="G119" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>19</v>
@@ -5256,28 +5268,28 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>447</v>
+        <v>287</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>163</v>
+        <v>285</v>
       </c>
       <c r="G120" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I120" s="0" t="s">
         <v>19</v>
@@ -5288,31 +5300,31 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>448</v>
+        <v>67</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E121" s="0" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="J121" s="0" t="s">
         <v>19</v>
@@ -5320,28 +5332,28 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>68</v>
+        <v>445</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I122" s="0" t="s">
         <v>19</v>
@@ -5352,31 +5364,31 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>231</v>
+        <v>338</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>232</v>
+        <v>339</v>
       </c>
       <c r="E123" s="0" t="s">
-        <v>233</v>
+        <v>340</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>15</v>
+        <v>167</v>
       </c>
       <c r="G123" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="J123" s="0" t="s">
         <v>19</v>
@@ -5384,19 +5396,19 @@
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>266</v>
+        <v>448</v>
       </c>
       <c r="E124" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F124" s="0" t="s">
         <v>15</v>
@@ -5405,7 +5417,7 @@
         <v>16</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I124" s="0" t="s">
         <v>19</v>
@@ -5416,31 +5428,31 @@
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>245</v>
+        <v>449</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>246</v>
+        <v>450</v>
       </c>
       <c r="E125" s="0" t="s">
-        <v>247</v>
+        <v>22</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>248</v>
+        <v>451</v>
       </c>
       <c r="G125" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J125" s="0" t="s">
         <v>19</v>
@@ -5448,31 +5460,31 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>89</v>
+        <v>452</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>90</v>
+        <v>453</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="J126" s="0" t="s">
         <v>19</v>
@@ -5480,31 +5492,31 @@
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>152</v>
+        <v>93</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>153</v>
+        <v>454</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>154</v>
+        <v>22</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="G127" s="0" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="J127" s="0" t="s">
         <v>19</v>
@@ -5512,31 +5524,31 @@
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>452</v>
+        <v>252</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>453</v>
+        <v>253</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>19</v>
+        <v>254</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>454</v>
+        <v>15</v>
       </c>
       <c r="G128" s="0" t="s">
         <v>16</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>19</v>
+        <v>190</v>
       </c>
       <c r="J128" s="0" t="s">
         <v>19</v>
@@ -5544,38 +5556,198 @@
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>92</v>
+        <v>455</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>93</v>
+        <v>287</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="G129" s="0" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J129" s="0" t="s">
         <v>19</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="B130" s="0" t="s">
+        <v>431</v>
+      </c>
+      <c r="C130" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="D130" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="E130" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="F130" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="G130" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H130" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I130" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="J130" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="B131" s="0" t="s">
+        <v>431</v>
+      </c>
+      <c r="C131" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="D131" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="E131" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="F131" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="G131" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H131" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I131" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="J131" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="B132" s="0" t="s">
+        <v>431</v>
+      </c>
+      <c r="C132" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="D132" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="E132" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="F132" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="G132" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H132" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I132" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="J132" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="B133" s="0" t="s">
+        <v>431</v>
+      </c>
+      <c r="C133" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="D133" s="0" t="s">
+        <v>457</v>
+      </c>
+      <c r="E133" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F133" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="G133" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H133" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I133" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="J133" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="B134" s="0" t="s">
+        <v>431</v>
+      </c>
+      <c r="C134" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="D134" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="E134" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="F134" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="G134" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H134" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I134" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="J134" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J129"/>
+  <autoFilter ref="A1:J134"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/Excel/liste_complete.xlsx
+++ b/Excel/liste_complete.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
   <si>
     <t>GROUPE</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>Nafyad</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Éthiopie</t>
@@ -947,9 +950,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="22" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -977,34 +979,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1021,23 +1023,23 @@
       <c r="D2" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="1">
-        <v>36322</v>
+      <c r="E2" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="1">
-        <v>45923</v>
-      </c>
-      <c r="J2" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -1048,28 +1050,28 @@
         <v>10</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="1">
-        <v>38760</v>
+        <v>18</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1">
-        <v>45939</v>
-      </c>
-      <c r="J3" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -1080,28 +1082,28 @@
         <v>10</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="1">
-        <v>35469</v>
+        <v>21</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="1">
-        <v>45938</v>
-      </c>
-      <c r="J4" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -1112,28 +1114,28 @@
         <v>10</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="1">
-        <v>39050</v>
+        <v>26</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="1">
-        <v>45967</v>
-      </c>
-      <c r="J5" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -1144,28 +1146,28 @@
         <v>10</v>
       </c>
       <c r="C6" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="1">
-        <v>44633</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>26</v>
-      </c>
       <c r="G6" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="1">
-        <v>45967</v>
-      </c>
-      <c r="J6" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -1176,28 +1178,28 @@
         <v>10</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="1">
-        <v>28876</v>
+        <v>31</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="1">
-        <v>44934</v>
-      </c>
-      <c r="J7" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I7" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1208,28 +1210,28 @@
         <v>10</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="1">
-        <v>2</v>
+        <v>34</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="1">
-        <v>45981</v>
-      </c>
-      <c r="J8" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I8" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -1240,28 +1242,28 @@
         <v>10</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="1">
-        <v>21680</v>
+        <v>37</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="1">
-        <v>45713</v>
-      </c>
-      <c r="J9" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I9" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -1272,28 +1274,28 @@
         <v>10</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="1">
-        <v>33421</v>
+        <v>39</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="1">
-        <v>45937</v>
-      </c>
-      <c r="J10" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I10" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -1304,28 +1306,28 @@
         <v>10</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="1">
-        <v>38947</v>
+        <v>41</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="1">
-        <v>45939</v>
-      </c>
-      <c r="J11" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I11" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -1336,28 +1338,28 @@
         <v>10</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="1">
-        <v>19370</v>
+        <v>44</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="1">
-        <v>45939</v>
-      </c>
-      <c r="J12" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I12" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -1368,28 +1370,28 @@
         <v>10</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="1">
-        <v>31088</v>
+        <v>48</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="1">
-        <v>45967</v>
-      </c>
-      <c r="J13" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I13" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -1400,28 +1402,28 @@
         <v>10</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="1">
-        <v>23048</v>
+        <v>50</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="1">
-        <v>45545</v>
-      </c>
-      <c r="J14" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I14" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -1432,28 +1434,28 @@
         <v>10</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="1">
-        <v>35591</v>
+        <v>52</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="1">
-        <v>45937</v>
-      </c>
-      <c r="J15" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I15" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -1464,316 +1466,316 @@
         <v>10</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" s="1">
-        <v>32278</v>
+        <v>54</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="1">
-        <v>45925</v>
-      </c>
-      <c r="J16" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I16" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="1">
-        <v>23377</v>
+        <v>59</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="1">
-        <v>45554</v>
-      </c>
-      <c r="J17" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I17" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="1">
-        <v>2</v>
+        <v>62</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="1">
-        <v>2</v>
-      </c>
-      <c r="J18" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I18" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" s="1">
-        <v>31778</v>
+        <v>65</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="1">
-        <v>45925</v>
-      </c>
-      <c r="J19" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I19" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="E20" s="1">
-        <v>35935</v>
+        <v>67</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="1">
-        <v>45965</v>
-      </c>
-      <c r="J20" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I20" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" s="1">
-        <v>33884</v>
+        <v>70</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" s="1">
-        <v>45736</v>
-      </c>
-      <c r="J21" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I21" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C22" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" s="1">
-        <v>22184</v>
-      </c>
-      <c r="F22" s="0" t="s">
-        <v>70</v>
-      </c>
       <c r="G22" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" s="1">
-        <v>45196</v>
-      </c>
-      <c r="J22" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I22" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="E23" s="1">
-        <v>32725</v>
+        <v>75</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I23" s="1">
-        <v>45916</v>
-      </c>
-      <c r="J23" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I23" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D24" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="1">
-        <v>31252</v>
-      </c>
-      <c r="F24" s="0" t="s">
-        <v>75</v>
-      </c>
       <c r="G24" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="1">
-        <v>45916</v>
-      </c>
-      <c r="J24" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I24" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="E25" s="1">
-        <v>30670</v>
+        <v>79</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="1">
-        <v>45903</v>
-      </c>
-      <c r="J25" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I25" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="26">
@@ -1781,31 +1783,31 @@
         <v>2</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="E26" s="1">
-        <v>30317</v>
+        <v>82</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="1">
-        <v>45545</v>
-      </c>
-      <c r="J26" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I26" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="27">
@@ -1813,31 +1815,31 @@
         <v>2</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="E27" s="1">
-        <v>2</v>
+        <v>84</v>
+      </c>
+      <c r="E27" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I27" s="1">
-        <v>45901</v>
-      </c>
-      <c r="J27" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I27" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="28">
@@ -1845,31 +1847,31 @@
         <v>2</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="E28" s="1">
-        <v>36757</v>
+        <v>86</v>
+      </c>
+      <c r="E28" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" s="1">
-        <v>45923</v>
-      </c>
-      <c r="J28" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I28" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="29">
@@ -1877,31 +1879,31 @@
         <v>2</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="E29" s="1">
-        <v>29498</v>
+        <v>88</v>
+      </c>
+      <c r="E29" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I29" s="1">
-        <v>45636</v>
-      </c>
-      <c r="J29" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I29" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J29" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="30">
@@ -1909,31 +1911,31 @@
         <v>2</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="E30" s="1">
-        <v>35522</v>
+        <v>90</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="1">
-        <v>45210</v>
-      </c>
-      <c r="J30" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I30" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="31">
@@ -1941,31 +1943,31 @@
         <v>2</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="E31" s="1">
-        <v>2</v>
+        <v>92</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I31" s="1">
-        <v>45916</v>
-      </c>
-      <c r="J31" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I31" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="32">
@@ -1973,31 +1975,31 @@
         <v>2</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="E32" s="1">
-        <v>29262</v>
+        <v>94</v>
+      </c>
+      <c r="E32" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I32" s="1">
-        <v>45967</v>
-      </c>
-      <c r="J32" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I32" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J32" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="33">
@@ -2005,31 +2007,31 @@
         <v>2</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="E33" s="1">
-        <v>29361</v>
+        <v>70</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="1">
-        <v>45968</v>
-      </c>
-      <c r="J33" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I33" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="34">
@@ -2037,31 +2039,31 @@
         <v>2</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="E34" s="1">
-        <v>31650</v>
+        <v>96</v>
+      </c>
+      <c r="E34" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="1">
-        <v>44840</v>
-      </c>
-      <c r="J34" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I34" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="35">
@@ -2069,31 +2071,31 @@
         <v>2</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="E35" s="1">
-        <v>35430</v>
+        <v>98</v>
+      </c>
+      <c r="E35" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="1">
-        <v>45925</v>
-      </c>
-      <c r="J35" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I35" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="36">
@@ -2101,31 +2103,31 @@
         <v>2</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="E36" s="1">
-        <v>28688</v>
+        <v>100</v>
+      </c>
+      <c r="E36" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I36" s="1">
-        <v>45916</v>
-      </c>
-      <c r="J36" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I36" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="37">
@@ -2133,31 +2135,31 @@
         <v>2</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="E37" s="1">
-        <v>25720</v>
+        <v>103</v>
+      </c>
+      <c r="E37" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="1">
-        <v>44880</v>
-      </c>
-      <c r="J37" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I37" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J37" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="38">
@@ -2165,31 +2167,31 @@
         <v>2</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="E38" s="1">
-        <v>18937</v>
+        <v>106</v>
+      </c>
+      <c r="E38" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" s="1">
-        <v>45910</v>
-      </c>
-      <c r="J38" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I38" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="39">
@@ -2197,31 +2199,31 @@
         <v>2</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>107</v>
-      </c>
-      <c r="E39" s="1">
-        <v>30866</v>
+        <v>108</v>
+      </c>
+      <c r="E39" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I39" s="1">
-        <v>45901</v>
-      </c>
-      <c r="J39" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I39" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="40">
@@ -2229,31 +2231,31 @@
         <v>2</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="E40" s="1">
-        <v>38176</v>
+        <v>111</v>
+      </c>
+      <c r="E40" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" s="1">
-        <v>45903</v>
-      </c>
-      <c r="J40" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I40" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="41">
@@ -2261,31 +2263,31 @@
         <v>2</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="E41" s="1">
-        <v>29711</v>
+        <v>113</v>
+      </c>
+      <c r="E41" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I41" s="1">
-        <v>45916</v>
-      </c>
-      <c r="J41" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I41" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J41" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="42">
@@ -2293,31 +2295,31 @@
         <v>2</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>114</v>
-      </c>
-      <c r="E42" s="1">
-        <v>38226</v>
+        <v>115</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I42" s="1">
-        <v>45916</v>
-      </c>
-      <c r="J42" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I42" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="43">
@@ -2325,31 +2327,31 @@
         <v>2</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>116</v>
-      </c>
-      <c r="E43" s="1">
-        <v>30991</v>
+        <v>117</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I43" s="1">
-        <v>45440</v>
-      </c>
-      <c r="J43" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I43" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J43" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="44">
@@ -2357,31 +2359,31 @@
         <v>2</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="E44" s="1">
-        <v>35555</v>
+        <v>119</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I44" s="1">
-        <v>45911</v>
-      </c>
-      <c r="J44" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I44" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J44" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="45">
@@ -2389,31 +2391,31 @@
         <v>3</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="E45" s="1">
-        <v>27488</v>
+        <v>122</v>
+      </c>
+      <c r="E45" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I45" s="1">
-        <v>45552</v>
-      </c>
-      <c r="J45" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I45" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="46">
@@ -2421,31 +2423,31 @@
         <v>3</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="E46" s="1">
-        <v>35565</v>
+        <v>125</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I46" s="1">
-        <v>45536</v>
-      </c>
-      <c r="J46" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I46" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="47">
@@ -2453,31 +2455,31 @@
         <v>3</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="E47" s="1">
-        <v>27210</v>
+        <v>127</v>
+      </c>
+      <c r="E47" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I47" s="1">
-        <v>45694</v>
-      </c>
-      <c r="J47" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I47" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J47" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="48">
@@ -2485,31 +2487,31 @@
         <v>3</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>128</v>
-      </c>
-      <c r="E48" s="1">
-        <v>30317</v>
+        <v>129</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I48" s="1">
-        <v>45009</v>
-      </c>
-      <c r="J48" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I48" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J48" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="49">
@@ -2517,31 +2519,31 @@
         <v>3</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="E49" s="1">
-        <v>29137</v>
+        <v>132</v>
+      </c>
+      <c r="E49" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I49" s="1">
-        <v>45434</v>
-      </c>
-      <c r="J49" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I49" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J49" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="50">
@@ -2549,31 +2551,31 @@
         <v>3</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="E50" s="1">
-        <v>26685</v>
+        <v>134</v>
+      </c>
+      <c r="E50" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I50" s="1">
-        <v>45566</v>
-      </c>
-      <c r="J50" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I50" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="51">
@@ -2581,31 +2583,31 @@
         <v>3</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>135</v>
-      </c>
-      <c r="E51" s="1">
-        <v>32089</v>
+        <v>136</v>
+      </c>
+      <c r="E51" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I51" s="1">
-        <v>45694</v>
-      </c>
-      <c r="J51" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I51" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J51" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="52">
@@ -2613,31 +2615,31 @@
         <v>3</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="E52" s="1">
-        <v>30993</v>
+        <v>138</v>
+      </c>
+      <c r="E52" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I52" s="1">
-        <v>45771</v>
-      </c>
-      <c r="J52" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I52" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J52" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="53">
@@ -2645,31 +2647,31 @@
         <v>3</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="E53" s="1">
-        <v>31243</v>
+        <v>140</v>
+      </c>
+      <c r="E53" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I53" s="1">
-        <v>45547</v>
-      </c>
-      <c r="J53" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I53" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="54">
@@ -2677,31 +2679,31 @@
         <v>3</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>141</v>
-      </c>
-      <c r="E54" s="1">
-        <v>36509</v>
+        <v>142</v>
+      </c>
+      <c r="E54" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I54" s="1">
-        <v>45923</v>
-      </c>
-      <c r="J54" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I54" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="55">
@@ -2709,31 +2711,31 @@
         <v>3</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>143</v>
-      </c>
-      <c r="E55" s="1">
-        <v>33008</v>
+        <v>144</v>
+      </c>
+      <c r="E55" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I55" s="1">
-        <v>45669</v>
-      </c>
-      <c r="J55" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I55" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J55" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="56">
@@ -2741,31 +2743,31 @@
         <v>3</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="E56" s="1">
-        <v>34847</v>
+        <v>147</v>
+      </c>
+      <c r="E56" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I56" s="1">
-        <v>45170</v>
-      </c>
-      <c r="J56" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I56" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J56" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="57">
@@ -2773,31 +2775,31 @@
         <v>3</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="E57" s="1">
-        <v>28144</v>
+        <v>150</v>
+      </c>
+      <c r="E57" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I57" s="1">
-        <v>45901</v>
-      </c>
-      <c r="J57" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I57" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="58">
@@ -2805,31 +2807,31 @@
         <v>3</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="E58" s="1">
-        <v>33332</v>
+        <v>152</v>
+      </c>
+      <c r="E58" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I58" s="1">
-        <v>45678</v>
-      </c>
-      <c r="J58" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I58" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="59">
@@ -2837,31 +2839,31 @@
         <v>3</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="E59" s="1">
-        <v>30234</v>
+        <v>155</v>
+      </c>
+      <c r="E59" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I59" s="1">
-        <v>45249</v>
-      </c>
-      <c r="J59" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I59" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J59" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="60">
@@ -2869,31 +2871,31 @@
         <v>3</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="E60" s="1">
-        <v>31836</v>
+        <v>158</v>
+      </c>
+      <c r="E60" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I60" s="1">
-        <v>45617</v>
-      </c>
-      <c r="J60" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I60" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J60" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="61">
@@ -2901,31 +2903,31 @@
         <v>3</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="E61" s="1">
-        <v>34335</v>
+        <v>160</v>
+      </c>
+      <c r="E61" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I61" s="1">
-        <v>45552</v>
-      </c>
-      <c r="J61" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I61" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J61" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="62">
@@ -2933,31 +2935,31 @@
         <v>3</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>161</v>
-      </c>
-      <c r="E62" s="1">
-        <v>26206</v>
+        <v>162</v>
+      </c>
+      <c r="E62" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I62" s="1">
-        <v>45545</v>
-      </c>
-      <c r="J62" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I62" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J62" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="63">
@@ -2965,31 +2967,31 @@
         <v>3</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>163</v>
-      </c>
-      <c r="E63" s="1">
-        <v>25987</v>
+        <v>164</v>
+      </c>
+      <c r="E63" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I63" s="1">
-        <v>45901</v>
-      </c>
-      <c r="J63" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I63" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J63" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="64">
@@ -2997,31 +2999,31 @@
         <v>3</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>167</v>
-      </c>
-      <c r="E64" s="1">
-        <v>30926</v>
+        <v>168</v>
+      </c>
+      <c r="E64" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I64" s="1">
-        <v>45552</v>
-      </c>
-      <c r="J64" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I64" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J64" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="65">
@@ -3029,31 +3031,31 @@
         <v>3</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>169</v>
-      </c>
-      <c r="E65" s="1">
-        <v>35796</v>
+        <v>170</v>
+      </c>
+      <c r="E65" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I65" s="1">
-        <v>45545</v>
-      </c>
-      <c r="J65" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I65" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J65" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="66">
@@ -3061,31 +3063,31 @@
         <v>3</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>172</v>
-      </c>
-      <c r="E66" s="1">
-        <v>20699</v>
+        <v>173</v>
+      </c>
+      <c r="E66" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I66" s="1">
-        <v>45246</v>
-      </c>
-      <c r="J66" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I66" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J66" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="67">
@@ -3093,31 +3095,31 @@
         <v>3</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="E67" s="1">
-        <v>29037</v>
+        <v>176</v>
+      </c>
+      <c r="E67" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I67" s="1">
-        <v>45536</v>
-      </c>
-      <c r="J67" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I67" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="68">
@@ -3125,31 +3127,31 @@
         <v>4</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>178</v>
-      </c>
-      <c r="E68" s="1">
-        <v>33473</v>
+        <v>179</v>
+      </c>
+      <c r="E68" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I68" s="1">
-        <v>45981</v>
-      </c>
-      <c r="J68" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I68" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J68" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="69">
@@ -3157,31 +3159,31 @@
         <v>4</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>180</v>
-      </c>
-      <c r="E69" s="1">
-        <v>28855</v>
+        <v>181</v>
+      </c>
+      <c r="E69" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I69" s="1">
-        <v>45901</v>
-      </c>
-      <c r="J69" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I69" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J69" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="70">
@@ -3189,31 +3191,31 @@
         <v>4</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>183</v>
-      </c>
-      <c r="E70" s="1">
-        <v>34172</v>
+        <v>184</v>
+      </c>
+      <c r="E70" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I70" s="1">
-        <v>45413</v>
-      </c>
-      <c r="J70" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I70" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J70" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="71">
@@ -3221,31 +3223,31 @@
         <v>4</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>185</v>
-      </c>
-      <c r="E71" s="1">
-        <v>36258</v>
+        <v>186</v>
+      </c>
+      <c r="E71" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I71" s="1">
-        <v>45621</v>
-      </c>
-      <c r="J71" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I71" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J71" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="72">
@@ -3253,31 +3255,31 @@
         <v>4</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>187</v>
-      </c>
-      <c r="E72" s="1">
-        <v>33217</v>
+        <v>188</v>
+      </c>
+      <c r="E72" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I72" s="1">
-        <v>45925</v>
-      </c>
-      <c r="J72" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I72" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J72" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="73">
@@ -3285,31 +3287,31 @@
         <v>4</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>189</v>
-      </c>
-      <c r="E73" s="1">
-        <v>33695</v>
+        <v>190</v>
+      </c>
+      <c r="E73" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I73" s="1">
-        <v>44562</v>
-      </c>
-      <c r="J73" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I73" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J73" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="74">
@@ -3317,31 +3319,31 @@
         <v>4</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>191</v>
-      </c>
-      <c r="E74" s="1">
-        <v>24778</v>
+        <v>192</v>
+      </c>
+      <c r="E74" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I74" s="1">
-        <v>45923</v>
-      </c>
-      <c r="J74" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I74" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J74" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="75">
@@ -3349,31 +3351,31 @@
         <v>4</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="E75" s="1">
-        <v>2</v>
+        <v>194</v>
+      </c>
+      <c r="E75" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I75" s="1">
-        <v>45916</v>
-      </c>
-      <c r="J75" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I75" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J75" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="76">
@@ -3381,31 +3383,31 @@
         <v>4</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>195</v>
-      </c>
-      <c r="E76" s="1">
-        <v>34699</v>
+        <v>196</v>
+      </c>
+      <c r="E76" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I76" s="1">
-        <v>45621</v>
-      </c>
-      <c r="J76" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I76" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J76" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="77">
@@ -3413,31 +3415,31 @@
         <v>4</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>197</v>
-      </c>
-      <c r="E77" s="1">
-        <v>21551</v>
+        <v>198</v>
+      </c>
+      <c r="E77" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I77" s="1">
-        <v>44819</v>
-      </c>
-      <c r="J77" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I77" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J77" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="78">
@@ -3445,31 +3447,31 @@
         <v>4</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>199</v>
-      </c>
-      <c r="E78" s="1">
-        <v>2</v>
+        <v>200</v>
+      </c>
+      <c r="E78" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I78" s="1">
-        <v>45987</v>
-      </c>
-      <c r="J78" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I78" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J78" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="79">
@@ -3477,31 +3479,31 @@
         <v>4</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>201</v>
-      </c>
-      <c r="E79" s="1">
-        <v>36219</v>
+        <v>202</v>
+      </c>
+      <c r="E79" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I79" s="1">
-        <v>45939</v>
-      </c>
-      <c r="J79" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I79" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J79" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="80">
@@ -3509,31 +3511,31 @@
         <v>4</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="E80" s="1">
-        <v>28275</v>
+        <v>204</v>
+      </c>
+      <c r="E80" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I80" s="1">
-        <v>44691</v>
-      </c>
-      <c r="J80" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I80" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J80" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="81">
@@ -3541,31 +3543,31 @@
         <v>4</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="E81" s="1">
-        <v>30159</v>
+        <v>207</v>
+      </c>
+      <c r="E81" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I81" s="1">
-        <v>45916</v>
-      </c>
-      <c r="J81" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I81" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="82">
@@ -3573,31 +3575,31 @@
         <v>4</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>208</v>
-      </c>
-      <c r="E82" s="1">
-        <v>36955</v>
+        <v>209</v>
+      </c>
+      <c r="E82" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I82" s="1">
-        <v>45916</v>
-      </c>
-      <c r="J82" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I82" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J82" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="83">
@@ -3605,31 +3607,31 @@
         <v>4</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="E83" s="1">
-        <v>37640</v>
+        <v>211</v>
+      </c>
+      <c r="E83" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I83" s="1">
-        <v>45918</v>
-      </c>
-      <c r="J83" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I83" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J83" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="84">
@@ -3637,31 +3639,31 @@
         <v>4</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="E84" s="1">
-        <v>32323</v>
+        <v>214</v>
+      </c>
+      <c r="E84" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I84" s="1">
-        <v>45910</v>
-      </c>
-      <c r="J84" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I84" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J84" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="85">
@@ -3669,31 +3671,31 @@
         <v>4</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>215</v>
-      </c>
-      <c r="E85" s="1">
-        <v>37483</v>
+        <v>216</v>
+      </c>
+      <c r="E85" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I85" s="1">
-        <v>45968</v>
-      </c>
-      <c r="J85" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I85" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J85" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="86">
@@ -3701,31 +3703,31 @@
         <v>4</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>217</v>
-      </c>
-      <c r="E86" s="1">
-        <v>28932</v>
+        <v>218</v>
+      </c>
+      <c r="E86" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I86" s="1">
-        <v>45986</v>
-      </c>
-      <c r="J86" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I86" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J86" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="87">
@@ -3733,31 +3735,31 @@
         <v>4</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="E87" s="1">
-        <v>43249</v>
+        <v>220</v>
+      </c>
+      <c r="E87" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I87" s="1">
-        <v>45975</v>
-      </c>
-      <c r="J87" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I87" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J87" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="88">
@@ -3765,31 +3767,31 @@
         <v>4</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>221</v>
-      </c>
-      <c r="E88" s="1">
-        <v>34545</v>
+        <v>222</v>
+      </c>
+      <c r="E88" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I88" s="1">
-        <v>45975</v>
-      </c>
-      <c r="J88" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I88" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J88" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="89">
@@ -3797,31 +3799,31 @@
         <v>4</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>223</v>
-      </c>
-      <c r="E89" s="1">
-        <v>29561</v>
+        <v>224</v>
+      </c>
+      <c r="E89" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I89" s="1">
-        <v>45981</v>
-      </c>
-      <c r="J89" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I89" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J89" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="90">
@@ -3829,31 +3831,31 @@
         <v>4</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>225</v>
-      </c>
-      <c r="E90" s="1">
-        <v>31760</v>
+        <v>226</v>
+      </c>
+      <c r="E90" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I90" s="1">
-        <v>45445</v>
-      </c>
-      <c r="J90" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I90" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J90" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="91">
@@ -3861,31 +3863,31 @@
         <v>4</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>227</v>
-      </c>
-      <c r="E91" s="1">
-        <v>33921</v>
+        <v>228</v>
+      </c>
+      <c r="E91" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I91" s="1">
-        <v>45916</v>
-      </c>
-      <c r="J91" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I91" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J91" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="92">
@@ -3893,31 +3895,31 @@
         <v>4</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>230</v>
-      </c>
-      <c r="E92" s="1">
-        <v>35384</v>
+        <v>231</v>
+      </c>
+      <c r="E92" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I92" s="1">
-        <v>45566</v>
-      </c>
-      <c r="J92" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I92" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J92" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="93">
@@ -3925,31 +3927,31 @@
         <v>4</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>233</v>
-      </c>
-      <c r="E93" s="1">
-        <v>30580</v>
+        <v>234</v>
+      </c>
+      <c r="E93" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I93" s="1">
-        <v>44481</v>
-      </c>
-      <c r="J93" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I93" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J93" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="94">
@@ -3957,31 +3959,31 @@
         <v>4</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>235</v>
-      </c>
-      <c r="E94" s="1">
-        <v>23021</v>
+        <v>236</v>
+      </c>
+      <c r="E94" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I94" s="1">
-        <v>42381</v>
-      </c>
-      <c r="J94" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I94" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J94" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="95">
@@ -3989,31 +3991,31 @@
         <v>4</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>237</v>
-      </c>
-      <c r="E95" s="1">
-        <v>34840</v>
+        <v>238</v>
+      </c>
+      <c r="E95" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I95" s="1">
-        <v>45722</v>
-      </c>
-      <c r="J95" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I95" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J95" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="96">
@@ -4021,31 +4023,31 @@
         <v>5</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="E96" s="1">
-        <v>26978</v>
+        <v>242</v>
+      </c>
+      <c r="E96" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I96" s="1">
-        <v>44810</v>
-      </c>
-      <c r="J96" s="1">
-        <v>45992</v>
+        <v>16</v>
+      </c>
+      <c r="I96" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J96" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="97">
@@ -4053,31 +4055,31 @@
         <v>5</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>243</v>
-      </c>
-      <c r="E97" s="1">
-        <v>38905</v>
+        <v>244</v>
+      </c>
+      <c r="E97" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I97" s="1">
-        <v>45911</v>
-      </c>
-      <c r="J97" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I97" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J97" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="98">
@@ -4085,31 +4087,31 @@
         <v>5</v>
       </c>
       <c r="B98" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="C98" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="D98" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="E98" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F98" s="0" t="s">
         <v>239</v>
       </c>
-      <c r="C98" s="0" t="s">
-        <v>244</v>
-      </c>
-      <c r="D98" s="0" t="s">
-        <v>245</v>
-      </c>
-      <c r="E98" s="1">
-        <v>2</v>
-      </c>
-      <c r="F98" s="0" t="s">
-        <v>238</v>
-      </c>
       <c r="G98" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I98" s="1">
-        <v>45673</v>
-      </c>
-      <c r="J98" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I98" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J98" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="99">
@@ -4117,31 +4119,31 @@
         <v>5</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>247</v>
-      </c>
-      <c r="E99" s="1">
-        <v>34630</v>
+        <v>248</v>
+      </c>
+      <c r="E99" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I99" s="1">
-        <v>45077</v>
-      </c>
-      <c r="J99" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I99" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J99" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="100">
@@ -4149,31 +4151,31 @@
         <v>5</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>249</v>
-      </c>
-      <c r="E100" s="1">
-        <v>28909</v>
+        <v>250</v>
+      </c>
+      <c r="E100" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I100" s="1">
-        <v>45239</v>
-      </c>
-      <c r="J100" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I100" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J100" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="101">
@@ -4181,31 +4183,31 @@
         <v>5</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>251</v>
-      </c>
-      <c r="E101" s="1">
-        <v>33653</v>
+        <v>252</v>
+      </c>
+      <c r="E101" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I101" s="1">
-        <v>45189</v>
-      </c>
-      <c r="J101" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I101" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J101" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="102">
@@ -4213,31 +4215,31 @@
         <v>5</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="E102" s="1">
-        <v>34335</v>
+        <v>254</v>
+      </c>
+      <c r="E102" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I102" s="1">
-        <v>45689</v>
-      </c>
-      <c r="J102" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I102" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J102" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="103">
@@ -4245,31 +4247,31 @@
         <v>5</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>255</v>
-      </c>
-      <c r="E103" s="1">
-        <v>33049</v>
+        <v>256</v>
+      </c>
+      <c r="E103" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I103" s="1">
-        <v>45916</v>
-      </c>
-      <c r="J103" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I103" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J103" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="104">
@@ -4277,31 +4279,31 @@
         <v>5</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>257</v>
-      </c>
-      <c r="E104" s="1">
-        <v>34459</v>
+        <v>258</v>
+      </c>
+      <c r="E104" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I104" s="1">
-        <v>45925</v>
-      </c>
-      <c r="J104" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I104" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J104" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="105">
@@ -4309,31 +4311,31 @@
         <v>5</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>259</v>
-      </c>
-      <c r="E105" s="1">
-        <v>33133</v>
+        <v>260</v>
+      </c>
+      <c r="E105" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I105" s="1">
-        <v>43642</v>
-      </c>
-      <c r="J105" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I105" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J105" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="106">
@@ -4341,31 +4343,31 @@
         <v>5</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>261</v>
-      </c>
-      <c r="E106" s="1">
-        <v>34335</v>
+        <v>262</v>
+      </c>
+      <c r="E106" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I106" s="1">
-        <v>45554</v>
-      </c>
-      <c r="J106" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I106" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J106" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="107">
@@ -4373,31 +4375,31 @@
         <v>5</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>264</v>
-      </c>
-      <c r="E107" s="1">
-        <v>27776</v>
+        <v>265</v>
+      </c>
+      <c r="E107" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I107" s="1">
-        <v>45552</v>
-      </c>
-      <c r="J107" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I107" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J107" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="108">
@@ -4405,31 +4407,31 @@
         <v>5</v>
       </c>
       <c r="B108" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="C108" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="D108" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="E108" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F108" s="0" t="s">
         <v>239</v>
       </c>
-      <c r="C108" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="D108" s="0" t="s">
-        <v>266</v>
-      </c>
-      <c r="E108" s="1">
-        <v>31561</v>
-      </c>
-      <c r="F108" s="0" t="s">
-        <v>238</v>
-      </c>
       <c r="G108" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I108" s="1">
-        <v>45783</v>
-      </c>
-      <c r="J108" s="1">
-        <v>45992</v>
+        <v>24</v>
+      </c>
+      <c r="I108" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J108" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="109">
@@ -4437,831 +4439,831 @@
         <v>5</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>268</v>
-      </c>
-      <c r="E109" s="1">
-        <v>32692</v>
+        <v>269</v>
+      </c>
+      <c r="E109" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I109" s="1">
-        <v>45673</v>
-      </c>
-      <c r="J109" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I109" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J109" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="E110" s="1">
-        <v>30317</v>
+        <v>82</v>
+      </c>
+      <c r="E110" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I110" s="1">
-        <v>45545</v>
-      </c>
-      <c r="J110" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I110" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J110" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="E111" s="1">
-        <v>2</v>
+        <v>62</v>
+      </c>
+      <c r="E111" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G111" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I111" s="1">
-        <v>2</v>
-      </c>
-      <c r="J111" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I111" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J111" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="E112" s="1">
-        <v>31778</v>
+        <v>65</v>
+      </c>
+      <c r="E112" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I112" s="1">
-        <v>45925</v>
-      </c>
-      <c r="J112" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I112" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J112" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>274</v>
-      </c>
-      <c r="E113" s="1">
-        <v>2</v>
+        <v>275</v>
+      </c>
+      <c r="E113" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I113" s="1">
-        <v>2</v>
-      </c>
-      <c r="J113" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I113" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J113" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>275</v>
-      </c>
-      <c r="E114" s="1">
-        <v>36258</v>
+        <v>276</v>
+      </c>
+      <c r="E114" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I114" s="1">
-        <v>45621</v>
-      </c>
-      <c r="J114" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I114" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J114" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>277</v>
-      </c>
-      <c r="E115" s="1">
-        <v>2</v>
+        <v>278</v>
+      </c>
+      <c r="E115" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I115" s="1">
-        <v>2</v>
-      </c>
-      <c r="J115" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I115" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J115" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>278</v>
-      </c>
-      <c r="E116" s="1">
-        <v>38760</v>
+        <v>279</v>
+      </c>
+      <c r="E116" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I116" s="1">
-        <v>45939</v>
-      </c>
-      <c r="J116" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I116" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J116" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="E117" s="1">
-        <v>2</v>
+        <v>194</v>
+      </c>
+      <c r="E117" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I117" s="1">
-        <v>45916</v>
-      </c>
-      <c r="J117" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I117" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J117" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>280</v>
-      </c>
-      <c r="E118" s="1">
-        <v>2</v>
+        <v>281</v>
+      </c>
+      <c r="E118" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I118" s="1">
-        <v>2</v>
-      </c>
-      <c r="J118" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I118" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J118" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>281</v>
-      </c>
-      <c r="E119" s="1">
-        <v>2</v>
+        <v>282</v>
+      </c>
+      <c r="E119" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I119" s="1">
-        <v>2</v>
-      </c>
-      <c r="J119" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I119" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J119" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>183</v>
-      </c>
-      <c r="E120" s="1">
-        <v>2</v>
+        <v>184</v>
+      </c>
+      <c r="E120" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I120" s="1">
-        <v>2</v>
-      </c>
-      <c r="J120" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I120" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J120" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>283</v>
-      </c>
-      <c r="E121" s="1">
-        <v>35469</v>
+        <v>284</v>
+      </c>
+      <c r="E121" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I121" s="1">
-        <v>45938</v>
-      </c>
-      <c r="J121" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I121" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J121" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>285</v>
-      </c>
-      <c r="E122" s="1">
-        <v>2</v>
+        <v>286</v>
+      </c>
+      <c r="E122" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I122" s="1">
-        <v>2</v>
-      </c>
-      <c r="J122" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I122" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J122" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>215</v>
-      </c>
-      <c r="E123" s="1">
-        <v>37483</v>
+        <v>216</v>
+      </c>
+      <c r="E123" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I123" s="1">
-        <v>45968</v>
-      </c>
-      <c r="J123" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I123" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J123" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>287</v>
-      </c>
-      <c r="E124" s="1">
-        <v>2</v>
+        <v>288</v>
+      </c>
+      <c r="E124" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I124" s="1">
-        <v>2</v>
-      </c>
-      <c r="J124" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I124" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J124" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>289</v>
-      </c>
-      <c r="E125" s="1">
-        <v>2</v>
+        <v>290</v>
+      </c>
+      <c r="E125" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I125" s="1">
-        <v>2</v>
-      </c>
-      <c r="J125" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I125" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J125" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>292</v>
-      </c>
-      <c r="E126" s="1">
-        <v>2</v>
+        <v>293</v>
+      </c>
+      <c r="E126" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I126" s="1">
-        <v>2</v>
-      </c>
-      <c r="J126" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I126" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J126" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>293</v>
-      </c>
-      <c r="E127" s="1">
-        <v>2</v>
+        <v>294</v>
+      </c>
+      <c r="E127" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G127" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I127" s="1">
-        <v>2</v>
-      </c>
-      <c r="J127" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I127" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J127" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="E128" s="1">
-        <v>34335</v>
+        <v>160</v>
+      </c>
+      <c r="E128" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G128" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I128" s="1">
-        <v>45552</v>
-      </c>
-      <c r="J128" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I128" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J128" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>183</v>
-      </c>
-      <c r="E129" s="1">
-        <v>2</v>
+        <v>184</v>
+      </c>
+      <c r="E129" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G129" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I129" s="1">
-        <v>2</v>
-      </c>
-      <c r="J129" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I129" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J129" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>169</v>
-      </c>
-      <c r="E130" s="1">
-        <v>35796</v>
+        <v>170</v>
+      </c>
+      <c r="E130" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G130" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I130" s="1">
-        <v>45545</v>
-      </c>
-      <c r="J130" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I130" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J130" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="E131" s="1">
-        <v>35591</v>
+        <v>52</v>
+      </c>
+      <c r="E131" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G131" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I131" s="1">
-        <v>45937</v>
-      </c>
-      <c r="J131" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I131" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J131" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>114</v>
-      </c>
-      <c r="E132" s="1">
-        <v>38226</v>
+        <v>115</v>
+      </c>
+      <c r="E132" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G132" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I132" s="1">
-        <v>45916</v>
-      </c>
-      <c r="J132" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I132" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J132" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>296</v>
-      </c>
-      <c r="E133" s="1">
-        <v>2</v>
+        <v>297</v>
+      </c>
+      <c r="E133" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G133" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I133" s="1">
-        <v>2</v>
-      </c>
-      <c r="J133" s="1">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="I133" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J133" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="E134" s="1">
-        <v>32278</v>
+        <v>54</v>
+      </c>
+      <c r="E134" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G134" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="I134" s="1">
-        <v>45925</v>
-      </c>
-      <c r="J134" s="1">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="I134" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="J134" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/liste_complete.xlsx
+++ b/Excel/liste_complete.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="298">
   <si>
     <t>GROUPE</t>
   </si>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>Nafyad</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Éthiopie</t>
@@ -950,8 +947,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="22" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -979,34 +977,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1023,23 +1021,23 @@
       <c r="D2" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1">
+        <v>36322</v>
+      </c>
+      <c r="F2" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="0" t="s">
-        <v>14</v>
-      </c>
       <c r="G2" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I2" s="1">
+        <v>45923</v>
+      </c>
+      <c r="J2" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1050,28 +1048,28 @@
         <v>10</v>
       </c>
       <c r="C3" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="E3" s="1">
+        <v>38760</v>
+      </c>
+      <c r="F3" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>19</v>
-      </c>
       <c r="G3" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I3" s="1">
+        <v>45939</v>
+      </c>
+      <c r="J3" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1082,28 +1080,28 @@
         <v>10</v>
       </c>
       <c r="C4" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="E4" s="1">
+        <v>35469</v>
+      </c>
+      <c r="F4" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="0" t="s">
+      <c r="G4" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="0" t="s">
-        <v>23</v>
-      </c>
       <c r="H4" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I4" s="1">
+        <v>45938</v>
+      </c>
+      <c r="J4" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1114,28 +1112,28 @@
         <v>10</v>
       </c>
       <c r="C5" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="E5" s="1">
+        <v>39050</v>
+      </c>
+      <c r="F5" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>27</v>
-      </c>
       <c r="G5" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I5" s="1">
+        <v>45967</v>
+      </c>
+      <c r="J5" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1146,28 +1144,28 @@
         <v>10</v>
       </c>
       <c r="C6" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>13</v>
+      <c r="E6" s="1">
+        <v>44633</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I6" s="1">
+        <v>45967</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1178,28 +1176,28 @@
         <v>10</v>
       </c>
       <c r="C7" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="E7" s="1">
+        <v>28876</v>
+      </c>
+      <c r="F7" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>32</v>
-      </c>
       <c r="G7" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I7" s="1">
+        <v>44934</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1210,28 +1208,28 @@
         <v>10</v>
       </c>
       <c r="C8" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="E8" s="1">
+        <v>2</v>
+      </c>
+      <c r="F8" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>35</v>
-      </c>
       <c r="G8" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I8" s="1">
+        <v>45981</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1242,28 +1240,28 @@
         <v>10</v>
       </c>
       <c r="C9" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>13</v>
+      <c r="E9" s="1">
+        <v>21680</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I9" s="1">
+        <v>45713</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1274,28 +1272,28 @@
         <v>10</v>
       </c>
       <c r="C10" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>13</v>
+      <c r="E10" s="1">
+        <v>33421</v>
       </c>
       <c r="F10" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="0" t="s">
-        <v>23</v>
-      </c>
       <c r="H10" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I10" s="1">
+        <v>45937</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1306,28 +1304,28 @@
         <v>10</v>
       </c>
       <c r="C11" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="E11" s="1">
+        <v>38947</v>
+      </c>
+      <c r="F11" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="0" t="s">
-        <v>42</v>
-      </c>
       <c r="G11" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I11" s="1">
+        <v>45939</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1338,28 +1336,28 @@
         <v>10</v>
       </c>
       <c r="C12" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="E12" s="1">
+        <v>19370</v>
+      </c>
+      <c r="F12" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="0" t="s">
+      <c r="G12" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="G12" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="H12" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I12" s="1">
+        <v>45939</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1370,28 +1368,28 @@
         <v>10</v>
       </c>
       <c r="C13" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>13</v>
+      <c r="E13" s="1">
+        <v>31088</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J13" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I13" s="1">
+        <v>45967</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1402,28 +1400,28 @@
         <v>10</v>
       </c>
       <c r="C14" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="0" t="s">
-        <v>13</v>
+      <c r="E14" s="1">
+        <v>23048</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J14" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I14" s="1">
+        <v>45545</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1434,28 +1432,28 @@
         <v>10</v>
       </c>
       <c r="C15" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="0" t="s">
-        <v>13</v>
+      <c r="E15" s="1">
+        <v>35591</v>
       </c>
       <c r="F15" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="0" t="s">
-        <v>23</v>
-      </c>
       <c r="H15" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J15" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I15" s="1">
+        <v>45937</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1466,316 +1464,316 @@
         <v>10</v>
       </c>
       <c r="C16" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="E16" s="1">
+        <v>32278</v>
+      </c>
+      <c r="F16" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="0" t="s">
-        <v>55</v>
-      </c>
       <c r="G16" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J16" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I16" s="1">
+        <v>45925</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="C17" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="D17" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="E17" s="1">
+        <v>23377</v>
+      </c>
+      <c r="F17" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="0" t="s">
-        <v>60</v>
-      </c>
       <c r="G17" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J17" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I17" s="1">
+        <v>45554</v>
+      </c>
+      <c r="J17" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="0" t="s">
-        <v>57</v>
-      </c>
       <c r="C18" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="F18" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="0" t="s">
-        <v>63</v>
-      </c>
       <c r="G18" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I18" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J18" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2</v>
+      </c>
+      <c r="J18" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="0" t="s">
-        <v>57</v>
-      </c>
       <c r="C19" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19" s="0" t="s">
-        <v>13</v>
+      <c r="E19" s="1">
+        <v>31778</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J19" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I19" s="1">
+        <v>45925</v>
+      </c>
+      <c r="J19" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="0" t="s">
-        <v>57</v>
-      </c>
       <c r="C20" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="E20" s="1">
+        <v>35935</v>
+      </c>
+      <c r="F20" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="0" t="s">
-        <v>68</v>
-      </c>
       <c r="G20" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J20" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I20" s="1">
+        <v>45965</v>
+      </c>
+      <c r="J20" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="0" t="s">
-        <v>57</v>
-      </c>
       <c r="C21" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="E21" s="1">
+        <v>33884</v>
+      </c>
+      <c r="F21" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="0" t="s">
-        <v>71</v>
-      </c>
       <c r="G21" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J21" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I21" s="1">
+        <v>45736</v>
+      </c>
+      <c r="J21" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="0" t="s">
-        <v>57</v>
-      </c>
       <c r="C22" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22" s="0" t="s">
-        <v>13</v>
+      <c r="E22" s="1">
+        <v>22184</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J22" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I22" s="1">
+        <v>45196</v>
+      </c>
+      <c r="J22" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="0" t="s">
-        <v>57</v>
-      </c>
       <c r="C23" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="E23" s="1">
+        <v>32725</v>
+      </c>
+      <c r="F23" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="E23" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="0" t="s">
-        <v>76</v>
-      </c>
       <c r="G23" s="0" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I23" s="1">
+        <v>45916</v>
+      </c>
+      <c r="J23" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="0" t="s">
-        <v>57</v>
-      </c>
       <c r="C24" s="0" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>13</v>
+        <v>76</v>
+      </c>
+      <c r="E24" s="1">
+        <v>31252</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J24" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I24" s="1">
+        <v>45916</v>
+      </c>
+      <c r="J24" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="0" t="s">
-        <v>57</v>
-      </c>
       <c r="C25" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="E25" s="0" t="s">
-        <v>13</v>
+      <c r="E25" s="1">
+        <v>30670</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I25" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J25" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I25" s="1">
+        <v>45903</v>
+      </c>
+      <c r="J25" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1783,31 +1781,31 @@
         <v>2</v>
       </c>
       <c r="B26" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="0" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="D26" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="D26" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="E26" s="0" t="s">
-        <v>13</v>
+      <c r="E26" s="1">
+        <v>30317</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I26" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J26" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I26" s="1">
+        <v>45545</v>
+      </c>
+      <c r="J26" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1815,31 +1813,31 @@
         <v>2</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C27" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="E27" s="0" t="s">
-        <v>13</v>
+      <c r="E27" s="1">
+        <v>2</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I27" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J27" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I27" s="1">
+        <v>45901</v>
+      </c>
+      <c r="J27" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1847,31 +1845,31 @@
         <v>2</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C28" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="D28" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="E28" s="0" t="s">
-        <v>13</v>
+      <c r="E28" s="1">
+        <v>36757</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I28" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J28" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I28" s="1">
+        <v>45923</v>
+      </c>
+      <c r="J28" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1879,31 +1877,31 @@
         <v>2</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C29" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="0" t="s">
         <v>87</v>
       </c>
-      <c r="D29" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="E29" s="0" t="s">
-        <v>13</v>
+      <c r="E29" s="1">
+        <v>29498</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I29" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J29" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I29" s="1">
+        <v>45636</v>
+      </c>
+      <c r="J29" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1911,31 +1909,31 @@
         <v>2</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C30" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="0" t="s">
-        <v>90</v>
-      </c>
-      <c r="E30" s="0" t="s">
-        <v>13</v>
+      <c r="E30" s="1">
+        <v>35522</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I30" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J30" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I30" s="1">
+        <v>45210</v>
+      </c>
+      <c r="J30" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1943,31 +1941,31 @@
         <v>2</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C31" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="0" t="s">
         <v>91</v>
       </c>
-      <c r="D31" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="E31" s="0" t="s">
+      <c r="E31" s="1">
+        <v>2</v>
+      </c>
+      <c r="F31" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="F31" s="0" t="s">
-        <v>14</v>
-      </c>
       <c r="G31" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I31" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J31" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I31" s="1">
+        <v>45916</v>
+      </c>
+      <c r="J31" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1975,31 +1973,31 @@
         <v>2</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C32" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="D32" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="E32" s="0" t="s">
-        <v>13</v>
+      <c r="E32" s="1">
+        <v>29262</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I32" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J32" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I32" s="1">
+        <v>45967</v>
+      </c>
+      <c r="J32" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2007,31 +2005,31 @@
         <v>2</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D33" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="1">
+        <v>29361</v>
+      </c>
+      <c r="F33" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="E33" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="0" t="s">
-        <v>71</v>
-      </c>
       <c r="G33" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J33" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I33" s="1">
+        <v>45968</v>
+      </c>
+      <c r="J33" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2039,31 +2037,31 @@
         <v>2</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C34" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="D34" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="E34" s="0" t="s">
-        <v>13</v>
+      <c r="E34" s="1">
+        <v>31650</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I34" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J34" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I34" s="1">
+        <v>44840</v>
+      </c>
+      <c r="J34" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2071,31 +2069,31 @@
         <v>2</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C35" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" s="0" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="E35" s="0" t="s">
-        <v>13</v>
+      <c r="E35" s="1">
+        <v>35430</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I35" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J35" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I35" s="1">
+        <v>45925</v>
+      </c>
+      <c r="J35" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2103,31 +2101,31 @@
         <v>2</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C36" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="D36" s="0" t="s">
         <v>99</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="E36" s="1">
+        <v>28688</v>
+      </c>
+      <c r="F36" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="E36" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="0" t="s">
-        <v>101</v>
-      </c>
       <c r="G36" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I36" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J36" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I36" s="1">
+        <v>45916</v>
+      </c>
+      <c r="J36" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2135,31 +2133,31 @@
         <v>2</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C37" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="D37" s="0" t="s">
         <v>102</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="E37" s="1">
+        <v>25720</v>
+      </c>
+      <c r="F37" s="0" t="s">
         <v>103</v>
       </c>
-      <c r="E37" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="0" t="s">
-        <v>104</v>
-      </c>
       <c r="G37" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I37" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J37" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I37" s="1">
+        <v>44880</v>
+      </c>
+      <c r="J37" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2167,31 +2165,31 @@
         <v>2</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C38" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" s="0" t="s">
         <v>105</v>
       </c>
-      <c r="D38" s="0" t="s">
-        <v>106</v>
-      </c>
-      <c r="E38" s="0" t="s">
-        <v>13</v>
+      <c r="E38" s="1">
+        <v>18937</v>
       </c>
       <c r="F38" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="G38" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="G38" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="H38" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I38" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J38" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I38" s="1">
+        <v>45910</v>
+      </c>
+      <c r="J38" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2199,31 +2197,31 @@
         <v>2</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C39" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" s="0" t="s">
         <v>107</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="E39" s="1">
+        <v>30866</v>
+      </c>
+      <c r="F39" s="0" t="s">
         <v>108</v>
       </c>
-      <c r="E39" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="0" t="s">
-        <v>109</v>
-      </c>
       <c r="G39" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I39" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J39" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I39" s="1">
+        <v>45901</v>
+      </c>
+      <c r="J39" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2231,31 +2229,31 @@
         <v>2</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C40" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="D40" s="0" t="s">
-        <v>111</v>
-      </c>
-      <c r="E40" s="0" t="s">
-        <v>13</v>
+      <c r="E40" s="1">
+        <v>38176</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I40" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J40" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I40" s="1">
+        <v>45903</v>
+      </c>
+      <c r="J40" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2263,31 +2261,31 @@
         <v>2</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C41" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="D41" s="0" t="s">
         <v>112</v>
       </c>
-      <c r="D41" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="E41" s="0" t="s">
-        <v>13</v>
+      <c r="E41" s="1">
+        <v>29711</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I41" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J41" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I41" s="1">
+        <v>45916</v>
+      </c>
+      <c r="J41" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2295,31 +2293,31 @@
         <v>2</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C42" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="D42" s="0" t="s">
         <v>114</v>
       </c>
-      <c r="D42" s="0" t="s">
-        <v>115</v>
-      </c>
-      <c r="E42" s="0" t="s">
+      <c r="E42" s="1">
+        <v>38226</v>
+      </c>
+      <c r="F42" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="0" t="s">
-        <v>14</v>
-      </c>
       <c r="G42" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I42" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J42" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I42" s="1">
+        <v>45916</v>
+      </c>
+      <c r="J42" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2327,31 +2325,31 @@
         <v>2</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C43" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="D43" s="0" t="s">
         <v>116</v>
       </c>
-      <c r="D43" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="E43" s="0" t="s">
-        <v>13</v>
+      <c r="E43" s="1">
+        <v>30991</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I43" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J43" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I43" s="1">
+        <v>45440</v>
+      </c>
+      <c r="J43" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2359,31 +2357,31 @@
         <v>2</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C44" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="D44" s="0" t="s">
         <v>118</v>
       </c>
-      <c r="D44" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="E44" s="0" t="s">
+      <c r="E44" s="1">
+        <v>35555</v>
+      </c>
+      <c r="F44" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="F44" s="0" t="s">
-        <v>14</v>
-      </c>
       <c r="G44" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I44" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J44" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I44" s="1">
+        <v>45911</v>
+      </c>
+      <c r="J44" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2391,31 +2389,31 @@
         <v>3</v>
       </c>
       <c r="B45" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="C45" s="0" t="s">
         <v>120</v>
       </c>
-      <c r="C45" s="0" t="s">
+      <c r="D45" s="0" t="s">
         <v>121</v>
       </c>
-      <c r="D45" s="0" t="s">
+      <c r="E45" s="1">
+        <v>27488</v>
+      </c>
+      <c r="F45" s="0" t="s">
         <v>122</v>
       </c>
-      <c r="E45" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F45" s="0" t="s">
-        <v>123</v>
-      </c>
       <c r="G45" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I45" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J45" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I45" s="1">
+        <v>45552</v>
+      </c>
+      <c r="J45" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -2423,31 +2421,31 @@
         <v>3</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C46" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="D46" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="D46" s="0" t="s">
-        <v>125</v>
-      </c>
-      <c r="E46" s="0" t="s">
-        <v>13</v>
+      <c r="E46" s="1">
+        <v>35565</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I46" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J46" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I46" s="1">
+        <v>45536</v>
+      </c>
+      <c r="J46" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -2455,31 +2453,31 @@
         <v>3</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C47" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="D47" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="D47" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="E47" s="0" t="s">
-        <v>13</v>
+      <c r="E47" s="1">
+        <v>27210</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I47" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J47" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I47" s="1">
+        <v>45694</v>
+      </c>
+      <c r="J47" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -2487,31 +2485,31 @@
         <v>3</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C48" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="D48" s="0" t="s">
         <v>128</v>
       </c>
-      <c r="D48" s="0" t="s">
+      <c r="E48" s="1">
+        <v>30317</v>
+      </c>
+      <c r="F48" s="0" t="s">
         <v>129</v>
       </c>
-      <c r="E48" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" s="0" t="s">
-        <v>130</v>
-      </c>
       <c r="G48" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I48" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J48" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I48" s="1">
+        <v>45009</v>
+      </c>
+      <c r="J48" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -2519,31 +2517,31 @@
         <v>3</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C49" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" s="0" t="s">
         <v>131</v>
       </c>
-      <c r="D49" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="E49" s="0" t="s">
-        <v>13</v>
+      <c r="E49" s="1">
+        <v>29137</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I49" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J49" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I49" s="1">
+        <v>45434</v>
+      </c>
+      <c r="J49" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -2551,31 +2549,31 @@
         <v>3</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C50" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="D50" s="0" t="s">
         <v>133</v>
       </c>
-      <c r="D50" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="E50" s="0" t="s">
-        <v>13</v>
+      <c r="E50" s="1">
+        <v>26685</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I50" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J50" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I50" s="1">
+        <v>45566</v>
+      </c>
+      <c r="J50" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -2583,31 +2581,31 @@
         <v>3</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C51" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="D51" s="0" t="s">
         <v>135</v>
       </c>
-      <c r="D51" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="E51" s="0" t="s">
-        <v>13</v>
+      <c r="E51" s="1">
+        <v>32089</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I51" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J51" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I51" s="1">
+        <v>45694</v>
+      </c>
+      <c r="J51" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -2615,31 +2613,31 @@
         <v>3</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C52" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="D52" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="D52" s="0" t="s">
-        <v>138</v>
-      </c>
-      <c r="E52" s="0" t="s">
-        <v>13</v>
+      <c r="E52" s="1">
+        <v>30993</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I52" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J52" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I52" s="1">
+        <v>45771</v>
+      </c>
+      <c r="J52" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -2647,31 +2645,31 @@
         <v>3</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C53" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="D53" s="0" t="s">
         <v>139</v>
       </c>
-      <c r="D53" s="0" t="s">
-        <v>140</v>
-      </c>
-      <c r="E53" s="0" t="s">
-        <v>13</v>
+      <c r="E53" s="1">
+        <v>31243</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I53" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J53" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I53" s="1">
+        <v>45547</v>
+      </c>
+      <c r="J53" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -2679,31 +2677,31 @@
         <v>3</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C54" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="D54" s="0" t="s">
         <v>141</v>
       </c>
-      <c r="D54" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="E54" s="0" t="s">
-        <v>13</v>
+      <c r="E54" s="1">
+        <v>36509</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I54" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J54" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I54" s="1">
+        <v>45923</v>
+      </c>
+      <c r="J54" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -2711,31 +2709,31 @@
         <v>3</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C55" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="D55" s="0" t="s">
         <v>143</v>
       </c>
-      <c r="D55" s="0" t="s">
+      <c r="E55" s="1">
+        <v>33008</v>
+      </c>
+      <c r="F55" s="0" t="s">
         <v>144</v>
       </c>
-      <c r="E55" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F55" s="0" t="s">
-        <v>145</v>
-      </c>
       <c r="G55" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I55" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J55" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I55" s="1">
+        <v>45669</v>
+      </c>
+      <c r="J55" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -2743,31 +2741,31 @@
         <v>3</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C56" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="D56" s="0" t="s">
         <v>146</v>
       </c>
-      <c r="D56" s="0" t="s">
+      <c r="E56" s="1">
+        <v>34847</v>
+      </c>
+      <c r="F56" s="0" t="s">
         <v>147</v>
       </c>
-      <c r="E56" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" s="0" t="s">
-        <v>148</v>
-      </c>
       <c r="G56" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I56" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J56" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I56" s="1">
+        <v>45170</v>
+      </c>
+      <c r="J56" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -2775,31 +2773,31 @@
         <v>3</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C57" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="D57" s="0" t="s">
         <v>149</v>
       </c>
-      <c r="D57" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="E57" s="0" t="s">
-        <v>13</v>
+      <c r="E57" s="1">
+        <v>28144</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I57" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J57" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I57" s="1">
+        <v>45901</v>
+      </c>
+      <c r="J57" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -2807,31 +2805,31 @@
         <v>3</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C58" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="D58" s="0" t="s">
         <v>151</v>
       </c>
-      <c r="D58" s="0" t="s">
+      <c r="E58" s="1">
+        <v>33332</v>
+      </c>
+      <c r="F58" s="0" t="s">
         <v>152</v>
       </c>
-      <c r="E58" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F58" s="0" t="s">
-        <v>153</v>
-      </c>
       <c r="G58" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I58" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J58" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I58" s="1">
+        <v>45678</v>
+      </c>
+      <c r="J58" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -2839,31 +2837,31 @@
         <v>3</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C59" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="D59" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="D59" s="0" t="s">
+      <c r="E59" s="1">
+        <v>30234</v>
+      </c>
+      <c r="F59" s="0" t="s">
         <v>155</v>
       </c>
-      <c r="E59" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" s="0" t="s">
-        <v>156</v>
-      </c>
       <c r="G59" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I59" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J59" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I59" s="1">
+        <v>45249</v>
+      </c>
+      <c r="J59" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -2871,31 +2869,31 @@
         <v>3</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C60" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="D60" s="0" t="s">
         <v>157</v>
       </c>
-      <c r="D60" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="E60" s="0" t="s">
-        <v>13</v>
+      <c r="E60" s="1">
+        <v>31836</v>
       </c>
       <c r="F60" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="G60" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="G60" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="H60" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I60" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J60" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I60" s="1">
+        <v>45617</v>
+      </c>
+      <c r="J60" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -2903,31 +2901,31 @@
         <v>3</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C61" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="D61" s="0" t="s">
         <v>159</v>
       </c>
-      <c r="D61" s="0" t="s">
-        <v>160</v>
-      </c>
-      <c r="E61" s="0" t="s">
-        <v>13</v>
+      <c r="E61" s="1">
+        <v>34335</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I61" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J61" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I61" s="1">
+        <v>45552</v>
+      </c>
+      <c r="J61" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -2935,31 +2933,31 @@
         <v>3</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C62" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="D62" s="0" t="s">
         <v>161</v>
       </c>
-      <c r="D62" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="E62" s="0" t="s">
-        <v>13</v>
+      <c r="E62" s="1">
+        <v>26206</v>
       </c>
       <c r="F62" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="G62" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="G62" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="H62" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I62" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J62" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I62" s="1">
+        <v>45545</v>
+      </c>
+      <c r="J62" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -2967,31 +2965,31 @@
         <v>3</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C63" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="D63" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="D63" s="0" t="s">
+      <c r="E63" s="1">
+        <v>25987</v>
+      </c>
+      <c r="F63" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="E63" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F63" s="0" t="s">
+      <c r="G63" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="G63" s="0" t="s">
-        <v>166</v>
-      </c>
       <c r="H63" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I63" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J63" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I63" s="1">
+        <v>45901</v>
+      </c>
+      <c r="J63" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -2999,31 +2997,31 @@
         <v>3</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C64" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="D64" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="D64" s="0" t="s">
-        <v>168</v>
-      </c>
-      <c r="E64" s="0" t="s">
-        <v>13</v>
+      <c r="E64" s="1">
+        <v>30926</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I64" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J64" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I64" s="1">
+        <v>45552</v>
+      </c>
+      <c r="J64" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -3031,31 +3029,31 @@
         <v>3</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C65" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="D65" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="D65" s="0" t="s">
+      <c r="E65" s="1">
+        <v>35796</v>
+      </c>
+      <c r="F65" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F65" s="0" t="s">
-        <v>171</v>
-      </c>
       <c r="G65" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I65" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J65" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I65" s="1">
+        <v>45545</v>
+      </c>
+      <c r="J65" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -3063,31 +3061,31 @@
         <v>3</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C66" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="D66" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="D66" s="0" t="s">
+      <c r="E66" s="1">
+        <v>20699</v>
+      </c>
+      <c r="F66" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="E66" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="0" t="s">
-        <v>174</v>
-      </c>
       <c r="G66" s="0" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I66" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J66" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I66" s="1">
+        <v>45246</v>
+      </c>
+      <c r="J66" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -3095,31 +3093,31 @@
         <v>3</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C67" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="D67" s="0" t="s">
         <v>175</v>
       </c>
-      <c r="D67" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="E67" s="0" t="s">
-        <v>13</v>
+      <c r="E67" s="1">
+        <v>29037</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I67" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J67" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I67" s="1">
+        <v>45536</v>
+      </c>
+      <c r="J67" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -3127,31 +3125,31 @@
         <v>4</v>
       </c>
       <c r="B68" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="C68" s="0" t="s">
         <v>177</v>
       </c>
-      <c r="C68" s="0" t="s">
+      <c r="D68" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="D68" s="0" t="s">
-        <v>179</v>
-      </c>
-      <c r="E68" s="0" t="s">
-        <v>13</v>
+      <c r="E68" s="1">
+        <v>33473</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I68" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J68" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I68" s="1">
+        <v>45981</v>
+      </c>
+      <c r="J68" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -3159,31 +3157,31 @@
         <v>4</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C69" s="0" t="s">
+        <v>179</v>
+      </c>
+      <c r="D69" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="D69" s="0" t="s">
+      <c r="E69" s="1">
+        <v>28855</v>
+      </c>
+      <c r="F69" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="E69" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F69" s="0" t="s">
-        <v>182</v>
-      </c>
       <c r="G69" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I69" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J69" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I69" s="1">
+        <v>45901</v>
+      </c>
+      <c r="J69" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -3191,31 +3189,31 @@
         <v>4</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C70" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="D70" s="0" t="s">
         <v>183</v>
       </c>
-      <c r="D70" s="0" t="s">
-        <v>184</v>
-      </c>
-      <c r="E70" s="0" t="s">
-        <v>13</v>
+      <c r="E70" s="1">
+        <v>34172</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I70" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J70" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I70" s="1">
+        <v>45413</v>
+      </c>
+      <c r="J70" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -3223,31 +3221,31 @@
         <v>4</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C71" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="D71" s="0" t="s">
         <v>185</v>
       </c>
-      <c r="D71" s="0" t="s">
-        <v>186</v>
-      </c>
-      <c r="E71" s="0" t="s">
-        <v>13</v>
+      <c r="E71" s="1">
+        <v>36258</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I71" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J71" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I71" s="1">
+        <v>45621</v>
+      </c>
+      <c r="J71" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -3255,31 +3253,31 @@
         <v>4</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C72" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="D72" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="D72" s="0" t="s">
-        <v>188</v>
-      </c>
-      <c r="E72" s="0" t="s">
-        <v>13</v>
+      <c r="E72" s="1">
+        <v>33217</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I72" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J72" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I72" s="1">
+        <v>45925</v>
+      </c>
+      <c r="J72" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -3287,31 +3285,31 @@
         <v>4</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C73" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="D73" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="D73" s="0" t="s">
-        <v>190</v>
-      </c>
-      <c r="E73" s="0" t="s">
-        <v>13</v>
+      <c r="E73" s="1">
+        <v>33695</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I73" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J73" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I73" s="1">
+        <v>44562</v>
+      </c>
+      <c r="J73" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -3319,31 +3317,31 @@
         <v>4</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C74" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="D74" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="D74" s="0" t="s">
-        <v>192</v>
-      </c>
-      <c r="E74" s="0" t="s">
-        <v>13</v>
+      <c r="E74" s="1">
+        <v>24778</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I74" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J74" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I74" s="1">
+        <v>45923</v>
+      </c>
+      <c r="J74" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -3351,31 +3349,31 @@
         <v>4</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C75" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="D75" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="D75" s="0" t="s">
-        <v>194</v>
-      </c>
-      <c r="E75" s="0" t="s">
-        <v>13</v>
+      <c r="E75" s="1">
+        <v>2</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I75" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J75" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I75" s="1">
+        <v>45916</v>
+      </c>
+      <c r="J75" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -3383,31 +3381,31 @@
         <v>4</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C76" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="D76" s="0" t="s">
         <v>195</v>
       </c>
-      <c r="D76" s="0" t="s">
-        <v>196</v>
-      </c>
-      <c r="E76" s="0" t="s">
-        <v>13</v>
+      <c r="E76" s="1">
+        <v>34699</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I76" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J76" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I76" s="1">
+        <v>45621</v>
+      </c>
+      <c r="J76" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -3415,31 +3413,31 @@
         <v>4</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C77" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="D77" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="D77" s="0" t="s">
-        <v>198</v>
-      </c>
-      <c r="E77" s="0" t="s">
-        <v>13</v>
+      <c r="E77" s="1">
+        <v>21551</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I77" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J77" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I77" s="1">
+        <v>44819</v>
+      </c>
+      <c r="J77" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -3447,31 +3445,31 @@
         <v>4</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C78" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="D78" s="0" t="s">
         <v>199</v>
       </c>
-      <c r="D78" s="0" t="s">
-        <v>200</v>
-      </c>
-      <c r="E78" s="0" t="s">
-        <v>13</v>
+      <c r="E78" s="1">
+        <v>2</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I78" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J78" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I78" s="1">
+        <v>45987</v>
+      </c>
+      <c r="J78" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -3479,31 +3477,31 @@
         <v>4</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C79" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="D79" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="D79" s="0" t="s">
-        <v>202</v>
-      </c>
-      <c r="E79" s="0" t="s">
-        <v>13</v>
+      <c r="E79" s="1">
+        <v>36219</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I79" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J79" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I79" s="1">
+        <v>45939</v>
+      </c>
+      <c r="J79" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -3511,31 +3509,31 @@
         <v>4</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C80" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="D80" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="D80" s="0" t="s">
+      <c r="E80" s="1">
+        <v>28275</v>
+      </c>
+      <c r="F80" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="E80" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F80" s="0" t="s">
-        <v>205</v>
-      </c>
       <c r="G80" s="0" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I80" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J80" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I80" s="1">
+        <v>44691</v>
+      </c>
+      <c r="J80" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -3543,31 +3541,31 @@
         <v>4</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C81" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="D81" s="0" t="s">
         <v>206</v>
       </c>
-      <c r="D81" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="E81" s="0" t="s">
-        <v>13</v>
+      <c r="E81" s="1">
+        <v>30159</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I81" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J81" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I81" s="1">
+        <v>45916</v>
+      </c>
+      <c r="J81" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -3575,31 +3573,31 @@
         <v>4</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C82" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="D82" s="0" t="s">
         <v>208</v>
       </c>
-      <c r="D82" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="E82" s="0" t="s">
-        <v>13</v>
+      <c r="E82" s="1">
+        <v>36955</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I82" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J82" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I82" s="1">
+        <v>45916</v>
+      </c>
+      <c r="J82" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -3607,31 +3605,31 @@
         <v>4</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C83" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="D83" s="0" t="s">
         <v>210</v>
       </c>
-      <c r="D83" s="0" t="s">
+      <c r="E83" s="1">
+        <v>37640</v>
+      </c>
+      <c r="F83" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="E83" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="0" t="s">
-        <v>212</v>
-      </c>
       <c r="G83" s="0" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I83" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J83" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I83" s="1">
+        <v>45918</v>
+      </c>
+      <c r="J83" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -3639,31 +3637,31 @@
         <v>4</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C84" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="D84" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="D84" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="E84" s="0" t="s">
-        <v>13</v>
+      <c r="E84" s="1">
+        <v>32323</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I84" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J84" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I84" s="1">
+        <v>45910</v>
+      </c>
+      <c r="J84" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -3671,31 +3669,31 @@
         <v>4</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C85" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="D85" s="0" t="s">
         <v>215</v>
       </c>
-      <c r="D85" s="0" t="s">
-        <v>216</v>
-      </c>
-      <c r="E85" s="0" t="s">
-        <v>13</v>
+      <c r="E85" s="1">
+        <v>37483</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I85" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J85" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I85" s="1">
+        <v>45968</v>
+      </c>
+      <c r="J85" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -3703,31 +3701,31 @@
         <v>4</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C86" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="D86" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="D86" s="0" t="s">
-        <v>218</v>
-      </c>
-      <c r="E86" s="0" t="s">
-        <v>13</v>
+      <c r="E86" s="1">
+        <v>28932</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I86" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J86" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I86" s="1">
+        <v>45986</v>
+      </c>
+      <c r="J86" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -3735,31 +3733,31 @@
         <v>4</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C87" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="D87" s="0" t="s">
         <v>219</v>
       </c>
-      <c r="D87" s="0" t="s">
-        <v>220</v>
-      </c>
-      <c r="E87" s="0" t="s">
-        <v>13</v>
+      <c r="E87" s="1">
+        <v>43249</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I87" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J87" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I87" s="1">
+        <v>45975</v>
+      </c>
+      <c r="J87" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -3767,31 +3765,31 @@
         <v>4</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C88" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="D88" s="0" t="s">
         <v>221</v>
       </c>
-      <c r="D88" s="0" t="s">
-        <v>222</v>
-      </c>
-      <c r="E88" s="0" t="s">
-        <v>13</v>
+      <c r="E88" s="1">
+        <v>34545</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I88" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J88" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I88" s="1">
+        <v>45975</v>
+      </c>
+      <c r="J88" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -3799,31 +3797,31 @@
         <v>4</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C89" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="D89" s="0" t="s">
         <v>223</v>
       </c>
-      <c r="D89" s="0" t="s">
-        <v>224</v>
-      </c>
-      <c r="E89" s="0" t="s">
-        <v>13</v>
+      <c r="E89" s="1">
+        <v>29561</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I89" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J89" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I89" s="1">
+        <v>45981</v>
+      </c>
+      <c r="J89" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -3831,31 +3829,31 @@
         <v>4</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C90" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="D90" s="0" t="s">
         <v>225</v>
       </c>
-      <c r="D90" s="0" t="s">
-        <v>226</v>
-      </c>
-      <c r="E90" s="0" t="s">
-        <v>13</v>
+      <c r="E90" s="1">
+        <v>31760</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I90" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J90" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I90" s="1">
+        <v>45445</v>
+      </c>
+      <c r="J90" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -3863,31 +3861,31 @@
         <v>4</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C91" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="D91" s="0" t="s">
         <v>227</v>
       </c>
-      <c r="D91" s="0" t="s">
+      <c r="E91" s="1">
+        <v>33921</v>
+      </c>
+      <c r="F91" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="E91" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F91" s="0" t="s">
-        <v>229</v>
-      </c>
       <c r="G91" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I91" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J91" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I91" s="1">
+        <v>45916</v>
+      </c>
+      <c r="J91" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -3895,31 +3893,31 @@
         <v>4</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C92" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="D92" s="0" t="s">
         <v>230</v>
       </c>
-      <c r="D92" s="0" t="s">
+      <c r="E92" s="1">
+        <v>35384</v>
+      </c>
+      <c r="F92" s="0" t="s">
         <v>231</v>
       </c>
-      <c r="E92" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F92" s="0" t="s">
-        <v>232</v>
-      </c>
       <c r="G92" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I92" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J92" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I92" s="1">
+        <v>45566</v>
+      </c>
+      <c r="J92" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -3927,31 +3925,31 @@
         <v>4</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C93" s="0" t="s">
+        <v>232</v>
+      </c>
+      <c r="D93" s="0" t="s">
         <v>233</v>
       </c>
-      <c r="D93" s="0" t="s">
-        <v>234</v>
-      </c>
-      <c r="E93" s="0" t="s">
-        <v>13</v>
+      <c r="E93" s="1">
+        <v>30580</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I93" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J93" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I93" s="1">
+        <v>44481</v>
+      </c>
+      <c r="J93" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -3959,31 +3957,31 @@
         <v>4</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C94" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="D94" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="D94" s="0" t="s">
-        <v>236</v>
-      </c>
-      <c r="E94" s="0" t="s">
-        <v>13</v>
+      <c r="E94" s="1">
+        <v>23021</v>
       </c>
       <c r="F94" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="G94" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="G94" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="H94" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I94" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J94" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I94" s="1">
+        <v>42381</v>
+      </c>
+      <c r="J94" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -3991,31 +3989,31 @@
         <v>4</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C95" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="D95" s="0" t="s">
         <v>237</v>
       </c>
-      <c r="D95" s="0" t="s">
+      <c r="E95" s="1">
+        <v>34840</v>
+      </c>
+      <c r="F95" s="0" t="s">
         <v>238</v>
       </c>
-      <c r="E95" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F95" s="0" t="s">
-        <v>239</v>
-      </c>
       <c r="G95" s="0" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I95" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J95" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I95" s="1">
+        <v>45722</v>
+      </c>
+      <c r="J95" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -4023,31 +4021,31 @@
         <v>5</v>
       </c>
       <c r="B96" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="C96" s="0" t="s">
         <v>240</v>
       </c>
-      <c r="C96" s="0" t="s">
+      <c r="D96" s="0" t="s">
         <v>241</v>
       </c>
-      <c r="D96" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="E96" s="0" t="s">
-        <v>13</v>
+      <c r="E96" s="1">
+        <v>26978</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I96" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J96" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I96" s="1">
+        <v>44810</v>
+      </c>
+      <c r="J96" s="1">
+        <v>45992</v>
       </c>
     </row>
     <row r="97">
@@ -4055,31 +4053,31 @@
         <v>5</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C97" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="D97" s="0" t="s">
         <v>243</v>
       </c>
-      <c r="D97" s="0" t="s">
-        <v>244</v>
-      </c>
-      <c r="E97" s="0" t="s">
-        <v>13</v>
+      <c r="E97" s="1">
+        <v>38905</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I97" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J97" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I97" s="1">
+        <v>45911</v>
+      </c>
+      <c r="J97" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -4087,31 +4085,31 @@
         <v>5</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C98" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="D98" s="0" t="s">
         <v>245</v>
       </c>
-      <c r="D98" s="0" t="s">
-        <v>246</v>
-      </c>
-      <c r="E98" s="0" t="s">
-        <v>13</v>
+      <c r="E98" s="1">
+        <v>2</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I98" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J98" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I98" s="1">
+        <v>45673</v>
+      </c>
+      <c r="J98" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -4119,31 +4117,31 @@
         <v>5</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C99" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="D99" s="0" t="s">
         <v>247</v>
       </c>
-      <c r="D99" s="0" t="s">
-        <v>248</v>
-      </c>
-      <c r="E99" s="0" t="s">
-        <v>13</v>
+      <c r="E99" s="1">
+        <v>34630</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I99" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J99" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I99" s="1">
+        <v>45077</v>
+      </c>
+      <c r="J99" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -4151,31 +4149,31 @@
         <v>5</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C100" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="D100" s="0" t="s">
         <v>249</v>
       </c>
-      <c r="D100" s="0" t="s">
-        <v>250</v>
-      </c>
-      <c r="E100" s="0" t="s">
-        <v>13</v>
+      <c r="E100" s="1">
+        <v>28909</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I100" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J100" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I100" s="1">
+        <v>45239</v>
+      </c>
+      <c r="J100" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -4183,31 +4181,31 @@
         <v>5</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C101" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="D101" s="0" t="s">
         <v>251</v>
       </c>
-      <c r="D101" s="0" t="s">
-        <v>252</v>
-      </c>
-      <c r="E101" s="0" t="s">
-        <v>13</v>
+      <c r="E101" s="1">
+        <v>33653</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I101" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J101" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I101" s="1">
+        <v>45189</v>
+      </c>
+      <c r="J101" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -4215,31 +4213,31 @@
         <v>5</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C102" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="D102" s="0" t="s">
         <v>253</v>
       </c>
-      <c r="D102" s="0" t="s">
-        <v>254</v>
-      </c>
-      <c r="E102" s="0" t="s">
-        <v>13</v>
+      <c r="E102" s="1">
+        <v>34335</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I102" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J102" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I102" s="1">
+        <v>45689</v>
+      </c>
+      <c r="J102" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -4247,31 +4245,31 @@
         <v>5</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C103" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="D103" s="0" t="s">
         <v>255</v>
       </c>
-      <c r="D103" s="0" t="s">
-        <v>256</v>
-      </c>
-      <c r="E103" s="0" t="s">
-        <v>13</v>
+      <c r="E103" s="1">
+        <v>33049</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I103" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J103" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I103" s="1">
+        <v>45916</v>
+      </c>
+      <c r="J103" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -4279,31 +4277,31 @@
         <v>5</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C104" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="D104" s="0" t="s">
         <v>257</v>
       </c>
-      <c r="D104" s="0" t="s">
-        <v>258</v>
-      </c>
-      <c r="E104" s="0" t="s">
-        <v>13</v>
+      <c r="E104" s="1">
+        <v>34459</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I104" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J104" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I104" s="1">
+        <v>45925</v>
+      </c>
+      <c r="J104" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -4311,31 +4309,31 @@
         <v>5</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C105" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="D105" s="0" t="s">
         <v>259</v>
       </c>
-      <c r="D105" s="0" t="s">
-        <v>260</v>
-      </c>
-      <c r="E105" s="0" t="s">
-        <v>13</v>
+      <c r="E105" s="1">
+        <v>33133</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I105" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J105" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I105" s="1">
+        <v>43642</v>
+      </c>
+      <c r="J105" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -4343,31 +4341,31 @@
         <v>5</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C106" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="D106" s="0" t="s">
         <v>261</v>
       </c>
-      <c r="D106" s="0" t="s">
+      <c r="E106" s="1">
+        <v>34335</v>
+      </c>
+      <c r="F106" s="0" t="s">
         <v>262</v>
       </c>
-      <c r="E106" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F106" s="0" t="s">
-        <v>263</v>
-      </c>
       <c r="G106" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I106" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J106" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I106" s="1">
+        <v>45554</v>
+      </c>
+      <c r="J106" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -4375,31 +4373,31 @@
         <v>5</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C107" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="D107" s="0" t="s">
         <v>264</v>
       </c>
-      <c r="D107" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="E107" s="0" t="s">
-        <v>13</v>
+      <c r="E107" s="1">
+        <v>27776</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I107" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J107" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I107" s="1">
+        <v>45552</v>
+      </c>
+      <c r="J107" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -4407,31 +4405,31 @@
         <v>5</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C108" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="D108" s="0" t="s">
         <v>266</v>
       </c>
-      <c r="D108" s="0" t="s">
-        <v>267</v>
-      </c>
-      <c r="E108" s="0" t="s">
-        <v>13</v>
+      <c r="E108" s="1">
+        <v>31561</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I108" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J108" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I108" s="1">
+        <v>45783</v>
+      </c>
+      <c r="J108" s="1">
+        <v>45992</v>
       </c>
     </row>
     <row r="109">
@@ -4439,831 +4437,831 @@
         <v>5</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C109" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="D109" s="0" t="s">
         <v>268</v>
       </c>
-      <c r="D109" s="0" t="s">
-        <v>269</v>
-      </c>
-      <c r="E109" s="0" t="s">
-        <v>13</v>
+      <c r="E109" s="1">
+        <v>32692</v>
       </c>
       <c r="F109" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="G109" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="G109" s="0" t="s">
-        <v>166</v>
-      </c>
       <c r="H109" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I109" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J109" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I109" s="1">
+        <v>45673</v>
+      </c>
+      <c r="J109" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B110" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B110" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C110" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="D110" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="D110" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="E110" s="0" t="s">
-        <v>13</v>
+      <c r="E110" s="1">
+        <v>30317</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I110" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J110" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I110" s="1">
+        <v>45545</v>
+      </c>
+      <c r="J110" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B111" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B111" s="0" t="s">
+      <c r="C111" s="0" t="s">
         <v>271</v>
       </c>
-      <c r="C111" s="0" t="s">
-        <v>272</v>
-      </c>
       <c r="D111" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="E111" s="0" t="s">
-        <v>13</v>
+        <v>61</v>
+      </c>
+      <c r="E111" s="1">
+        <v>2</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G111" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I111" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J111" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I111" s="1">
+        <v>2</v>
+      </c>
+      <c r="J111" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B112" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B112" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C112" s="0" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="E112" s="0" t="s">
-        <v>13</v>
+        <v>64</v>
+      </c>
+      <c r="E112" s="1">
+        <v>31778</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I112" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J112" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I112" s="1">
+        <v>45925</v>
+      </c>
+      <c r="J112" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B113" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B113" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C113" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="D113" s="0" t="s">
         <v>274</v>
       </c>
-      <c r="D113" s="0" t="s">
-        <v>275</v>
-      </c>
-      <c r="E113" s="0" t="s">
-        <v>13</v>
+      <c r="E113" s="1">
+        <v>2</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I113" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J113" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I113" s="1">
+        <v>2</v>
+      </c>
+      <c r="J113" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B114" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B114" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C114" s="0" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>276</v>
-      </c>
-      <c r="E114" s="0" t="s">
-        <v>13</v>
+        <v>275</v>
+      </c>
+      <c r="E114" s="1">
+        <v>36258</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I114" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J114" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I114" s="1">
+        <v>45621</v>
+      </c>
+      <c r="J114" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B115" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B115" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C115" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="D115" s="0" t="s">
         <v>277</v>
       </c>
-      <c r="D115" s="0" t="s">
-        <v>278</v>
-      </c>
-      <c r="E115" s="0" t="s">
-        <v>13</v>
+      <c r="E115" s="1">
+        <v>2</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I115" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J115" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I115" s="1">
+        <v>2</v>
+      </c>
+      <c r="J115" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B116" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B116" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C116" s="0" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>279</v>
-      </c>
-      <c r="E116" s="0" t="s">
-        <v>13</v>
+        <v>278</v>
+      </c>
+      <c r="E116" s="1">
+        <v>38760</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I116" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J116" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I116" s="1">
+        <v>45939</v>
+      </c>
+      <c r="J116" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B117" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B117" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C117" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="D117" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="D117" s="0" t="s">
-        <v>194</v>
-      </c>
-      <c r="E117" s="0" t="s">
-        <v>13</v>
+      <c r="E117" s="1">
+        <v>2</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I117" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J117" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I117" s="1">
+        <v>45916</v>
+      </c>
+      <c r="J117" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B118" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B118" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C118" s="0" t="s">
+        <v>279</v>
+      </c>
+      <c r="D118" s="0" t="s">
         <v>280</v>
       </c>
-      <c r="D118" s="0" t="s">
-        <v>281</v>
-      </c>
-      <c r="E118" s="0" t="s">
-        <v>13</v>
+      <c r="E118" s="1">
+        <v>2</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I118" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J118" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I118" s="1">
+        <v>2</v>
+      </c>
+      <c r="J118" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B119" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B119" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C119" s="0" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>282</v>
-      </c>
-      <c r="E119" s="0" t="s">
-        <v>13</v>
+        <v>281</v>
+      </c>
+      <c r="E119" s="1">
+        <v>2</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I119" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J119" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I119" s="1">
+        <v>2</v>
+      </c>
+      <c r="J119" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B120" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B120" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C120" s="0" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>184</v>
-      </c>
-      <c r="E120" s="0" t="s">
-        <v>13</v>
+        <v>183</v>
+      </c>
+      <c r="E120" s="1">
+        <v>2</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I120" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J120" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I120" s="1">
+        <v>2</v>
+      </c>
+      <c r="J120" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B121" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B121" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C121" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>284</v>
-      </c>
-      <c r="E121" s="0" t="s">
-        <v>13</v>
+        <v>283</v>
+      </c>
+      <c r="E121" s="1">
+        <v>35469</v>
       </c>
       <c r="F121" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="G121" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="G121" s="0" t="s">
-        <v>23</v>
-      </c>
       <c r="H121" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I121" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J121" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I121" s="1">
+        <v>45938</v>
+      </c>
+      <c r="J121" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B122" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B122" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C122" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="D122" s="0" t="s">
         <v>285</v>
       </c>
-      <c r="D122" s="0" t="s">
-        <v>286</v>
-      </c>
-      <c r="E122" s="0" t="s">
-        <v>13</v>
+      <c r="E122" s="1">
+        <v>2</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I122" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J122" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I122" s="1">
+        <v>2</v>
+      </c>
+      <c r="J122" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B123" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B123" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C123" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="D123" s="0" t="s">
         <v>215</v>
       </c>
-      <c r="D123" s="0" t="s">
-        <v>216</v>
-      </c>
-      <c r="E123" s="0" t="s">
-        <v>13</v>
+      <c r="E123" s="1">
+        <v>37483</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I123" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J123" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I123" s="1">
+        <v>45968</v>
+      </c>
+      <c r="J123" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B124" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B124" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C124" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="D124" s="0" t="s">
         <v>287</v>
       </c>
-      <c r="D124" s="0" t="s">
-        <v>288</v>
-      </c>
-      <c r="E124" s="0" t="s">
-        <v>13</v>
+      <c r="E124" s="1">
+        <v>2</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I124" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J124" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I124" s="1">
+        <v>2</v>
+      </c>
+      <c r="J124" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B125" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B125" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C125" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="D125" s="0" t="s">
         <v>289</v>
       </c>
-      <c r="D125" s="0" t="s">
+      <c r="E125" s="1">
+        <v>2</v>
+      </c>
+      <c r="F125" s="0" t="s">
         <v>290</v>
       </c>
-      <c r="E125" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F125" s="0" t="s">
-        <v>291</v>
-      </c>
       <c r="G125" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I125" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J125" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I125" s="1">
+        <v>2</v>
+      </c>
+      <c r="J125" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B126" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B126" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C126" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="D126" s="0" t="s">
         <v>292</v>
       </c>
-      <c r="D126" s="0" t="s">
-        <v>293</v>
-      </c>
-      <c r="E126" s="0" t="s">
-        <v>13</v>
+      <c r="E126" s="1">
+        <v>2</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I126" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J126" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I126" s="1">
+        <v>2</v>
+      </c>
+      <c r="J126" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B127" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B127" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C127" s="0" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>294</v>
-      </c>
-      <c r="E127" s="0" t="s">
-        <v>13</v>
+        <v>293</v>
+      </c>
+      <c r="E127" s="1">
+        <v>2</v>
       </c>
       <c r="F127" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="G127" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="G127" s="0" t="s">
-        <v>23</v>
-      </c>
       <c r="H127" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I127" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J127" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I127" s="1">
+        <v>2</v>
+      </c>
+      <c r="J127" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B128" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B128" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C128" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="D128" s="0" t="s">
         <v>159</v>
       </c>
-      <c r="D128" s="0" t="s">
-        <v>160</v>
-      </c>
-      <c r="E128" s="0" t="s">
-        <v>13</v>
+      <c r="E128" s="1">
+        <v>34335</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G128" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I128" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J128" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I128" s="1">
+        <v>45552</v>
+      </c>
+      <c r="J128" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B129" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B129" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C129" s="0" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>184</v>
-      </c>
-      <c r="E129" s="0" t="s">
-        <v>13</v>
+        <v>183</v>
+      </c>
+      <c r="E129" s="1">
+        <v>2</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G129" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I129" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J129" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I129" s="1">
+        <v>2</v>
+      </c>
+      <c r="J129" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B130" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B130" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C130" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="D130" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="D130" s="0" t="s">
+      <c r="E130" s="1">
+        <v>35796</v>
+      </c>
+      <c r="F130" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="E130" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F130" s="0" t="s">
-        <v>171</v>
-      </c>
       <c r="G130" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I130" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J130" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I130" s="1">
+        <v>45545</v>
+      </c>
+      <c r="J130" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B131" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B131" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C131" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="D131" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="D131" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="E131" s="0" t="s">
-        <v>13</v>
+      <c r="E131" s="1">
+        <v>35591</v>
       </c>
       <c r="F131" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="G131" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="G131" s="0" t="s">
-        <v>23</v>
-      </c>
       <c r="H131" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I131" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J131" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I131" s="1">
+        <v>45937</v>
+      </c>
+      <c r="J131" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B132" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B132" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C132" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="D132" s="0" t="s">
         <v>114</v>
       </c>
-      <c r="D132" s="0" t="s">
-        <v>115</v>
-      </c>
-      <c r="E132" s="0" t="s">
+      <c r="E132" s="1">
+        <v>38226</v>
+      </c>
+      <c r="F132" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="F132" s="0" t="s">
-        <v>14</v>
-      </c>
       <c r="G132" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I132" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J132" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I132" s="1">
+        <v>45916</v>
+      </c>
+      <c r="J132" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B133" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B133" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C133" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="D133" s="0" t="s">
         <v>296</v>
       </c>
-      <c r="D133" s="0" t="s">
+      <c r="E133" s="1">
+        <v>2</v>
+      </c>
+      <c r="F133" s="0" t="s">
         <v>297</v>
       </c>
-      <c r="E133" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F133" s="0" t="s">
-        <v>298</v>
-      </c>
       <c r="G133" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="I133" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J133" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I133" s="1">
+        <v>2</v>
+      </c>
+      <c r="J133" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B134" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B134" s="0" t="s">
-        <v>271</v>
-      </c>
       <c r="C134" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="D134" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="D134" s="0" t="s">
+      <c r="E134" s="1">
+        <v>32278</v>
+      </c>
+      <c r="F134" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="E134" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F134" s="0" t="s">
-        <v>55</v>
-      </c>
       <c r="G134" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I134" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J134" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I134" s="1">
+        <v>45925</v>
+      </c>
+      <c r="J134" s="1">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
